--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -387,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O957"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -440,6 +440,5741 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4">
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <f t="shared" ref="A68:A131" si="1">A67+1</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <f t="shared" ref="A132:A195" si="2">A131+1</f>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <f t="shared" si="2"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <f t="shared" si="2"/>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <f t="shared" si="2"/>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <f t="shared" si="2"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <f t="shared" si="2"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <f t="shared" si="2"/>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <f t="shared" si="2"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <f t="shared" si="2"/>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <f t="shared" si="2"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <f t="shared" si="2"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <f t="shared" si="2"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <f t="shared" si="2"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <f t="shared" si="2"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <f t="shared" si="2"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <f t="shared" si="2"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <f t="shared" si="2"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <f t="shared" si="2"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <f t="shared" si="2"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <f t="shared" si="2"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <f t="shared" si="2"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <f t="shared" si="2"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <f t="shared" si="2"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <f t="shared" si="2"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <f t="shared" si="2"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <f t="shared" si="2"/>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <f t="shared" si="2"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <f t="shared" si="2"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <f t="shared" si="2"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <f t="shared" si="2"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <f t="shared" si="2"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <f t="shared" si="2"/>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <f t="shared" si="2"/>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <f t="shared" si="2"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <f t="shared" si="2"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <f t="shared" ref="A196:A259" si="3">A195+1</f>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <f t="shared" si="3"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <f t="shared" si="3"/>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <f t="shared" si="3"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <f t="shared" si="3"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <f t="shared" si="3"/>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <f t="shared" si="3"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <f t="shared" si="3"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <f t="shared" si="3"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <f t="shared" si="3"/>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <f t="shared" si="3"/>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <f t="shared" si="3"/>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <f t="shared" si="3"/>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <f t="shared" si="3"/>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <f t="shared" si="3"/>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <f t="shared" si="3"/>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <f t="shared" si="3"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <f t="shared" si="3"/>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <f t="shared" si="3"/>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <f t="shared" si="3"/>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <f t="shared" si="3"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <f t="shared" si="3"/>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <f t="shared" si="3"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <f t="shared" si="3"/>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <f t="shared" si="3"/>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <f t="shared" si="3"/>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <f t="shared" si="3"/>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <f t="shared" si="3"/>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <f t="shared" si="3"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <f t="shared" si="3"/>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <f t="shared" si="3"/>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <f t="shared" si="3"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <f t="shared" si="3"/>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <f t="shared" si="3"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <f t="shared" si="3"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <f t="shared" si="3"/>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <f t="shared" si="3"/>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <f t="shared" si="3"/>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <f t="shared" si="3"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <f t="shared" si="3"/>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <f t="shared" si="3"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <f t="shared" si="3"/>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <f t="shared" si="3"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <f t="shared" si="3"/>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <f t="shared" si="3"/>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <f t="shared" si="3"/>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <f t="shared" si="3"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <f t="shared" si="3"/>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <f t="shared" si="3"/>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <f t="shared" si="3"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <f t="shared" si="3"/>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <f t="shared" si="3"/>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <f t="shared" si="3"/>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <f t="shared" si="3"/>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <f t="shared" si="3"/>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <f t="shared" ref="A260:A323" si="4">A259+1</f>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <f t="shared" si="4"/>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <f t="shared" si="4"/>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <f t="shared" si="4"/>
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <f t="shared" si="4"/>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <f t="shared" si="4"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <f t="shared" si="4"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <f t="shared" si="4"/>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <f t="shared" si="4"/>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <f t="shared" si="4"/>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <f t="shared" si="4"/>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <f t="shared" si="4"/>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <f t="shared" si="4"/>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <f t="shared" si="4"/>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <f t="shared" si="4"/>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <f t="shared" si="4"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <f t="shared" si="4"/>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <f t="shared" si="4"/>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <f t="shared" si="4"/>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <f t="shared" si="4"/>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <f t="shared" si="4"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <f t="shared" si="4"/>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <f t="shared" si="4"/>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <f t="shared" si="4"/>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <f t="shared" si="4"/>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <f t="shared" si="4"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <f t="shared" si="4"/>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <f t="shared" si="4"/>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290">
+        <f t="shared" si="4"/>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291">
+        <f t="shared" si="4"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292">
+        <f t="shared" si="4"/>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293">
+        <f t="shared" si="4"/>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294">
+        <f t="shared" si="4"/>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295">
+        <f t="shared" si="4"/>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296">
+        <f t="shared" si="4"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297">
+        <f t="shared" si="4"/>
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298">
+        <f t="shared" si="4"/>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299">
+        <f t="shared" si="4"/>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300">
+        <f t="shared" si="4"/>
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302">
+        <f t="shared" si="4"/>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303">
+        <f t="shared" si="4"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304">
+        <f t="shared" si="4"/>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305">
+        <f t="shared" si="4"/>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306">
+        <f t="shared" si="4"/>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307">
+        <f t="shared" si="4"/>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308">
+        <f t="shared" si="4"/>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309">
+        <f t="shared" si="4"/>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310">
+        <f t="shared" si="4"/>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311">
+        <f t="shared" si="4"/>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312">
+        <f t="shared" si="4"/>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313">
+        <f t="shared" si="4"/>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314">
+        <f t="shared" si="4"/>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315">
+        <f t="shared" si="4"/>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316">
+        <f t="shared" si="4"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317">
+        <f t="shared" si="4"/>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318">
+        <f t="shared" si="4"/>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319">
+        <f t="shared" si="4"/>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320">
+        <f t="shared" si="4"/>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321">
+        <f t="shared" si="4"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322">
+        <f t="shared" si="4"/>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323">
+        <f t="shared" si="4"/>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324">
+        <f t="shared" ref="A324:A387" si="5">A323+1</f>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325">
+        <f t="shared" si="5"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326">
+        <f t="shared" si="5"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327">
+        <f t="shared" si="5"/>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328">
+        <f t="shared" si="5"/>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329">
+        <f t="shared" si="5"/>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330">
+        <f t="shared" si="5"/>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331">
+        <f t="shared" si="5"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332">
+        <f t="shared" si="5"/>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333">
+        <f t="shared" si="5"/>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334">
+        <f t="shared" si="5"/>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335">
+        <f t="shared" si="5"/>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336">
+        <f t="shared" si="5"/>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337">
+        <f t="shared" si="5"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338">
+        <f t="shared" si="5"/>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339">
+        <f t="shared" si="5"/>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340">
+        <f t="shared" si="5"/>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341">
+        <f t="shared" si="5"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342">
+        <f t="shared" si="5"/>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343">
+        <f t="shared" si="5"/>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344">
+        <f t="shared" si="5"/>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345">
+        <f t="shared" si="5"/>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346">
+        <f t="shared" si="5"/>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347">
+        <f t="shared" si="5"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348">
+        <f t="shared" si="5"/>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349">
+        <f t="shared" si="5"/>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350">
+        <f t="shared" si="5"/>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352">
+        <f t="shared" si="5"/>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353">
+        <f t="shared" si="5"/>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354">
+        <f t="shared" si="5"/>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355">
+        <f t="shared" si="5"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356">
+        <f t="shared" si="5"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357">
+        <f t="shared" si="5"/>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358">
+        <f t="shared" si="5"/>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359">
+        <f t="shared" si="5"/>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360">
+        <f t="shared" si="5"/>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361">
+        <f t="shared" si="5"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362">
+        <f t="shared" si="5"/>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363">
+        <f t="shared" si="5"/>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364">
+        <f t="shared" si="5"/>
+        <v>363</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365">
+        <f t="shared" si="5"/>
+        <v>364</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366">
+        <f t="shared" si="5"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367">
+        <f t="shared" si="5"/>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368">
+        <f t="shared" si="5"/>
+        <v>367</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369">
+        <f t="shared" si="5"/>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370">
+        <f t="shared" si="5"/>
+        <v>369</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371">
+        <f t="shared" si="5"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372">
+        <f t="shared" si="5"/>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373">
+        <f t="shared" si="5"/>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374">
+        <f t="shared" si="5"/>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375">
+        <f t="shared" si="5"/>
+        <v>374</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376">
+        <f t="shared" si="5"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377">
+        <f t="shared" si="5"/>
+        <v>376</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378">
+        <f t="shared" si="5"/>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379">
+        <f t="shared" si="5"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380">
+        <f t="shared" si="5"/>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381">
+        <f t="shared" si="5"/>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382">
+        <f t="shared" si="5"/>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383">
+        <f t="shared" si="5"/>
+        <v>382</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384">
+        <f t="shared" si="5"/>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385">
+        <f t="shared" si="5"/>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386">
+        <f t="shared" si="5"/>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387">
+        <f t="shared" si="5"/>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388">
+        <f t="shared" ref="A388:A451" si="6">A387+1</f>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389">
+        <f t="shared" si="6"/>
+        <v>388</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390">
+        <f t="shared" si="6"/>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391">
+        <f t="shared" si="6"/>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392">
+        <f t="shared" si="6"/>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393">
+        <f t="shared" si="6"/>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394">
+        <f t="shared" si="6"/>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395">
+        <f t="shared" si="6"/>
+        <v>394</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396">
+        <f t="shared" si="6"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397">
+        <f t="shared" si="6"/>
+        <v>396</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398">
+        <f t="shared" si="6"/>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399">
+        <f t="shared" si="6"/>
+        <v>398</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400">
+        <f t="shared" si="6"/>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402">
+        <f t="shared" si="6"/>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403">
+        <f t="shared" si="6"/>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404">
+        <f t="shared" si="6"/>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405">
+        <f t="shared" si="6"/>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406">
+        <f t="shared" si="6"/>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407">
+        <f t="shared" si="6"/>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408">
+        <f t="shared" si="6"/>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409">
+        <f t="shared" si="6"/>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410">
+        <f t="shared" si="6"/>
+        <v>409</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411">
+        <f t="shared" si="6"/>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412">
+        <f t="shared" si="6"/>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413">
+        <f t="shared" si="6"/>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414">
+        <f t="shared" si="6"/>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415">
+        <f t="shared" si="6"/>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416">
+        <f t="shared" si="6"/>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417">
+        <f t="shared" si="6"/>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418">
+        <f t="shared" si="6"/>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419">
+        <f t="shared" si="6"/>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420">
+        <f t="shared" si="6"/>
+        <v>419</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421">
+        <f t="shared" si="6"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422">
+        <f t="shared" si="6"/>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423">
+        <f t="shared" si="6"/>
+        <v>422</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424">
+        <f t="shared" si="6"/>
+        <v>423</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425">
+        <f t="shared" si="6"/>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426">
+        <f t="shared" si="6"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427">
+        <f t="shared" si="6"/>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428">
+        <f t="shared" si="6"/>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429">
+        <f t="shared" si="6"/>
+        <v>428</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430">
+        <f t="shared" si="6"/>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431">
+        <f t="shared" si="6"/>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432">
+        <f t="shared" si="6"/>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433">
+        <f t="shared" si="6"/>
+        <v>432</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434">
+        <f t="shared" si="6"/>
+        <v>433</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435">
+        <f t="shared" si="6"/>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436">
+        <f t="shared" si="6"/>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437">
+        <f t="shared" si="6"/>
+        <v>436</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438">
+        <f t="shared" si="6"/>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439">
+        <f t="shared" si="6"/>
+        <v>438</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440">
+        <f t="shared" si="6"/>
+        <v>439</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441">
+        <f t="shared" si="6"/>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442">
+        <f t="shared" si="6"/>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443">
+        <f t="shared" si="6"/>
+        <v>442</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444">
+        <f t="shared" si="6"/>
+        <v>443</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445">
+        <f t="shared" si="6"/>
+        <v>444</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446">
+        <f t="shared" si="6"/>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447">
+        <f t="shared" si="6"/>
+        <v>446</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448">
+        <f t="shared" si="6"/>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449">
+        <f t="shared" si="6"/>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450">
+        <f t="shared" si="6"/>
+        <v>449</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451">
+        <f t="shared" si="6"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452">
+        <f t="shared" ref="A452:A515" si="7">A451+1</f>
+        <v>451</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453">
+        <f t="shared" si="7"/>
+        <v>452</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454">
+        <f t="shared" si="7"/>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455">
+        <f t="shared" si="7"/>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456">
+        <f t="shared" si="7"/>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457">
+        <f t="shared" si="7"/>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458">
+        <f t="shared" si="7"/>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459">
+        <f t="shared" si="7"/>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460">
+        <f t="shared" si="7"/>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461">
+        <f t="shared" si="7"/>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462">
+        <f t="shared" si="7"/>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463">
+        <f t="shared" si="7"/>
+        <v>462</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464">
+        <f t="shared" si="7"/>
+        <v>463</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465">
+        <f t="shared" si="7"/>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466">
+        <f t="shared" si="7"/>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467">
+        <f t="shared" si="7"/>
+        <v>466</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468">
+        <f t="shared" si="7"/>
+        <v>467</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469">
+        <f t="shared" si="7"/>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470">
+        <f t="shared" si="7"/>
+        <v>469</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471">
+        <f t="shared" si="7"/>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472">
+        <f t="shared" si="7"/>
+        <v>471</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473">
+        <f t="shared" si="7"/>
+        <v>472</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474">
+        <f t="shared" si="7"/>
+        <v>473</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475">
+        <f t="shared" si="7"/>
+        <v>474</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476">
+        <f t="shared" si="7"/>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477">
+        <f t="shared" si="7"/>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478">
+        <f t="shared" si="7"/>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479">
+        <f t="shared" si="7"/>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480">
+        <f t="shared" si="7"/>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481">
+        <f t="shared" si="7"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482">
+        <f t="shared" si="7"/>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483">
+        <f t="shared" si="7"/>
+        <v>482</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484">
+        <f t="shared" si="7"/>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485">
+        <f t="shared" si="7"/>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486">
+        <f t="shared" si="7"/>
+        <v>485</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487">
+        <f t="shared" si="7"/>
+        <v>486</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488">
+        <f t="shared" si="7"/>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489">
+        <f t="shared" si="7"/>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490">
+        <f t="shared" si="7"/>
+        <v>489</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491">
+        <f t="shared" si="7"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492">
+        <f t="shared" si="7"/>
+        <v>491</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493">
+        <f t="shared" si="7"/>
+        <v>492</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494">
+        <f t="shared" si="7"/>
+        <v>493</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495">
+        <f t="shared" si="7"/>
+        <v>494</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1">
+      <c r="A496">
+        <f t="shared" si="7"/>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1">
+      <c r="A497">
+        <f t="shared" si="7"/>
+        <v>496</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1">
+      <c r="A498">
+        <f t="shared" si="7"/>
+        <v>497</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1">
+      <c r="A499">
+        <f t="shared" si="7"/>
+        <v>498</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1">
+      <c r="A500">
+        <f t="shared" si="7"/>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1">
+      <c r="A501">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1">
+      <c r="A502">
+        <f t="shared" si="7"/>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1">
+      <c r="A503">
+        <f t="shared" si="7"/>
+        <v>502</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1">
+      <c r="A504">
+        <f t="shared" si="7"/>
+        <v>503</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1">
+      <c r="A505">
+        <f t="shared" si="7"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1">
+      <c r="A506">
+        <f t="shared" si="7"/>
+        <v>505</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1">
+      <c r="A507">
+        <f t="shared" si="7"/>
+        <v>506</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1">
+      <c r="A508">
+        <f t="shared" si="7"/>
+        <v>507</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1">
+      <c r="A509">
+        <f t="shared" si="7"/>
+        <v>508</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1">
+      <c r="A510">
+        <f t="shared" si="7"/>
+        <v>509</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1">
+      <c r="A511">
+        <f t="shared" si="7"/>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1">
+      <c r="A512">
+        <f t="shared" si="7"/>
+        <v>511</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1">
+      <c r="A513">
+        <f t="shared" si="7"/>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1">
+      <c r="A514">
+        <f t="shared" si="7"/>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1">
+      <c r="A515">
+        <f t="shared" si="7"/>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1">
+      <c r="A516">
+        <f t="shared" ref="A516:A579" si="8">A515+1</f>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1">
+      <c r="A517">
+        <f t="shared" si="8"/>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1">
+      <c r="A518">
+        <f t="shared" si="8"/>
+        <v>517</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1">
+      <c r="A519">
+        <f t="shared" si="8"/>
+        <v>518</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1">
+      <c r="A520">
+        <f t="shared" si="8"/>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1">
+      <c r="A521">
+        <f t="shared" si="8"/>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1">
+      <c r="A522">
+        <f t="shared" si="8"/>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1">
+      <c r="A523">
+        <f t="shared" si="8"/>
+        <v>522</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1">
+      <c r="A524">
+        <f t="shared" si="8"/>
+        <v>523</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1">
+      <c r="A525">
+        <f t="shared" si="8"/>
+        <v>524</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1">
+      <c r="A526">
+        <f t="shared" si="8"/>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1">
+      <c r="A527">
+        <f t="shared" si="8"/>
+        <v>526</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1">
+      <c r="A528">
+        <f t="shared" si="8"/>
+        <v>527</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1">
+      <c r="A529">
+        <f t="shared" si="8"/>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1">
+      <c r="A530">
+        <f t="shared" si="8"/>
+        <v>529</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1">
+      <c r="A531">
+        <f t="shared" si="8"/>
+        <v>530</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1">
+      <c r="A532">
+        <f t="shared" si="8"/>
+        <v>531</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1">
+      <c r="A533">
+        <f t="shared" si="8"/>
+        <v>532</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1">
+      <c r="A534">
+        <f t="shared" si="8"/>
+        <v>533</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1">
+      <c r="A535">
+        <f t="shared" si="8"/>
+        <v>534</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1">
+      <c r="A536">
+        <f t="shared" si="8"/>
+        <v>535</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1">
+      <c r="A537">
+        <f t="shared" si="8"/>
+        <v>536</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1">
+      <c r="A538">
+        <f t="shared" si="8"/>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1">
+      <c r="A539">
+        <f t="shared" si="8"/>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1">
+      <c r="A540">
+        <f t="shared" si="8"/>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1">
+      <c r="A541">
+        <f t="shared" si="8"/>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1">
+      <c r="A542">
+        <f t="shared" si="8"/>
+        <v>541</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1">
+      <c r="A543">
+        <f t="shared" si="8"/>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1">
+      <c r="A544">
+        <f t="shared" si="8"/>
+        <v>543</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1">
+      <c r="A545">
+        <f t="shared" si="8"/>
+        <v>544</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1">
+      <c r="A546">
+        <f t="shared" si="8"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1">
+      <c r="A547">
+        <f t="shared" si="8"/>
+        <v>546</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1">
+      <c r="A548">
+        <f t="shared" si="8"/>
+        <v>547</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1">
+      <c r="A549">
+        <f t="shared" si="8"/>
+        <v>548</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1">
+      <c r="A550">
+        <f t="shared" si="8"/>
+        <v>549</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1">
+      <c r="A551">
+        <f t="shared" si="8"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1">
+      <c r="A552">
+        <f t="shared" si="8"/>
+        <v>551</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1">
+      <c r="A553">
+        <f t="shared" si="8"/>
+        <v>552</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1">
+      <c r="A554">
+        <f t="shared" si="8"/>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1">
+      <c r="A555">
+        <f t="shared" si="8"/>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1">
+      <c r="A556">
+        <f t="shared" si="8"/>
+        <v>555</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1">
+      <c r="A557">
+        <f t="shared" si="8"/>
+        <v>556</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1">
+      <c r="A558">
+        <f t="shared" si="8"/>
+        <v>557</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1">
+      <c r="A559">
+        <f t="shared" si="8"/>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1">
+      <c r="A560">
+        <f t="shared" si="8"/>
+        <v>559</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1">
+      <c r="A561">
+        <f t="shared" si="8"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1">
+      <c r="A562">
+        <f t="shared" si="8"/>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1">
+      <c r="A563">
+        <f t="shared" si="8"/>
+        <v>562</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1">
+      <c r="A564">
+        <f t="shared" si="8"/>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1">
+      <c r="A565">
+        <f t="shared" si="8"/>
+        <v>564</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1">
+      <c r="A566">
+        <f t="shared" si="8"/>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1">
+      <c r="A567">
+        <f t="shared" si="8"/>
+        <v>566</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1">
+      <c r="A568">
+        <f t="shared" si="8"/>
+        <v>567</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1">
+      <c r="A569">
+        <f t="shared" si="8"/>
+        <v>568</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1">
+      <c r="A570">
+        <f t="shared" si="8"/>
+        <v>569</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1">
+      <c r="A571">
+        <f t="shared" si="8"/>
+        <v>570</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1">
+      <c r="A572">
+        <f t="shared" si="8"/>
+        <v>571</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1">
+      <c r="A573">
+        <f t="shared" si="8"/>
+        <v>572</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1">
+      <c r="A574">
+        <f t="shared" si="8"/>
+        <v>573</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1">
+      <c r="A575">
+        <f t="shared" si="8"/>
+        <v>574</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1">
+      <c r="A576">
+        <f t="shared" si="8"/>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1">
+      <c r="A577">
+        <f t="shared" si="8"/>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1">
+      <c r="A578">
+        <f t="shared" si="8"/>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1">
+      <c r="A579">
+        <f t="shared" si="8"/>
+        <v>578</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1">
+      <c r="A580">
+        <f t="shared" ref="A580:A643" si="9">A579+1</f>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1">
+      <c r="A581">
+        <f t="shared" si="9"/>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1">
+      <c r="A582">
+        <f t="shared" si="9"/>
+        <v>581</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1">
+      <c r="A583">
+        <f t="shared" si="9"/>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1">
+      <c r="A584">
+        <f t="shared" si="9"/>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1">
+      <c r="A585">
+        <f t="shared" si="9"/>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1">
+      <c r="A586">
+        <f t="shared" si="9"/>
+        <v>585</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1">
+      <c r="A587">
+        <f t="shared" si="9"/>
+        <v>586</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1">
+      <c r="A588">
+        <f t="shared" si="9"/>
+        <v>587</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1">
+      <c r="A589">
+        <f t="shared" si="9"/>
+        <v>588</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1">
+      <c r="A590">
+        <f t="shared" si="9"/>
+        <v>589</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1">
+      <c r="A591">
+        <f t="shared" si="9"/>
+        <v>590</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1">
+      <c r="A592">
+        <f t="shared" si="9"/>
+        <v>591</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1">
+      <c r="A593">
+        <f t="shared" si="9"/>
+        <v>592</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1">
+      <c r="A594">
+        <f t="shared" si="9"/>
+        <v>593</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1">
+      <c r="A595">
+        <f t="shared" si="9"/>
+        <v>594</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1">
+      <c r="A596">
+        <f t="shared" si="9"/>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1">
+      <c r="A597">
+        <f t="shared" si="9"/>
+        <v>596</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1">
+      <c r="A598">
+        <f t="shared" si="9"/>
+        <v>597</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1">
+      <c r="A599">
+        <f t="shared" si="9"/>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1">
+      <c r="A600">
+        <f t="shared" si="9"/>
+        <v>599</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1">
+      <c r="A601">
+        <f t="shared" si="9"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1">
+      <c r="A602">
+        <f t="shared" si="9"/>
+        <v>601</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1">
+      <c r="A603">
+        <f t="shared" si="9"/>
+        <v>602</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1">
+      <c r="A604">
+        <f t="shared" si="9"/>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1">
+      <c r="A605">
+        <f t="shared" si="9"/>
+        <v>604</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1">
+      <c r="A606">
+        <f t="shared" si="9"/>
+        <v>605</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1">
+      <c r="A607">
+        <f t="shared" si="9"/>
+        <v>606</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1">
+      <c r="A608">
+        <f t="shared" si="9"/>
+        <v>607</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1">
+      <c r="A609">
+        <f t="shared" si="9"/>
+        <v>608</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1">
+      <c r="A610">
+        <f t="shared" si="9"/>
+        <v>609</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1">
+      <c r="A611">
+        <f t="shared" si="9"/>
+        <v>610</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1">
+      <c r="A612">
+        <f t="shared" si="9"/>
+        <v>611</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1">
+      <c r="A613">
+        <f t="shared" si="9"/>
+        <v>612</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1">
+      <c r="A614">
+        <f t="shared" si="9"/>
+        <v>613</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1">
+      <c r="A615">
+        <f t="shared" si="9"/>
+        <v>614</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1">
+      <c r="A616">
+        <f t="shared" si="9"/>
+        <v>615</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1">
+      <c r="A617">
+        <f t="shared" si="9"/>
+        <v>616</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1">
+      <c r="A618">
+        <f t="shared" si="9"/>
+        <v>617</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1">
+      <c r="A619">
+        <f t="shared" si="9"/>
+        <v>618</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1">
+      <c r="A620">
+        <f t="shared" si="9"/>
+        <v>619</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1">
+      <c r="A621">
+        <f t="shared" si="9"/>
+        <v>620</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1">
+      <c r="A622">
+        <f t="shared" si="9"/>
+        <v>621</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1">
+      <c r="A623">
+        <f t="shared" si="9"/>
+        <v>622</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1">
+      <c r="A624">
+        <f t="shared" si="9"/>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1">
+      <c r="A625">
+        <f t="shared" si="9"/>
+        <v>624</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1">
+      <c r="A626">
+        <f t="shared" si="9"/>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1">
+      <c r="A627">
+        <f t="shared" si="9"/>
+        <v>626</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1">
+      <c r="A628">
+        <f t="shared" si="9"/>
+        <v>627</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1">
+      <c r="A629">
+        <f t="shared" si="9"/>
+        <v>628</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1">
+      <c r="A630">
+        <f t="shared" si="9"/>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1">
+      <c r="A631">
+        <f t="shared" si="9"/>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1">
+      <c r="A632">
+        <f t="shared" si="9"/>
+        <v>631</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1">
+      <c r="A633">
+        <f t="shared" si="9"/>
+        <v>632</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1">
+      <c r="A634">
+        <f t="shared" si="9"/>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1">
+      <c r="A635">
+        <f t="shared" si="9"/>
+        <v>634</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1">
+      <c r="A636">
+        <f t="shared" si="9"/>
+        <v>635</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1">
+      <c r="A637">
+        <f t="shared" si="9"/>
+        <v>636</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1">
+      <c r="A638">
+        <f t="shared" si="9"/>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1">
+      <c r="A639">
+        <f t="shared" si="9"/>
+        <v>638</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1">
+      <c r="A640">
+        <f t="shared" si="9"/>
+        <v>639</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1">
+      <c r="A641">
+        <f t="shared" si="9"/>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1">
+      <c r="A642">
+        <f t="shared" si="9"/>
+        <v>641</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1">
+      <c r="A643">
+        <f t="shared" si="9"/>
+        <v>642</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1">
+      <c r="A644">
+        <f t="shared" ref="A644:A707" si="10">A643+1</f>
+        <v>643</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1">
+      <c r="A645">
+        <f t="shared" si="10"/>
+        <v>644</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1">
+      <c r="A646">
+        <f t="shared" si="10"/>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1">
+      <c r="A647">
+        <f t="shared" si="10"/>
+        <v>646</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1">
+      <c r="A648">
+        <f t="shared" si="10"/>
+        <v>647</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1">
+      <c r="A649">
+        <f t="shared" si="10"/>
+        <v>648</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1">
+      <c r="A650">
+        <f t="shared" si="10"/>
+        <v>649</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1">
+      <c r="A651">
+        <f t="shared" si="10"/>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1">
+      <c r="A652">
+        <f t="shared" si="10"/>
+        <v>651</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1">
+      <c r="A653">
+        <f t="shared" si="10"/>
+        <v>652</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1">
+      <c r="A654">
+        <f t="shared" si="10"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1">
+      <c r="A655">
+        <f t="shared" si="10"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1">
+      <c r="A656">
+        <f t="shared" si="10"/>
+        <v>655</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1">
+      <c r="A657">
+        <f t="shared" si="10"/>
+        <v>656</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1">
+      <c r="A658">
+        <f t="shared" si="10"/>
+        <v>657</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1">
+      <c r="A659">
+        <f t="shared" si="10"/>
+        <v>658</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1">
+      <c r="A660">
+        <f t="shared" si="10"/>
+        <v>659</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1">
+      <c r="A661">
+        <f t="shared" si="10"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1">
+      <c r="A662">
+        <f t="shared" si="10"/>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1">
+      <c r="A663">
+        <f t="shared" si="10"/>
+        <v>662</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1">
+      <c r="A664">
+        <f t="shared" si="10"/>
+        <v>663</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1">
+      <c r="A665">
+        <f t="shared" si="10"/>
+        <v>664</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1">
+      <c r="A666">
+        <f t="shared" si="10"/>
+        <v>665</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1">
+      <c r="A667">
+        <f t="shared" si="10"/>
+        <v>666</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1">
+      <c r="A668">
+        <f t="shared" si="10"/>
+        <v>667</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1">
+      <c r="A669">
+        <f t="shared" si="10"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="670" spans="1:1">
+      <c r="A670">
+        <f t="shared" si="10"/>
+        <v>669</v>
+      </c>
+    </row>
+    <row r="671" spans="1:1">
+      <c r="A671">
+        <f t="shared" si="10"/>
+        <v>670</v>
+      </c>
+    </row>
+    <row r="672" spans="1:1">
+      <c r="A672">
+        <f t="shared" si="10"/>
+        <v>671</v>
+      </c>
+    </row>
+    <row r="673" spans="1:1">
+      <c r="A673">
+        <f t="shared" si="10"/>
+        <v>672</v>
+      </c>
+    </row>
+    <row r="674" spans="1:1">
+      <c r="A674">
+        <f t="shared" si="10"/>
+        <v>673</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1">
+      <c r="A675">
+        <f t="shared" si="10"/>
+        <v>674</v>
+      </c>
+    </row>
+    <row r="676" spans="1:1">
+      <c r="A676">
+        <f t="shared" si="10"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="677" spans="1:1">
+      <c r="A677">
+        <f t="shared" si="10"/>
+        <v>676</v>
+      </c>
+    </row>
+    <row r="678" spans="1:1">
+      <c r="A678">
+        <f t="shared" si="10"/>
+        <v>677</v>
+      </c>
+    </row>
+    <row r="679" spans="1:1">
+      <c r="A679">
+        <f t="shared" si="10"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="680" spans="1:1">
+      <c r="A680">
+        <f t="shared" si="10"/>
+        <v>679</v>
+      </c>
+    </row>
+    <row r="681" spans="1:1">
+      <c r="A681">
+        <f t="shared" si="10"/>
+        <v>680</v>
+      </c>
+    </row>
+    <row r="682" spans="1:1">
+      <c r="A682">
+        <f t="shared" si="10"/>
+        <v>681</v>
+      </c>
+    </row>
+    <row r="683" spans="1:1">
+      <c r="A683">
+        <f t="shared" si="10"/>
+        <v>682</v>
+      </c>
+    </row>
+    <row r="684" spans="1:1">
+      <c r="A684">
+        <f t="shared" si="10"/>
+        <v>683</v>
+      </c>
+    </row>
+    <row r="685" spans="1:1">
+      <c r="A685">
+        <f t="shared" si="10"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="686" spans="1:1">
+      <c r="A686">
+        <f t="shared" si="10"/>
+        <v>685</v>
+      </c>
+    </row>
+    <row r="687" spans="1:1">
+      <c r="A687">
+        <f t="shared" si="10"/>
+        <v>686</v>
+      </c>
+    </row>
+    <row r="688" spans="1:1">
+      <c r="A688">
+        <f t="shared" si="10"/>
+        <v>687</v>
+      </c>
+    </row>
+    <row r="689" spans="1:1">
+      <c r="A689">
+        <f t="shared" si="10"/>
+        <v>688</v>
+      </c>
+    </row>
+    <row r="690" spans="1:1">
+      <c r="A690">
+        <f t="shared" si="10"/>
+        <v>689</v>
+      </c>
+    </row>
+    <row r="691" spans="1:1">
+      <c r="A691">
+        <f t="shared" si="10"/>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="692" spans="1:1">
+      <c r="A692">
+        <f t="shared" si="10"/>
+        <v>691</v>
+      </c>
+    </row>
+    <row r="693" spans="1:1">
+      <c r="A693">
+        <f t="shared" si="10"/>
+        <v>692</v>
+      </c>
+    </row>
+    <row r="694" spans="1:1">
+      <c r="A694">
+        <f t="shared" si="10"/>
+        <v>693</v>
+      </c>
+    </row>
+    <row r="695" spans="1:1">
+      <c r="A695">
+        <f t="shared" si="10"/>
+        <v>694</v>
+      </c>
+    </row>
+    <row r="696" spans="1:1">
+      <c r="A696">
+        <f t="shared" si="10"/>
+        <v>695</v>
+      </c>
+    </row>
+    <row r="697" spans="1:1">
+      <c r="A697">
+        <f t="shared" si="10"/>
+        <v>696</v>
+      </c>
+    </row>
+    <row r="698" spans="1:1">
+      <c r="A698">
+        <f t="shared" si="10"/>
+        <v>697</v>
+      </c>
+    </row>
+    <row r="699" spans="1:1">
+      <c r="A699">
+        <f t="shared" si="10"/>
+        <v>698</v>
+      </c>
+    </row>
+    <row r="700" spans="1:1">
+      <c r="A700">
+        <f t="shared" si="10"/>
+        <v>699</v>
+      </c>
+    </row>
+    <row r="701" spans="1:1">
+      <c r="A701">
+        <f t="shared" si="10"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="702" spans="1:1">
+      <c r="A702">
+        <f t="shared" si="10"/>
+        <v>701</v>
+      </c>
+    </row>
+    <row r="703" spans="1:1">
+      <c r="A703">
+        <f t="shared" si="10"/>
+        <v>702</v>
+      </c>
+    </row>
+    <row r="704" spans="1:1">
+      <c r="A704">
+        <f t="shared" si="10"/>
+        <v>703</v>
+      </c>
+    </row>
+    <row r="705" spans="1:1">
+      <c r="A705">
+        <f t="shared" si="10"/>
+        <v>704</v>
+      </c>
+    </row>
+    <row r="706" spans="1:1">
+      <c r="A706">
+        <f t="shared" si="10"/>
+        <v>705</v>
+      </c>
+    </row>
+    <row r="707" spans="1:1">
+      <c r="A707">
+        <f t="shared" si="10"/>
+        <v>706</v>
+      </c>
+    </row>
+    <row r="708" spans="1:1">
+      <c r="A708">
+        <f t="shared" ref="A708:A771" si="11">A707+1</f>
+        <v>707</v>
+      </c>
+    </row>
+    <row r="709" spans="1:1">
+      <c r="A709">
+        <f t="shared" si="11"/>
+        <v>708</v>
+      </c>
+    </row>
+    <row r="710" spans="1:1">
+      <c r="A710">
+        <f t="shared" si="11"/>
+        <v>709</v>
+      </c>
+    </row>
+    <row r="711" spans="1:1">
+      <c r="A711">
+        <f t="shared" si="11"/>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="712" spans="1:1">
+      <c r="A712">
+        <f t="shared" si="11"/>
+        <v>711</v>
+      </c>
+    </row>
+    <row r="713" spans="1:1">
+      <c r="A713">
+        <f t="shared" si="11"/>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="714" spans="1:1">
+      <c r="A714">
+        <f t="shared" si="11"/>
+        <v>713</v>
+      </c>
+    </row>
+    <row r="715" spans="1:1">
+      <c r="A715">
+        <f t="shared" si="11"/>
+        <v>714</v>
+      </c>
+    </row>
+    <row r="716" spans="1:1">
+      <c r="A716">
+        <f t="shared" si="11"/>
+        <v>715</v>
+      </c>
+    </row>
+    <row r="717" spans="1:1">
+      <c r="A717">
+        <f t="shared" si="11"/>
+        <v>716</v>
+      </c>
+    </row>
+    <row r="718" spans="1:1">
+      <c r="A718">
+        <f t="shared" si="11"/>
+        <v>717</v>
+      </c>
+    </row>
+    <row r="719" spans="1:1">
+      <c r="A719">
+        <f t="shared" si="11"/>
+        <v>718</v>
+      </c>
+    </row>
+    <row r="720" spans="1:1">
+      <c r="A720">
+        <f t="shared" si="11"/>
+        <v>719</v>
+      </c>
+    </row>
+    <row r="721" spans="1:1">
+      <c r="A721">
+        <f t="shared" si="11"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="722" spans="1:1">
+      <c r="A722">
+        <f t="shared" si="11"/>
+        <v>721</v>
+      </c>
+    </row>
+    <row r="723" spans="1:1">
+      <c r="A723">
+        <f t="shared" si="11"/>
+        <v>722</v>
+      </c>
+    </row>
+    <row r="724" spans="1:1">
+      <c r="A724">
+        <f t="shared" si="11"/>
+        <v>723</v>
+      </c>
+    </row>
+    <row r="725" spans="1:1">
+      <c r="A725">
+        <f t="shared" si="11"/>
+        <v>724</v>
+      </c>
+    </row>
+    <row r="726" spans="1:1">
+      <c r="A726">
+        <f t="shared" si="11"/>
+        <v>725</v>
+      </c>
+    </row>
+    <row r="727" spans="1:1">
+      <c r="A727">
+        <f t="shared" si="11"/>
+        <v>726</v>
+      </c>
+    </row>
+    <row r="728" spans="1:1">
+      <c r="A728">
+        <f t="shared" si="11"/>
+        <v>727</v>
+      </c>
+    </row>
+    <row r="729" spans="1:1">
+      <c r="A729">
+        <f t="shared" si="11"/>
+        <v>728</v>
+      </c>
+    </row>
+    <row r="730" spans="1:1">
+      <c r="A730">
+        <f t="shared" si="11"/>
+        <v>729</v>
+      </c>
+    </row>
+    <row r="731" spans="1:1">
+      <c r="A731">
+        <f t="shared" si="11"/>
+        <v>730</v>
+      </c>
+    </row>
+    <row r="732" spans="1:1">
+      <c r="A732">
+        <f t="shared" si="11"/>
+        <v>731</v>
+      </c>
+    </row>
+    <row r="733" spans="1:1">
+      <c r="A733">
+        <f t="shared" si="11"/>
+        <v>732</v>
+      </c>
+    </row>
+    <row r="734" spans="1:1">
+      <c r="A734">
+        <f t="shared" si="11"/>
+        <v>733</v>
+      </c>
+    </row>
+    <row r="735" spans="1:1">
+      <c r="A735">
+        <f t="shared" si="11"/>
+        <v>734</v>
+      </c>
+    </row>
+    <row r="736" spans="1:1">
+      <c r="A736">
+        <f t="shared" si="11"/>
+        <v>735</v>
+      </c>
+    </row>
+    <row r="737" spans="1:1">
+      <c r="A737">
+        <f t="shared" si="11"/>
+        <v>736</v>
+      </c>
+    </row>
+    <row r="738" spans="1:1">
+      <c r="A738">
+        <f t="shared" si="11"/>
+        <v>737</v>
+      </c>
+    </row>
+    <row r="739" spans="1:1">
+      <c r="A739">
+        <f t="shared" si="11"/>
+        <v>738</v>
+      </c>
+    </row>
+    <row r="740" spans="1:1">
+      <c r="A740">
+        <f t="shared" si="11"/>
+        <v>739</v>
+      </c>
+    </row>
+    <row r="741" spans="1:1">
+      <c r="A741">
+        <f t="shared" si="11"/>
+        <v>740</v>
+      </c>
+    </row>
+    <row r="742" spans="1:1">
+      <c r="A742">
+        <f t="shared" si="11"/>
+        <v>741</v>
+      </c>
+    </row>
+    <row r="743" spans="1:1">
+      <c r="A743">
+        <f t="shared" si="11"/>
+        <v>742</v>
+      </c>
+    </row>
+    <row r="744" spans="1:1">
+      <c r="A744">
+        <f t="shared" si="11"/>
+        <v>743</v>
+      </c>
+    </row>
+    <row r="745" spans="1:1">
+      <c r="A745">
+        <f t="shared" si="11"/>
+        <v>744</v>
+      </c>
+    </row>
+    <row r="746" spans="1:1">
+      <c r="A746">
+        <f t="shared" si="11"/>
+        <v>745</v>
+      </c>
+    </row>
+    <row r="747" spans="1:1">
+      <c r="A747">
+        <f t="shared" si="11"/>
+        <v>746</v>
+      </c>
+    </row>
+    <row r="748" spans="1:1">
+      <c r="A748">
+        <f t="shared" si="11"/>
+        <v>747</v>
+      </c>
+    </row>
+    <row r="749" spans="1:1">
+      <c r="A749">
+        <f t="shared" si="11"/>
+        <v>748</v>
+      </c>
+    </row>
+    <row r="750" spans="1:1">
+      <c r="A750">
+        <f t="shared" si="11"/>
+        <v>749</v>
+      </c>
+    </row>
+    <row r="751" spans="1:1">
+      <c r="A751">
+        <f t="shared" si="11"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="752" spans="1:1">
+      <c r="A752">
+        <f t="shared" si="11"/>
+        <v>751</v>
+      </c>
+    </row>
+    <row r="753" spans="1:1">
+      <c r="A753">
+        <f t="shared" si="11"/>
+        <v>752</v>
+      </c>
+    </row>
+    <row r="754" spans="1:1">
+      <c r="A754">
+        <f t="shared" si="11"/>
+        <v>753</v>
+      </c>
+    </row>
+    <row r="755" spans="1:1">
+      <c r="A755">
+        <f t="shared" si="11"/>
+        <v>754</v>
+      </c>
+    </row>
+    <row r="756" spans="1:1">
+      <c r="A756">
+        <f t="shared" si="11"/>
+        <v>755</v>
+      </c>
+    </row>
+    <row r="757" spans="1:1">
+      <c r="A757">
+        <f t="shared" si="11"/>
+        <v>756</v>
+      </c>
+    </row>
+    <row r="758" spans="1:1">
+      <c r="A758">
+        <f t="shared" si="11"/>
+        <v>757</v>
+      </c>
+    </row>
+    <row r="759" spans="1:1">
+      <c r="A759">
+        <f t="shared" si="11"/>
+        <v>758</v>
+      </c>
+    </row>
+    <row r="760" spans="1:1">
+      <c r="A760">
+        <f t="shared" si="11"/>
+        <v>759</v>
+      </c>
+    </row>
+    <row r="761" spans="1:1">
+      <c r="A761">
+        <f t="shared" si="11"/>
+        <v>760</v>
+      </c>
+    </row>
+    <row r="762" spans="1:1">
+      <c r="A762">
+        <f t="shared" si="11"/>
+        <v>761</v>
+      </c>
+    </row>
+    <row r="763" spans="1:1">
+      <c r="A763">
+        <f t="shared" si="11"/>
+        <v>762</v>
+      </c>
+    </row>
+    <row r="764" spans="1:1">
+      <c r="A764">
+        <f t="shared" si="11"/>
+        <v>763</v>
+      </c>
+    </row>
+    <row r="765" spans="1:1">
+      <c r="A765">
+        <f t="shared" si="11"/>
+        <v>764</v>
+      </c>
+    </row>
+    <row r="766" spans="1:1">
+      <c r="A766">
+        <f t="shared" si="11"/>
+        <v>765</v>
+      </c>
+    </row>
+    <row r="767" spans="1:1">
+      <c r="A767">
+        <f t="shared" si="11"/>
+        <v>766</v>
+      </c>
+    </row>
+    <row r="768" spans="1:1">
+      <c r="A768">
+        <f t="shared" si="11"/>
+        <v>767</v>
+      </c>
+    </row>
+    <row r="769" spans="1:1">
+      <c r="A769">
+        <f t="shared" si="11"/>
+        <v>768</v>
+      </c>
+    </row>
+    <row r="770" spans="1:1">
+      <c r="A770">
+        <f t="shared" si="11"/>
+        <v>769</v>
+      </c>
+    </row>
+    <row r="771" spans="1:1">
+      <c r="A771">
+        <f t="shared" si="11"/>
+        <v>770</v>
+      </c>
+    </row>
+    <row r="772" spans="1:1">
+      <c r="A772">
+        <f t="shared" ref="A772:A835" si="12">A771+1</f>
+        <v>771</v>
+      </c>
+    </row>
+    <row r="773" spans="1:1">
+      <c r="A773">
+        <f t="shared" si="12"/>
+        <v>772</v>
+      </c>
+    </row>
+    <row r="774" spans="1:1">
+      <c r="A774">
+        <f t="shared" si="12"/>
+        <v>773</v>
+      </c>
+    </row>
+    <row r="775" spans="1:1">
+      <c r="A775">
+        <f t="shared" si="12"/>
+        <v>774</v>
+      </c>
+    </row>
+    <row r="776" spans="1:1">
+      <c r="A776">
+        <f t="shared" si="12"/>
+        <v>775</v>
+      </c>
+    </row>
+    <row r="777" spans="1:1">
+      <c r="A777">
+        <f t="shared" si="12"/>
+        <v>776</v>
+      </c>
+    </row>
+    <row r="778" spans="1:1">
+      <c r="A778">
+        <f t="shared" si="12"/>
+        <v>777</v>
+      </c>
+    </row>
+    <row r="779" spans="1:1">
+      <c r="A779">
+        <f t="shared" si="12"/>
+        <v>778</v>
+      </c>
+    </row>
+    <row r="780" spans="1:1">
+      <c r="A780">
+        <f t="shared" si="12"/>
+        <v>779</v>
+      </c>
+    </row>
+    <row r="781" spans="1:1">
+      <c r="A781">
+        <f t="shared" si="12"/>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="782" spans="1:1">
+      <c r="A782">
+        <f t="shared" si="12"/>
+        <v>781</v>
+      </c>
+    </row>
+    <row r="783" spans="1:1">
+      <c r="A783">
+        <f t="shared" si="12"/>
+        <v>782</v>
+      </c>
+    </row>
+    <row r="784" spans="1:1">
+      <c r="A784">
+        <f t="shared" si="12"/>
+        <v>783</v>
+      </c>
+    </row>
+    <row r="785" spans="1:1">
+      <c r="A785">
+        <f t="shared" si="12"/>
+        <v>784</v>
+      </c>
+    </row>
+    <row r="786" spans="1:1">
+      <c r="A786">
+        <f t="shared" si="12"/>
+        <v>785</v>
+      </c>
+    </row>
+    <row r="787" spans="1:1">
+      <c r="A787">
+        <f t="shared" si="12"/>
+        <v>786</v>
+      </c>
+    </row>
+    <row r="788" spans="1:1">
+      <c r="A788">
+        <f t="shared" si="12"/>
+        <v>787</v>
+      </c>
+    </row>
+    <row r="789" spans="1:1">
+      <c r="A789">
+        <f t="shared" si="12"/>
+        <v>788</v>
+      </c>
+    </row>
+    <row r="790" spans="1:1">
+      <c r="A790">
+        <f t="shared" si="12"/>
+        <v>789</v>
+      </c>
+    </row>
+    <row r="791" spans="1:1">
+      <c r="A791">
+        <f t="shared" si="12"/>
+        <v>790</v>
+      </c>
+    </row>
+    <row r="792" spans="1:1">
+      <c r="A792">
+        <f t="shared" si="12"/>
+        <v>791</v>
+      </c>
+    </row>
+    <row r="793" spans="1:1">
+      <c r="A793">
+        <f t="shared" si="12"/>
+        <v>792</v>
+      </c>
+    </row>
+    <row r="794" spans="1:1">
+      <c r="A794">
+        <f t="shared" si="12"/>
+        <v>793</v>
+      </c>
+    </row>
+    <row r="795" spans="1:1">
+      <c r="A795">
+        <f t="shared" si="12"/>
+        <v>794</v>
+      </c>
+    </row>
+    <row r="796" spans="1:1">
+      <c r="A796">
+        <f t="shared" si="12"/>
+        <v>795</v>
+      </c>
+    </row>
+    <row r="797" spans="1:1">
+      <c r="A797">
+        <f t="shared" si="12"/>
+        <v>796</v>
+      </c>
+    </row>
+    <row r="798" spans="1:1">
+      <c r="A798">
+        <f t="shared" si="12"/>
+        <v>797</v>
+      </c>
+    </row>
+    <row r="799" spans="1:1">
+      <c r="A799">
+        <f t="shared" si="12"/>
+        <v>798</v>
+      </c>
+    </row>
+    <row r="800" spans="1:1">
+      <c r="A800">
+        <f t="shared" si="12"/>
+        <v>799</v>
+      </c>
+    </row>
+    <row r="801" spans="1:1">
+      <c r="A801">
+        <f t="shared" si="12"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="802" spans="1:1">
+      <c r="A802">
+        <f t="shared" si="12"/>
+        <v>801</v>
+      </c>
+    </row>
+    <row r="803" spans="1:1">
+      <c r="A803">
+        <f t="shared" si="12"/>
+        <v>802</v>
+      </c>
+    </row>
+    <row r="804" spans="1:1">
+      <c r="A804">
+        <f t="shared" si="12"/>
+        <v>803</v>
+      </c>
+    </row>
+    <row r="805" spans="1:1">
+      <c r="A805">
+        <f t="shared" si="12"/>
+        <v>804</v>
+      </c>
+    </row>
+    <row r="806" spans="1:1">
+      <c r="A806">
+        <f t="shared" si="12"/>
+        <v>805</v>
+      </c>
+    </row>
+    <row r="807" spans="1:1">
+      <c r="A807">
+        <f t="shared" si="12"/>
+        <v>806</v>
+      </c>
+    </row>
+    <row r="808" spans="1:1">
+      <c r="A808">
+        <f t="shared" si="12"/>
+        <v>807</v>
+      </c>
+    </row>
+    <row r="809" spans="1:1">
+      <c r="A809">
+        <f t="shared" si="12"/>
+        <v>808</v>
+      </c>
+    </row>
+    <row r="810" spans="1:1">
+      <c r="A810">
+        <f t="shared" si="12"/>
+        <v>809</v>
+      </c>
+    </row>
+    <row r="811" spans="1:1">
+      <c r="A811">
+        <f t="shared" si="12"/>
+        <v>810</v>
+      </c>
+    </row>
+    <row r="812" spans="1:1">
+      <c r="A812">
+        <f t="shared" si="12"/>
+        <v>811</v>
+      </c>
+    </row>
+    <row r="813" spans="1:1">
+      <c r="A813">
+        <f t="shared" si="12"/>
+        <v>812</v>
+      </c>
+    </row>
+    <row r="814" spans="1:1">
+      <c r="A814">
+        <f t="shared" si="12"/>
+        <v>813</v>
+      </c>
+    </row>
+    <row r="815" spans="1:1">
+      <c r="A815">
+        <f t="shared" si="12"/>
+        <v>814</v>
+      </c>
+    </row>
+    <row r="816" spans="1:1">
+      <c r="A816">
+        <f t="shared" si="12"/>
+        <v>815</v>
+      </c>
+    </row>
+    <row r="817" spans="1:1">
+      <c r="A817">
+        <f t="shared" si="12"/>
+        <v>816</v>
+      </c>
+    </row>
+    <row r="818" spans="1:1">
+      <c r="A818">
+        <f t="shared" si="12"/>
+        <v>817</v>
+      </c>
+    </row>
+    <row r="819" spans="1:1">
+      <c r="A819">
+        <f t="shared" si="12"/>
+        <v>818</v>
+      </c>
+    </row>
+    <row r="820" spans="1:1">
+      <c r="A820">
+        <f t="shared" si="12"/>
+        <v>819</v>
+      </c>
+    </row>
+    <row r="821" spans="1:1">
+      <c r="A821">
+        <f t="shared" si="12"/>
+        <v>820</v>
+      </c>
+    </row>
+    <row r="822" spans="1:1">
+      <c r="A822">
+        <f t="shared" si="12"/>
+        <v>821</v>
+      </c>
+    </row>
+    <row r="823" spans="1:1">
+      <c r="A823">
+        <f t="shared" si="12"/>
+        <v>822</v>
+      </c>
+    </row>
+    <row r="824" spans="1:1">
+      <c r="A824">
+        <f t="shared" si="12"/>
+        <v>823</v>
+      </c>
+    </row>
+    <row r="825" spans="1:1">
+      <c r="A825">
+        <f t="shared" si="12"/>
+        <v>824</v>
+      </c>
+    </row>
+    <row r="826" spans="1:1">
+      <c r="A826">
+        <f t="shared" si="12"/>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="827" spans="1:1">
+      <c r="A827">
+        <f t="shared" si="12"/>
+        <v>826</v>
+      </c>
+    </row>
+    <row r="828" spans="1:1">
+      <c r="A828">
+        <f t="shared" si="12"/>
+        <v>827</v>
+      </c>
+    </row>
+    <row r="829" spans="1:1">
+      <c r="A829">
+        <f t="shared" si="12"/>
+        <v>828</v>
+      </c>
+    </row>
+    <row r="830" spans="1:1">
+      <c r="A830">
+        <f t="shared" si="12"/>
+        <v>829</v>
+      </c>
+    </row>
+    <row r="831" spans="1:1">
+      <c r="A831">
+        <f t="shared" si="12"/>
+        <v>830</v>
+      </c>
+    </row>
+    <row r="832" spans="1:1">
+      <c r="A832">
+        <f t="shared" si="12"/>
+        <v>831</v>
+      </c>
+    </row>
+    <row r="833" spans="1:1">
+      <c r="A833">
+        <f t="shared" si="12"/>
+        <v>832</v>
+      </c>
+    </row>
+    <row r="834" spans="1:1">
+      <c r="A834">
+        <f t="shared" si="12"/>
+        <v>833</v>
+      </c>
+    </row>
+    <row r="835" spans="1:1">
+      <c r="A835">
+        <f t="shared" si="12"/>
+        <v>834</v>
+      </c>
+    </row>
+    <row r="836" spans="1:1">
+      <c r="A836">
+        <f t="shared" ref="A836:A899" si="13">A835+1</f>
+        <v>835</v>
+      </c>
+    </row>
+    <row r="837" spans="1:1">
+      <c r="A837">
+        <f t="shared" si="13"/>
+        <v>836</v>
+      </c>
+    </row>
+    <row r="838" spans="1:1">
+      <c r="A838">
+        <f t="shared" si="13"/>
+        <v>837</v>
+      </c>
+    </row>
+    <row r="839" spans="1:1">
+      <c r="A839">
+        <f t="shared" si="13"/>
+        <v>838</v>
+      </c>
+    </row>
+    <row r="840" spans="1:1">
+      <c r="A840">
+        <f t="shared" si="13"/>
+        <v>839</v>
+      </c>
+    </row>
+    <row r="841" spans="1:1">
+      <c r="A841">
+        <f t="shared" si="13"/>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="842" spans="1:1">
+      <c r="A842">
+        <f t="shared" si="13"/>
+        <v>841</v>
+      </c>
+    </row>
+    <row r="843" spans="1:1">
+      <c r="A843">
+        <f t="shared" si="13"/>
+        <v>842</v>
+      </c>
+    </row>
+    <row r="844" spans="1:1">
+      <c r="A844">
+        <f t="shared" si="13"/>
+        <v>843</v>
+      </c>
+    </row>
+    <row r="845" spans="1:1">
+      <c r="A845">
+        <f t="shared" si="13"/>
+        <v>844</v>
+      </c>
+    </row>
+    <row r="846" spans="1:1">
+      <c r="A846">
+        <f t="shared" si="13"/>
+        <v>845</v>
+      </c>
+    </row>
+    <row r="847" spans="1:1">
+      <c r="A847">
+        <f t="shared" si="13"/>
+        <v>846</v>
+      </c>
+    </row>
+    <row r="848" spans="1:1">
+      <c r="A848">
+        <f t="shared" si="13"/>
+        <v>847</v>
+      </c>
+    </row>
+    <row r="849" spans="1:1">
+      <c r="A849">
+        <f t="shared" si="13"/>
+        <v>848</v>
+      </c>
+    </row>
+    <row r="850" spans="1:1">
+      <c r="A850">
+        <f t="shared" si="13"/>
+        <v>849</v>
+      </c>
+    </row>
+    <row r="851" spans="1:1">
+      <c r="A851">
+        <f t="shared" si="13"/>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="852" spans="1:1">
+      <c r="A852">
+        <f t="shared" si="13"/>
+        <v>851</v>
+      </c>
+    </row>
+    <row r="853" spans="1:1">
+      <c r="A853">
+        <f t="shared" si="13"/>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="854" spans="1:1">
+      <c r="A854">
+        <f t="shared" si="13"/>
+        <v>853</v>
+      </c>
+    </row>
+    <row r="855" spans="1:1">
+      <c r="A855">
+        <f t="shared" si="13"/>
+        <v>854</v>
+      </c>
+    </row>
+    <row r="856" spans="1:1">
+      <c r="A856">
+        <f t="shared" si="13"/>
+        <v>855</v>
+      </c>
+    </row>
+    <row r="857" spans="1:1">
+      <c r="A857">
+        <f t="shared" si="13"/>
+        <v>856</v>
+      </c>
+    </row>
+    <row r="858" spans="1:1">
+      <c r="A858">
+        <f t="shared" si="13"/>
+        <v>857</v>
+      </c>
+    </row>
+    <row r="859" spans="1:1">
+      <c r="A859">
+        <f t="shared" si="13"/>
+        <v>858</v>
+      </c>
+    </row>
+    <row r="860" spans="1:1">
+      <c r="A860">
+        <f t="shared" si="13"/>
+        <v>859</v>
+      </c>
+    </row>
+    <row r="861" spans="1:1">
+      <c r="A861">
+        <f t="shared" si="13"/>
+        <v>860</v>
+      </c>
+    </row>
+    <row r="862" spans="1:1">
+      <c r="A862">
+        <f t="shared" si="13"/>
+        <v>861</v>
+      </c>
+    </row>
+    <row r="863" spans="1:1">
+      <c r="A863">
+        <f t="shared" si="13"/>
+        <v>862</v>
+      </c>
+    </row>
+    <row r="864" spans="1:1">
+      <c r="A864">
+        <f t="shared" si="13"/>
+        <v>863</v>
+      </c>
+    </row>
+    <row r="865" spans="1:1">
+      <c r="A865">
+        <f t="shared" si="13"/>
+        <v>864</v>
+      </c>
+    </row>
+    <row r="866" spans="1:1">
+      <c r="A866">
+        <f t="shared" si="13"/>
+        <v>865</v>
+      </c>
+    </row>
+    <row r="867" spans="1:1">
+      <c r="A867">
+        <f t="shared" si="13"/>
+        <v>866</v>
+      </c>
+    </row>
+    <row r="868" spans="1:1">
+      <c r="A868">
+        <f t="shared" si="13"/>
+        <v>867</v>
+      </c>
+    </row>
+    <row r="869" spans="1:1">
+      <c r="A869">
+        <f t="shared" si="13"/>
+        <v>868</v>
+      </c>
+    </row>
+    <row r="870" spans="1:1">
+      <c r="A870">
+        <f t="shared" si="13"/>
+        <v>869</v>
+      </c>
+    </row>
+    <row r="871" spans="1:1">
+      <c r="A871">
+        <f t="shared" si="13"/>
+        <v>870</v>
+      </c>
+    </row>
+    <row r="872" spans="1:1">
+      <c r="A872">
+        <f t="shared" si="13"/>
+        <v>871</v>
+      </c>
+    </row>
+    <row r="873" spans="1:1">
+      <c r="A873">
+        <f t="shared" si="13"/>
+        <v>872</v>
+      </c>
+    </row>
+    <row r="874" spans="1:1">
+      <c r="A874">
+        <f t="shared" si="13"/>
+        <v>873</v>
+      </c>
+    </row>
+    <row r="875" spans="1:1">
+      <c r="A875">
+        <f t="shared" si="13"/>
+        <v>874</v>
+      </c>
+    </row>
+    <row r="876" spans="1:1">
+      <c r="A876">
+        <f t="shared" si="13"/>
+        <v>875</v>
+      </c>
+    </row>
+    <row r="877" spans="1:1">
+      <c r="A877">
+        <f t="shared" si="13"/>
+        <v>876</v>
+      </c>
+    </row>
+    <row r="878" spans="1:1">
+      <c r="A878">
+        <f t="shared" si="13"/>
+        <v>877</v>
+      </c>
+    </row>
+    <row r="879" spans="1:1">
+      <c r="A879">
+        <f t="shared" si="13"/>
+        <v>878</v>
+      </c>
+    </row>
+    <row r="880" spans="1:1">
+      <c r="A880">
+        <f t="shared" si="13"/>
+        <v>879</v>
+      </c>
+    </row>
+    <row r="881" spans="1:1">
+      <c r="A881">
+        <f t="shared" si="13"/>
+        <v>880</v>
+      </c>
+    </row>
+    <row r="882" spans="1:1">
+      <c r="A882">
+        <f t="shared" si="13"/>
+        <v>881</v>
+      </c>
+    </row>
+    <row r="883" spans="1:1">
+      <c r="A883">
+        <f t="shared" si="13"/>
+        <v>882</v>
+      </c>
+    </row>
+    <row r="884" spans="1:1">
+      <c r="A884">
+        <f t="shared" si="13"/>
+        <v>883</v>
+      </c>
+    </row>
+    <row r="885" spans="1:1">
+      <c r="A885">
+        <f t="shared" si="13"/>
+        <v>884</v>
+      </c>
+    </row>
+    <row r="886" spans="1:1">
+      <c r="A886">
+        <f t="shared" si="13"/>
+        <v>885</v>
+      </c>
+    </row>
+    <row r="887" spans="1:1">
+      <c r="A887">
+        <f t="shared" si="13"/>
+        <v>886</v>
+      </c>
+    </row>
+    <row r="888" spans="1:1">
+      <c r="A888">
+        <f t="shared" si="13"/>
+        <v>887</v>
+      </c>
+    </row>
+    <row r="889" spans="1:1">
+      <c r="A889">
+        <f t="shared" si="13"/>
+        <v>888</v>
+      </c>
+    </row>
+    <row r="890" spans="1:1">
+      <c r="A890">
+        <f t="shared" si="13"/>
+        <v>889</v>
+      </c>
+    </row>
+    <row r="891" spans="1:1">
+      <c r="A891">
+        <f t="shared" si="13"/>
+        <v>890</v>
+      </c>
+    </row>
+    <row r="892" spans="1:1">
+      <c r="A892">
+        <f t="shared" si="13"/>
+        <v>891</v>
+      </c>
+    </row>
+    <row r="893" spans="1:1">
+      <c r="A893">
+        <f t="shared" si="13"/>
+        <v>892</v>
+      </c>
+    </row>
+    <row r="894" spans="1:1">
+      <c r="A894">
+        <f t="shared" si="13"/>
+        <v>893</v>
+      </c>
+    </row>
+    <row r="895" spans="1:1">
+      <c r="A895">
+        <f t="shared" si="13"/>
+        <v>894</v>
+      </c>
+    </row>
+    <row r="896" spans="1:1">
+      <c r="A896">
+        <f t="shared" si="13"/>
+        <v>895</v>
+      </c>
+    </row>
+    <row r="897" spans="1:1">
+      <c r="A897">
+        <f t="shared" si="13"/>
+        <v>896</v>
+      </c>
+    </row>
+    <row r="898" spans="1:1">
+      <c r="A898">
+        <f t="shared" si="13"/>
+        <v>897</v>
+      </c>
+    </row>
+    <row r="899" spans="1:1">
+      <c r="A899">
+        <f t="shared" si="13"/>
+        <v>898</v>
+      </c>
+    </row>
+    <row r="900" spans="1:1">
+      <c r="A900">
+        <f t="shared" ref="A900:A957" si="14">A899+1</f>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="901" spans="1:1">
+      <c r="A901">
+        <f t="shared" si="14"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="902" spans="1:1">
+      <c r="A902">
+        <f t="shared" si="14"/>
+        <v>901</v>
+      </c>
+    </row>
+    <row r="903" spans="1:1">
+      <c r="A903">
+        <f t="shared" si="14"/>
+        <v>902</v>
+      </c>
+    </row>
+    <row r="904" spans="1:1">
+      <c r="A904">
+        <f t="shared" si="14"/>
+        <v>903</v>
+      </c>
+    </row>
+    <row r="905" spans="1:1">
+      <c r="A905">
+        <f t="shared" si="14"/>
+        <v>904</v>
+      </c>
+    </row>
+    <row r="906" spans="1:1">
+      <c r="A906">
+        <f t="shared" si="14"/>
+        <v>905</v>
+      </c>
+    </row>
+    <row r="907" spans="1:1">
+      <c r="A907">
+        <f t="shared" si="14"/>
+        <v>906</v>
+      </c>
+    </row>
+    <row r="908" spans="1:1">
+      <c r="A908">
+        <f t="shared" si="14"/>
+        <v>907</v>
+      </c>
+    </row>
+    <row r="909" spans="1:1">
+      <c r="A909">
+        <f t="shared" si="14"/>
+        <v>908</v>
+      </c>
+    </row>
+    <row r="910" spans="1:1">
+      <c r="A910">
+        <f t="shared" si="14"/>
+        <v>909</v>
+      </c>
+    </row>
+    <row r="911" spans="1:1">
+      <c r="A911">
+        <f t="shared" si="14"/>
+        <v>910</v>
+      </c>
+    </row>
+    <row r="912" spans="1:1">
+      <c r="A912">
+        <f t="shared" si="14"/>
+        <v>911</v>
+      </c>
+    </row>
+    <row r="913" spans="1:1">
+      <c r="A913">
+        <f t="shared" si="14"/>
+        <v>912</v>
+      </c>
+    </row>
+    <row r="914" spans="1:1">
+      <c r="A914">
+        <f t="shared" si="14"/>
+        <v>913</v>
+      </c>
+    </row>
+    <row r="915" spans="1:1">
+      <c r="A915">
+        <f t="shared" si="14"/>
+        <v>914</v>
+      </c>
+    </row>
+    <row r="916" spans="1:1">
+      <c r="A916">
+        <f t="shared" si="14"/>
+        <v>915</v>
+      </c>
+    </row>
+    <row r="917" spans="1:1">
+      <c r="A917">
+        <f t="shared" si="14"/>
+        <v>916</v>
+      </c>
+    </row>
+    <row r="918" spans="1:1">
+      <c r="A918">
+        <f t="shared" si="14"/>
+        <v>917</v>
+      </c>
+    </row>
+    <row r="919" spans="1:1">
+      <c r="A919">
+        <f t="shared" si="14"/>
+        <v>918</v>
+      </c>
+    </row>
+    <row r="920" spans="1:1">
+      <c r="A920">
+        <f t="shared" si="14"/>
+        <v>919</v>
+      </c>
+    </row>
+    <row r="921" spans="1:1">
+      <c r="A921">
+        <f t="shared" si="14"/>
+        <v>920</v>
+      </c>
+    </row>
+    <row r="922" spans="1:1">
+      <c r="A922">
+        <f t="shared" si="14"/>
+        <v>921</v>
+      </c>
+    </row>
+    <row r="923" spans="1:1">
+      <c r="A923">
+        <f t="shared" si="14"/>
+        <v>922</v>
+      </c>
+    </row>
+    <row r="924" spans="1:1">
+      <c r="A924">
+        <f t="shared" si="14"/>
+        <v>923</v>
+      </c>
+    </row>
+    <row r="925" spans="1:1">
+      <c r="A925">
+        <f t="shared" si="14"/>
+        <v>924</v>
+      </c>
+    </row>
+    <row r="926" spans="1:1">
+      <c r="A926">
+        <f t="shared" si="14"/>
+        <v>925</v>
+      </c>
+    </row>
+    <row r="927" spans="1:1">
+      <c r="A927">
+        <f t="shared" si="14"/>
+        <v>926</v>
+      </c>
+    </row>
+    <row r="928" spans="1:1">
+      <c r="A928">
+        <f t="shared" si="14"/>
+        <v>927</v>
+      </c>
+    </row>
+    <row r="929" spans="1:1">
+      <c r="A929">
+        <f t="shared" si="14"/>
+        <v>928</v>
+      </c>
+    </row>
+    <row r="930" spans="1:1">
+      <c r="A930">
+        <f t="shared" si="14"/>
+        <v>929</v>
+      </c>
+    </row>
+    <row r="931" spans="1:1">
+      <c r="A931">
+        <f t="shared" si="14"/>
+        <v>930</v>
+      </c>
+    </row>
+    <row r="932" spans="1:1">
+      <c r="A932">
+        <f t="shared" si="14"/>
+        <v>931</v>
+      </c>
+    </row>
+    <row r="933" spans="1:1">
+      <c r="A933">
+        <f t="shared" si="14"/>
+        <v>932</v>
+      </c>
+    </row>
+    <row r="934" spans="1:1">
+      <c r="A934">
+        <f t="shared" si="14"/>
+        <v>933</v>
+      </c>
+    </row>
+    <row r="935" spans="1:1">
+      <c r="A935">
+        <f t="shared" si="14"/>
+        <v>934</v>
+      </c>
+    </row>
+    <row r="936" spans="1:1">
+      <c r="A936">
+        <f t="shared" si="14"/>
+        <v>935</v>
+      </c>
+    </row>
+    <row r="937" spans="1:1">
+      <c r="A937">
+        <f t="shared" si="14"/>
+        <v>936</v>
+      </c>
+    </row>
+    <row r="938" spans="1:1">
+      <c r="A938">
+        <f t="shared" si="14"/>
+        <v>937</v>
+      </c>
+    </row>
+    <row r="939" spans="1:1">
+      <c r="A939">
+        <f t="shared" si="14"/>
+        <v>938</v>
+      </c>
+    </row>
+    <row r="940" spans="1:1">
+      <c r="A940">
+        <f t="shared" si="14"/>
+        <v>939</v>
+      </c>
+    </row>
+    <row r="941" spans="1:1">
+      <c r="A941">
+        <f t="shared" si="14"/>
+        <v>940</v>
+      </c>
+    </row>
+    <row r="942" spans="1:1">
+      <c r="A942">
+        <f t="shared" si="14"/>
+        <v>941</v>
+      </c>
+    </row>
+    <row r="943" spans="1:1">
+      <c r="A943">
+        <f t="shared" si="14"/>
+        <v>942</v>
+      </c>
+    </row>
+    <row r="944" spans="1:1">
+      <c r="A944">
+        <f t="shared" si="14"/>
+        <v>943</v>
+      </c>
+    </row>
+    <row r="945" spans="1:1">
+      <c r="A945">
+        <f t="shared" si="14"/>
+        <v>944</v>
+      </c>
+    </row>
+    <row r="946" spans="1:1">
+      <c r="A946">
+        <f t="shared" si="14"/>
+        <v>945</v>
+      </c>
+    </row>
+    <row r="947" spans="1:1">
+      <c r="A947">
+        <f t="shared" si="14"/>
+        <v>946</v>
+      </c>
+    </row>
+    <row r="948" spans="1:1">
+      <c r="A948">
+        <f t="shared" si="14"/>
+        <v>947</v>
+      </c>
+    </row>
+    <row r="949" spans="1:1">
+      <c r="A949">
+        <f t="shared" si="14"/>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="950" spans="1:1">
+      <c r="A950">
+        <f t="shared" si="14"/>
+        <v>949</v>
+      </c>
+    </row>
+    <row r="951" spans="1:1">
+      <c r="A951">
+        <f t="shared" si="14"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="952" spans="1:1">
+      <c r="A952">
+        <f t="shared" si="14"/>
+        <v>951</v>
+      </c>
+    </row>
+    <row r="953" spans="1:1">
+      <c r="A953">
+        <f t="shared" si="14"/>
+        <v>952</v>
+      </c>
+    </row>
+    <row r="954" spans="1:1">
+      <c r="A954">
+        <f t="shared" si="14"/>
+        <v>953</v>
+      </c>
+    </row>
+    <row r="955" spans="1:1">
+      <c r="A955">
+        <f t="shared" si="14"/>
+        <v>954</v>
+      </c>
+    </row>
+    <row r="956" spans="1:1">
+      <c r="A956">
+        <f t="shared" si="14"/>
+        <v>955</v>
+      </c>
+    </row>
+    <row r="957" spans="1:1">
+      <c r="A957">
+        <f t="shared" si="14"/>
+        <v>956</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="27">
   <si>
     <t>ID</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>No person enrolled at this number.</t>
+  </si>
+  <si>
+    <t>Choctaw</t>
   </si>
 </sst>
 </file>
@@ -482,6 +485,9 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
       <c r="C2">
         <v>108</v>
       </c>
@@ -497,6 +503,9 @@
         <f>A2+1</f>
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
       <c r="C3">
         <f>C2</f>
         <v>108</v>
@@ -515,6 +524,9 @@
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
       <c r="C4">
         <f t="shared" ref="C4:C67" si="1">C3</f>
         <v>108</v>
@@ -533,6 +545,9 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
       <c r="C5">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -577,6 +592,9 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
       <c r="C6">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -594,6 +612,9 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
       <c r="C7">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -612,6 +633,9 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -630,6 +654,9 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -648,6 +675,9 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
       <c r="C10">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -666,6 +696,9 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
       <c r="C11">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -684,6 +717,9 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
       <c r="C12">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -702,6 +738,9 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
       <c r="C13">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -720,6 +759,9 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
       <c r="C14">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -738,6 +780,9 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
       <c r="C15">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -756,6 +801,9 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
       <c r="C16">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -774,6 +822,9 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
       <c r="C17">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -792,6 +843,9 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
       <c r="C18">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -810,6 +864,9 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
       <c r="C19">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -828,6 +885,9 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
       <c r="C20">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -846,6 +906,9 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
       <c r="C21">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -864,6 +927,9 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
       <c r="C22">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -882,6 +948,9 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
       <c r="C23">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -900,6 +969,9 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
       <c r="C24">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -917,6 +989,9 @@
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
       </c>
       <c r="C25">
         <f t="shared" si="1"/>
@@ -936,6 +1011,9 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
       <c r="C26">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -952,6 +1030,9 @@
     <row r="27" spans="1:14">
       <c r="A27">
         <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>26</v>
       </c>
       <c r="C27">
@@ -972,6 +1053,9 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
       <c r="C28">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -990,6 +1074,9 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
       <c r="C29">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1008,6 +1095,9 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
       <c r="C30">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1026,6 +1116,9 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
       <c r="C31">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1044,6 +1137,9 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
       <c r="C32">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1062,6 +1158,9 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
       <c r="C33">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1080,6 +1179,9 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
       <c r="C34">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1098,6 +1200,9 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
       <c r="C35">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1116,6 +1221,9 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
       <c r="C36">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1134,6 +1242,9 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
       <c r="C37">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1152,6 +1263,9 @@
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
       <c r="C38">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1170,6 +1284,9 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
       <c r="C39">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1188,6 +1305,9 @@
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
       <c r="C40">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1206,6 +1326,9 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
       <c r="C41">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1224,6 +1347,9 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
       <c r="C42">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1242,6 +1368,9 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
       <c r="C43">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1260,6 +1389,9 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
       <c r="C44">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1278,6 +1410,9 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
       <c r="C45">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1296,6 +1431,9 @@
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
       <c r="C46">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1314,6 +1452,9 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
       <c r="C47">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1332,6 +1473,9 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
       <c r="C48">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1350,6 +1494,9 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
       <c r="C49">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1368,6 +1515,9 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
       <c r="C50">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1386,6 +1536,9 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
       <c r="C51">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1404,6 +1557,9 @@
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
       <c r="C52">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1422,6 +1578,9 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
       <c r="C53">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1440,6 +1599,9 @@
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
       <c r="C54">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1458,6 +1620,9 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
       <c r="C55">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1476,6 +1641,9 @@
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
       <c r="C56">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1494,6 +1662,9 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
       <c r="C57">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1512,6 +1683,9 @@
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
       <c r="C58">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1530,6 +1704,9 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
       <c r="C59">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1548,6 +1725,9 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
       <c r="C60">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1566,6 +1746,9 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
       <c r="C61">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1584,6 +1767,9 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
       <c r="C62">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1602,6 +1788,9 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
       <c r="C63">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1620,6 +1809,9 @@
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
       <c r="C64">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1638,6 +1830,9 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
       <c r="C65">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1656,6 +1851,9 @@
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
       <c r="C66">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1674,6 +1872,9 @@
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
       <c r="C67">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -1692,6 +1893,9 @@
         <f t="shared" ref="A68:A131" si="4">A67+1</f>
         <v>67</v>
       </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
       <c r="C68">
         <f t="shared" ref="C68:C123" si="5">C67</f>
         <v>108</v>
@@ -1710,6 +1914,9 @@
         <f t="shared" si="4"/>
         <v>68</v>
       </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
       <c r="C69">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1728,6 +1935,9 @@
         <f t="shared" si="4"/>
         <v>69</v>
       </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
       <c r="C70">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1746,6 +1956,9 @@
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
       <c r="C71">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1764,6 +1977,9 @@
         <f t="shared" si="4"/>
         <v>71</v>
       </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
       <c r="C72">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1782,6 +1998,9 @@
         <f t="shared" si="4"/>
         <v>72</v>
       </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
       <c r="C73">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1800,6 +2019,9 @@
         <f t="shared" si="4"/>
         <v>73</v>
       </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
       <c r="C74">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1818,6 +2040,9 @@
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
       <c r="C75">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1836,6 +2061,9 @@
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
       <c r="C76">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1854,6 +2082,9 @@
         <f t="shared" si="4"/>
         <v>76</v>
       </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
       <c r="C77">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1872,6 +2103,9 @@
         <f t="shared" si="4"/>
         <v>77</v>
       </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
       <c r="C78">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1890,6 +2124,9 @@
         <f t="shared" si="4"/>
         <v>78</v>
       </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
       <c r="C79">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1908,6 +2145,9 @@
         <f t="shared" si="4"/>
         <v>79</v>
       </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
       <c r="C80">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1926,6 +2166,9 @@
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
       <c r="C81">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1944,6 +2187,9 @@
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
       <c r="C82">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1962,6 +2208,9 @@
         <f t="shared" si="4"/>
         <v>82</v>
       </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
       <c r="C83">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1980,6 +2229,9 @@
         <f t="shared" si="4"/>
         <v>83</v>
       </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
       <c r="C84">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -1998,6 +2250,9 @@
         <f t="shared" si="4"/>
         <v>84</v>
       </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
       <c r="C85">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2016,6 +2271,9 @@
         <f t="shared" si="4"/>
         <v>85</v>
       </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
       <c r="C86">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2034,6 +2292,9 @@
         <f t="shared" si="4"/>
         <v>86</v>
       </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
       <c r="C87">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2052,6 +2313,9 @@
         <f t="shared" si="4"/>
         <v>87</v>
       </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
       <c r="C88">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2070,6 +2334,9 @@
         <f t="shared" si="4"/>
         <v>88</v>
       </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
       <c r="C89">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2088,6 +2355,9 @@
         <f t="shared" si="4"/>
         <v>89</v>
       </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
       <c r="C90">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2106,6 +2376,9 @@
         <f t="shared" si="4"/>
         <v>90</v>
       </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
       <c r="C91">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2124,6 +2397,9 @@
         <f t="shared" si="4"/>
         <v>91</v>
       </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
       <c r="C92">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2142,6 +2418,9 @@
         <f t="shared" si="4"/>
         <v>92</v>
       </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
       <c r="C93">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2160,6 +2439,9 @@
         <f t="shared" si="4"/>
         <v>93</v>
       </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
       <c r="C94">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2178,6 +2460,9 @@
         <f t="shared" si="4"/>
         <v>94</v>
       </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
       <c r="C95">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2196,6 +2481,9 @@
         <f t="shared" si="4"/>
         <v>95</v>
       </c>
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
       <c r="C96">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2214,6 +2502,9 @@
         <f t="shared" si="4"/>
         <v>96</v>
       </c>
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
       <c r="C97">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2232,6 +2523,9 @@
         <f t="shared" si="4"/>
         <v>97</v>
       </c>
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
       <c r="C98">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2250,6 +2544,9 @@
         <f t="shared" si="4"/>
         <v>98</v>
       </c>
+      <c r="B99" t="s">
+        <v>26</v>
+      </c>
       <c r="C99">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2268,6 +2565,9 @@
         <f t="shared" si="4"/>
         <v>99</v>
       </c>
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
       <c r="C100">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2286,6 +2586,9 @@
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
+      <c r="B101" t="s">
+        <v>26</v>
+      </c>
       <c r="C101">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2304,6 +2607,9 @@
         <f t="shared" si="4"/>
         <v>101</v>
       </c>
+      <c r="B102" t="s">
+        <v>26</v>
+      </c>
       <c r="C102">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2322,6 +2628,9 @@
         <f t="shared" si="4"/>
         <v>102</v>
       </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
       <c r="C103">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2340,6 +2649,9 @@
         <f t="shared" si="4"/>
         <v>103</v>
       </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
       <c r="C104">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2358,6 +2670,9 @@
         <f t="shared" si="4"/>
         <v>104</v>
       </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
       <c r="C105">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2376,6 +2691,9 @@
         <f t="shared" si="4"/>
         <v>105</v>
       </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
       <c r="C106">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2394,6 +2712,9 @@
         <f t="shared" si="4"/>
         <v>106</v>
       </c>
+      <c r="B107" t="s">
+        <v>26</v>
+      </c>
       <c r="C107">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2412,6 +2733,9 @@
         <f t="shared" si="4"/>
         <v>107</v>
       </c>
+      <c r="B108" t="s">
+        <v>26</v>
+      </c>
       <c r="C108">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2430,6 +2754,9 @@
         <f t="shared" si="4"/>
         <v>108</v>
       </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
       <c r="C109">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2448,6 +2775,9 @@
         <f t="shared" si="4"/>
         <v>109</v>
       </c>
+      <c r="B110" t="s">
+        <v>26</v>
+      </c>
       <c r="C110">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2466,6 +2796,9 @@
         <f t="shared" si="4"/>
         <v>110</v>
       </c>
+      <c r="B111" t="s">
+        <v>26</v>
+      </c>
       <c r="C111">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2484,6 +2817,9 @@
         <f t="shared" si="4"/>
         <v>111</v>
       </c>
+      <c r="B112" t="s">
+        <v>26</v>
+      </c>
       <c r="C112">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2502,6 +2838,9 @@
         <f t="shared" si="4"/>
         <v>112</v>
       </c>
+      <c r="B113" t="s">
+        <v>26</v>
+      </c>
       <c r="C113">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2520,6 +2859,9 @@
         <f t="shared" si="4"/>
         <v>113</v>
       </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
       <c r="C114">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2538,6 +2880,9 @@
         <f t="shared" si="4"/>
         <v>114</v>
       </c>
+      <c r="B115" t="s">
+        <v>26</v>
+      </c>
       <c r="C115">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2556,6 +2901,9 @@
         <f t="shared" si="4"/>
         <v>115</v>
       </c>
+      <c r="B116" t="s">
+        <v>26</v>
+      </c>
       <c r="C116">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2574,6 +2922,9 @@
         <f t="shared" si="4"/>
         <v>116</v>
       </c>
+      <c r="B117" t="s">
+        <v>26</v>
+      </c>
       <c r="C117">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2592,6 +2943,9 @@
         <f t="shared" si="4"/>
         <v>117</v>
       </c>
+      <c r="B118" t="s">
+        <v>26</v>
+      </c>
       <c r="C118">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2610,6 +2964,9 @@
         <f t="shared" si="4"/>
         <v>118</v>
       </c>
+      <c r="B119" t="s">
+        <v>26</v>
+      </c>
       <c r="C119">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2628,6 +2985,9 @@
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
+      <c r="B120" t="s">
+        <v>26</v>
+      </c>
       <c r="C120">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2646,6 +3006,9 @@
         <f t="shared" si="4"/>
         <v>120</v>
       </c>
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
       <c r="C121">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2664,6 +3027,9 @@
         <f t="shared" si="4"/>
         <v>121</v>
       </c>
+      <c r="B122" t="s">
+        <v>26</v>
+      </c>
       <c r="C122">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2682,6 +3048,9 @@
         <f t="shared" si="4"/>
         <v>122</v>
       </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
       <c r="C123">
         <f t="shared" si="5"/>
         <v>108</v>
@@ -2700,6 +3069,9 @@
         <f t="shared" si="4"/>
         <v>123</v>
       </c>
+      <c r="B124" t="s">
+        <v>26</v>
+      </c>
       <c r="C124">
         <v>109</v>
       </c>
@@ -2716,6 +3088,9 @@
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
       <c r="C125">
         <f>C124</f>
         <v>109</v>
@@ -2734,6 +3109,9 @@
         <f t="shared" si="4"/>
         <v>125</v>
       </c>
+      <c r="B126" t="s">
+        <v>26</v>
+      </c>
       <c r="C126">
         <f t="shared" ref="C126:C189" si="8">C125</f>
         <v>109</v>
@@ -2752,6 +3130,9 @@
         <f t="shared" si="4"/>
         <v>126</v>
       </c>
+      <c r="B127" t="s">
+        <v>26</v>
+      </c>
       <c r="C127">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2770,6 +3151,9 @@
         <f t="shared" si="4"/>
         <v>127</v>
       </c>
+      <c r="B128" t="s">
+        <v>26</v>
+      </c>
       <c r="C128">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2788,6 +3172,9 @@
         <f t="shared" si="4"/>
         <v>128</v>
       </c>
+      <c r="B129" t="s">
+        <v>26</v>
+      </c>
       <c r="C129">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2806,6 +3193,9 @@
         <f t="shared" si="4"/>
         <v>129</v>
       </c>
+      <c r="B130" t="s">
+        <v>26</v>
+      </c>
       <c r="C130">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2824,6 +3214,9 @@
         <f t="shared" si="4"/>
         <v>130</v>
       </c>
+      <c r="B131" t="s">
+        <v>26</v>
+      </c>
       <c r="C131">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2842,6 +3235,9 @@
         <f t="shared" ref="A132:A195" si="10">A131+1</f>
         <v>131</v>
       </c>
+      <c r="B132" t="s">
+        <v>26</v>
+      </c>
       <c r="C132">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2860,6 +3256,9 @@
         <f t="shared" si="10"/>
         <v>132</v>
       </c>
+      <c r="B133" t="s">
+        <v>26</v>
+      </c>
       <c r="C133">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2878,6 +3277,9 @@
         <f t="shared" si="10"/>
         <v>133</v>
       </c>
+      <c r="B134" t="s">
+        <v>26</v>
+      </c>
       <c r="C134">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2896,6 +3298,9 @@
         <f t="shared" si="10"/>
         <v>134</v>
       </c>
+      <c r="B135" t="s">
+        <v>26</v>
+      </c>
       <c r="C135">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2914,6 +3319,9 @@
         <f t="shared" si="10"/>
         <v>135</v>
       </c>
+      <c r="B136" t="s">
+        <v>26</v>
+      </c>
       <c r="C136">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2932,6 +3340,9 @@
         <f t="shared" si="10"/>
         <v>136</v>
       </c>
+      <c r="B137" t="s">
+        <v>26</v>
+      </c>
       <c r="C137">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2950,6 +3361,9 @@
         <f t="shared" si="10"/>
         <v>137</v>
       </c>
+      <c r="B138" t="s">
+        <v>26</v>
+      </c>
       <c r="C138">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2968,6 +3382,9 @@
         <f t="shared" si="10"/>
         <v>138</v>
       </c>
+      <c r="B139" t="s">
+        <v>26</v>
+      </c>
       <c r="C139">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -2986,6 +3403,9 @@
         <f t="shared" si="10"/>
         <v>139</v>
       </c>
+      <c r="B140" t="s">
+        <v>26</v>
+      </c>
       <c r="C140">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3004,6 +3424,9 @@
         <f t="shared" si="10"/>
         <v>140</v>
       </c>
+      <c r="B141" t="s">
+        <v>26</v>
+      </c>
       <c r="C141">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3022,6 +3445,9 @@
         <f t="shared" si="10"/>
         <v>141</v>
       </c>
+      <c r="B142" t="s">
+        <v>26</v>
+      </c>
       <c r="C142">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3040,6 +3466,9 @@
         <f t="shared" si="10"/>
         <v>142</v>
       </c>
+      <c r="B143" t="s">
+        <v>26</v>
+      </c>
       <c r="C143">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3058,6 +3487,9 @@
         <f t="shared" si="10"/>
         <v>143</v>
       </c>
+      <c r="B144" t="s">
+        <v>26</v>
+      </c>
       <c r="C144">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3076,6 +3508,9 @@
         <f t="shared" si="10"/>
         <v>144</v>
       </c>
+      <c r="B145" t="s">
+        <v>26</v>
+      </c>
       <c r="C145">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3094,6 +3529,9 @@
         <f t="shared" si="10"/>
         <v>145</v>
       </c>
+      <c r="B146" t="s">
+        <v>26</v>
+      </c>
       <c r="C146">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3112,6 +3550,9 @@
         <f t="shared" si="10"/>
         <v>146</v>
       </c>
+      <c r="B147" t="s">
+        <v>26</v>
+      </c>
       <c r="C147">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3130,6 +3571,9 @@
         <f t="shared" si="10"/>
         <v>147</v>
       </c>
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
       <c r="C148">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3148,6 +3592,9 @@
         <f t="shared" si="10"/>
         <v>148</v>
       </c>
+      <c r="B149" t="s">
+        <v>26</v>
+      </c>
       <c r="C149">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3166,6 +3613,9 @@
         <f t="shared" si="10"/>
         <v>149</v>
       </c>
+      <c r="B150" t="s">
+        <v>26</v>
+      </c>
       <c r="C150">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3184,6 +3634,9 @@
         <f t="shared" si="10"/>
         <v>150</v>
       </c>
+      <c r="B151" t="s">
+        <v>26</v>
+      </c>
       <c r="C151">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3202,6 +3655,9 @@
         <f t="shared" si="10"/>
         <v>151</v>
       </c>
+      <c r="B152" t="s">
+        <v>26</v>
+      </c>
       <c r="C152">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3220,6 +3676,9 @@
         <f t="shared" si="10"/>
         <v>152</v>
       </c>
+      <c r="B153" t="s">
+        <v>26</v>
+      </c>
       <c r="C153">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3238,6 +3697,9 @@
         <f t="shared" si="10"/>
         <v>153</v>
       </c>
+      <c r="B154" t="s">
+        <v>26</v>
+      </c>
       <c r="C154">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3256,6 +3718,9 @@
         <f t="shared" si="10"/>
         <v>154</v>
       </c>
+      <c r="B155" t="s">
+        <v>26</v>
+      </c>
       <c r="C155">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3274,6 +3739,9 @@
         <f t="shared" si="10"/>
         <v>155</v>
       </c>
+      <c r="B156" t="s">
+        <v>26</v>
+      </c>
       <c r="C156">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3292,6 +3760,9 @@
         <f t="shared" si="10"/>
         <v>156</v>
       </c>
+      <c r="B157" t="s">
+        <v>26</v>
+      </c>
       <c r="C157">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3310,6 +3781,9 @@
         <f t="shared" si="10"/>
         <v>157</v>
       </c>
+      <c r="B158" t="s">
+        <v>26</v>
+      </c>
       <c r="C158">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3328,6 +3802,9 @@
         <f t="shared" si="10"/>
         <v>158</v>
       </c>
+      <c r="B159" t="s">
+        <v>26</v>
+      </c>
       <c r="C159">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3346,6 +3823,9 @@
         <f t="shared" si="10"/>
         <v>159</v>
       </c>
+      <c r="B160" t="s">
+        <v>26</v>
+      </c>
       <c r="C160">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3364,6 +3844,9 @@
         <f t="shared" si="10"/>
         <v>160</v>
       </c>
+      <c r="B161" t="s">
+        <v>26</v>
+      </c>
       <c r="C161">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3382,6 +3865,9 @@
         <f t="shared" si="10"/>
         <v>161</v>
       </c>
+      <c r="B162" t="s">
+        <v>26</v>
+      </c>
       <c r="C162">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3400,6 +3886,9 @@
         <f t="shared" si="10"/>
         <v>162</v>
       </c>
+      <c r="B163" t="s">
+        <v>26</v>
+      </c>
       <c r="C163">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3418,6 +3907,9 @@
         <f t="shared" si="10"/>
         <v>163</v>
       </c>
+      <c r="B164" t="s">
+        <v>26</v>
+      </c>
       <c r="C164">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3436,6 +3928,9 @@
         <f t="shared" si="10"/>
         <v>164</v>
       </c>
+      <c r="B165" t="s">
+        <v>26</v>
+      </c>
       <c r="C165">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3454,6 +3949,9 @@
         <f t="shared" si="10"/>
         <v>165</v>
       </c>
+      <c r="B166" t="s">
+        <v>26</v>
+      </c>
       <c r="C166">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3472,6 +3970,9 @@
         <f t="shared" si="10"/>
         <v>166</v>
       </c>
+      <c r="B167" t="s">
+        <v>26</v>
+      </c>
       <c r="C167">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3490,6 +3991,9 @@
         <f t="shared" si="10"/>
         <v>167</v>
       </c>
+      <c r="B168" t="s">
+        <v>26</v>
+      </c>
       <c r="C168">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3508,6 +4012,9 @@
         <f t="shared" si="10"/>
         <v>168</v>
       </c>
+      <c r="B169" t="s">
+        <v>26</v>
+      </c>
       <c r="C169">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3526,6 +4033,9 @@
         <f t="shared" si="10"/>
         <v>169</v>
       </c>
+      <c r="B170" t="s">
+        <v>26</v>
+      </c>
       <c r="C170">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3544,6 +4054,9 @@
         <f t="shared" si="10"/>
         <v>170</v>
       </c>
+      <c r="B171" t="s">
+        <v>26</v>
+      </c>
       <c r="C171">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3562,6 +4075,9 @@
         <f t="shared" si="10"/>
         <v>171</v>
       </c>
+      <c r="B172" t="s">
+        <v>26</v>
+      </c>
       <c r="C172">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3580,6 +4096,9 @@
         <f t="shared" si="10"/>
         <v>172</v>
       </c>
+      <c r="B173" t="s">
+        <v>26</v>
+      </c>
       <c r="C173">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3598,6 +4117,9 @@
         <f t="shared" si="10"/>
         <v>173</v>
       </c>
+      <c r="B174" t="s">
+        <v>26</v>
+      </c>
       <c r="C174">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3616,6 +4138,9 @@
         <f t="shared" si="10"/>
         <v>174</v>
       </c>
+      <c r="B175" t="s">
+        <v>26</v>
+      </c>
       <c r="C175">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3634,6 +4159,9 @@
         <f t="shared" si="10"/>
         <v>175</v>
       </c>
+      <c r="B176" t="s">
+        <v>26</v>
+      </c>
       <c r="C176">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3652,6 +4180,9 @@
         <f t="shared" si="10"/>
         <v>176</v>
       </c>
+      <c r="B177" t="s">
+        <v>26</v>
+      </c>
       <c r="C177">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3670,6 +4201,9 @@
         <f t="shared" si="10"/>
         <v>177</v>
       </c>
+      <c r="B178" t="s">
+        <v>26</v>
+      </c>
       <c r="C178">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3688,6 +4222,9 @@
         <f t="shared" si="10"/>
         <v>178</v>
       </c>
+      <c r="B179" t="s">
+        <v>26</v>
+      </c>
       <c r="C179">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3706,6 +4243,9 @@
         <f t="shared" si="10"/>
         <v>179</v>
       </c>
+      <c r="B180" t="s">
+        <v>26</v>
+      </c>
       <c r="C180">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3724,6 +4264,9 @@
         <f t="shared" si="10"/>
         <v>180</v>
       </c>
+      <c r="B181" t="s">
+        <v>26</v>
+      </c>
       <c r="C181">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3742,6 +4285,9 @@
         <f t="shared" si="10"/>
         <v>181</v>
       </c>
+      <c r="B182" t="s">
+        <v>26</v>
+      </c>
       <c r="C182">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3760,6 +4306,9 @@
         <f t="shared" si="10"/>
         <v>182</v>
       </c>
+      <c r="B183" t="s">
+        <v>26</v>
+      </c>
       <c r="C183">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3778,6 +4327,9 @@
         <f t="shared" si="10"/>
         <v>183</v>
       </c>
+      <c r="B184" t="s">
+        <v>26</v>
+      </c>
       <c r="C184">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3796,6 +4348,9 @@
         <f t="shared" si="10"/>
         <v>184</v>
       </c>
+      <c r="B185" t="s">
+        <v>26</v>
+      </c>
       <c r="C185">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3814,6 +4369,9 @@
         <f t="shared" si="10"/>
         <v>185</v>
       </c>
+      <c r="B186" t="s">
+        <v>26</v>
+      </c>
       <c r="C186">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3832,6 +4390,9 @@
         <f t="shared" si="10"/>
         <v>186</v>
       </c>
+      <c r="B187" t="s">
+        <v>26</v>
+      </c>
       <c r="C187">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3850,6 +4411,9 @@
         <f t="shared" si="10"/>
         <v>187</v>
       </c>
+      <c r="B188" t="s">
+        <v>26</v>
+      </c>
       <c r="C188">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3868,6 +4432,9 @@
         <f t="shared" si="10"/>
         <v>188</v>
       </c>
+      <c r="B189" t="s">
+        <v>26</v>
+      </c>
       <c r="C189">
         <f t="shared" si="8"/>
         <v>109</v>
@@ -3886,6 +4453,9 @@
         <f t="shared" si="10"/>
         <v>189</v>
       </c>
+      <c r="B190" t="s">
+        <v>26</v>
+      </c>
       <c r="C190">
         <f t="shared" ref="C190:C253" si="12">C189</f>
         <v>109</v>
@@ -3904,6 +4474,9 @@
         <f t="shared" si="10"/>
         <v>190</v>
       </c>
+      <c r="B191" t="s">
+        <v>26</v>
+      </c>
       <c r="C191">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -3922,6 +4495,9 @@
         <f t="shared" si="10"/>
         <v>191</v>
       </c>
+      <c r="B192" t="s">
+        <v>26</v>
+      </c>
       <c r="C192">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -3940,6 +4516,9 @@
         <f t="shared" si="10"/>
         <v>192</v>
       </c>
+      <c r="B193" t="s">
+        <v>26</v>
+      </c>
       <c r="C193">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -3958,6 +4537,9 @@
         <f t="shared" si="10"/>
         <v>193</v>
       </c>
+      <c r="B194" t="s">
+        <v>26</v>
+      </c>
       <c r="C194">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -3976,6 +4558,9 @@
         <f t="shared" si="10"/>
         <v>194</v>
       </c>
+      <c r="B195" t="s">
+        <v>26</v>
+      </c>
       <c r="C195">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -3994,6 +4579,9 @@
         <f t="shared" ref="A196:A259" si="14">A195+1</f>
         <v>195</v>
       </c>
+      <c r="B196" t="s">
+        <v>26</v>
+      </c>
       <c r="C196">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4012,6 +4600,9 @@
         <f t="shared" si="14"/>
         <v>196</v>
       </c>
+      <c r="B197" t="s">
+        <v>26</v>
+      </c>
       <c r="C197">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4030,6 +4621,9 @@
         <f t="shared" si="14"/>
         <v>197</v>
       </c>
+      <c r="B198" t="s">
+        <v>26</v>
+      </c>
       <c r="C198">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4048,6 +4642,9 @@
         <f t="shared" si="14"/>
         <v>198</v>
       </c>
+      <c r="B199" t="s">
+        <v>26</v>
+      </c>
       <c r="C199">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4066,6 +4663,9 @@
         <f t="shared" si="14"/>
         <v>199</v>
       </c>
+      <c r="B200" t="s">
+        <v>26</v>
+      </c>
       <c r="C200">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4084,6 +4684,9 @@
         <f t="shared" si="14"/>
         <v>200</v>
       </c>
+      <c r="B201" t="s">
+        <v>26</v>
+      </c>
       <c r="C201">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4102,6 +4705,9 @@
         <f t="shared" si="14"/>
         <v>201</v>
       </c>
+      <c r="B202" t="s">
+        <v>26</v>
+      </c>
       <c r="C202">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4120,6 +4726,9 @@
         <f t="shared" si="14"/>
         <v>202</v>
       </c>
+      <c r="B203" t="s">
+        <v>26</v>
+      </c>
       <c r="C203">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4138,6 +4747,9 @@
         <f t="shared" si="14"/>
         <v>203</v>
       </c>
+      <c r="B204" t="s">
+        <v>26</v>
+      </c>
       <c r="C204">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4156,6 +4768,9 @@
         <f t="shared" si="14"/>
         <v>204</v>
       </c>
+      <c r="B205" t="s">
+        <v>26</v>
+      </c>
       <c r="C205">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4174,6 +4789,9 @@
         <f t="shared" si="14"/>
         <v>205</v>
       </c>
+      <c r="B206" t="s">
+        <v>26</v>
+      </c>
       <c r="C206">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4192,6 +4810,9 @@
         <f t="shared" si="14"/>
         <v>206</v>
       </c>
+      <c r="B207" t="s">
+        <v>26</v>
+      </c>
       <c r="C207">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4210,6 +4831,9 @@
         <f t="shared" si="14"/>
         <v>207</v>
       </c>
+      <c r="B208" t="s">
+        <v>26</v>
+      </c>
       <c r="C208">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4228,6 +4852,9 @@
         <f t="shared" si="14"/>
         <v>208</v>
       </c>
+      <c r="B209" t="s">
+        <v>26</v>
+      </c>
       <c r="C209">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4246,6 +4873,9 @@
         <f t="shared" si="14"/>
         <v>209</v>
       </c>
+      <c r="B210" t="s">
+        <v>26</v>
+      </c>
       <c r="C210">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4264,6 +4894,9 @@
         <f t="shared" si="14"/>
         <v>210</v>
       </c>
+      <c r="B211" t="s">
+        <v>26</v>
+      </c>
       <c r="C211">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4282,6 +4915,9 @@
         <f t="shared" si="14"/>
         <v>211</v>
       </c>
+      <c r="B212" t="s">
+        <v>26</v>
+      </c>
       <c r="C212">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4300,6 +4936,9 @@
         <f t="shared" si="14"/>
         <v>212</v>
       </c>
+      <c r="B213" t="s">
+        <v>26</v>
+      </c>
       <c r="C213">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4318,6 +4957,9 @@
         <f t="shared" si="14"/>
         <v>213</v>
       </c>
+      <c r="B214" t="s">
+        <v>26</v>
+      </c>
       <c r="C214">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4336,6 +4978,9 @@
         <f t="shared" si="14"/>
         <v>214</v>
       </c>
+      <c r="B215" t="s">
+        <v>26</v>
+      </c>
       <c r="C215">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4354,6 +4999,9 @@
         <f t="shared" si="14"/>
         <v>215</v>
       </c>
+      <c r="B216" t="s">
+        <v>26</v>
+      </c>
       <c r="C216">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4372,6 +5020,9 @@
         <f t="shared" si="14"/>
         <v>216</v>
       </c>
+      <c r="B217" t="s">
+        <v>26</v>
+      </c>
       <c r="C217">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4390,6 +5041,9 @@
         <f t="shared" si="14"/>
         <v>217</v>
       </c>
+      <c r="B218" t="s">
+        <v>26</v>
+      </c>
       <c r="C218">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4408,6 +5062,9 @@
         <f t="shared" si="14"/>
         <v>218</v>
       </c>
+      <c r="B219" t="s">
+        <v>26</v>
+      </c>
       <c r="C219">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4426,6 +5083,9 @@
         <f t="shared" si="14"/>
         <v>219</v>
       </c>
+      <c r="B220" t="s">
+        <v>26</v>
+      </c>
       <c r="C220">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4444,6 +5104,9 @@
         <f t="shared" si="14"/>
         <v>220</v>
       </c>
+      <c r="B221" t="s">
+        <v>26</v>
+      </c>
       <c r="C221">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4462,6 +5125,9 @@
         <f t="shared" si="14"/>
         <v>221</v>
       </c>
+      <c r="B222" t="s">
+        <v>26</v>
+      </c>
       <c r="C222">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4480,6 +5146,9 @@
         <f t="shared" si="14"/>
         <v>222</v>
       </c>
+      <c r="B223" t="s">
+        <v>26</v>
+      </c>
       <c r="C223">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4498,6 +5167,9 @@
         <f t="shared" si="14"/>
         <v>223</v>
       </c>
+      <c r="B224" t="s">
+        <v>26</v>
+      </c>
       <c r="C224">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4516,6 +5188,9 @@
         <f t="shared" si="14"/>
         <v>224</v>
       </c>
+      <c r="B225" t="s">
+        <v>26</v>
+      </c>
       <c r="C225">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4534,6 +5209,9 @@
         <f t="shared" si="14"/>
         <v>225</v>
       </c>
+      <c r="B226" t="s">
+        <v>26</v>
+      </c>
       <c r="C226">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4552,6 +5230,9 @@
         <f t="shared" si="14"/>
         <v>226</v>
       </c>
+      <c r="B227" t="s">
+        <v>26</v>
+      </c>
       <c r="C227">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4570,6 +5251,9 @@
         <f t="shared" si="14"/>
         <v>227</v>
       </c>
+      <c r="B228" t="s">
+        <v>26</v>
+      </c>
       <c r="C228">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4588,6 +5272,9 @@
         <f t="shared" si="14"/>
         <v>228</v>
       </c>
+      <c r="B229" t="s">
+        <v>26</v>
+      </c>
       <c r="C229">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4606,6 +5293,9 @@
         <f t="shared" si="14"/>
         <v>229</v>
       </c>
+      <c r="B230" t="s">
+        <v>26</v>
+      </c>
       <c r="C230">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4624,6 +5314,9 @@
         <f t="shared" si="14"/>
         <v>230</v>
       </c>
+      <c r="B231" t="s">
+        <v>26</v>
+      </c>
       <c r="C231">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4642,6 +5335,9 @@
         <f t="shared" si="14"/>
         <v>231</v>
       </c>
+      <c r="B232" t="s">
+        <v>26</v>
+      </c>
       <c r="C232">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4660,6 +5356,9 @@
         <f t="shared" si="14"/>
         <v>232</v>
       </c>
+      <c r="B233" t="s">
+        <v>26</v>
+      </c>
       <c r="C233">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4678,6 +5377,9 @@
         <f t="shared" si="14"/>
         <v>233</v>
       </c>
+      <c r="B234" t="s">
+        <v>26</v>
+      </c>
       <c r="C234">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4696,6 +5398,9 @@
         <f t="shared" si="14"/>
         <v>234</v>
       </c>
+      <c r="B235" t="s">
+        <v>26</v>
+      </c>
       <c r="C235">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4714,6 +5419,9 @@
         <f t="shared" si="14"/>
         <v>235</v>
       </c>
+      <c r="B236" t="s">
+        <v>26</v>
+      </c>
       <c r="C236">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4732,6 +5440,9 @@
         <f t="shared" si="14"/>
         <v>236</v>
       </c>
+      <c r="B237" t="s">
+        <v>26</v>
+      </c>
       <c r="C237">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4750,6 +5461,9 @@
         <f t="shared" si="14"/>
         <v>237</v>
       </c>
+      <c r="B238" t="s">
+        <v>26</v>
+      </c>
       <c r="C238">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4768,6 +5482,9 @@
         <f t="shared" si="14"/>
         <v>238</v>
       </c>
+      <c r="B239" t="s">
+        <v>26</v>
+      </c>
       <c r="C239">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4786,6 +5503,9 @@
         <f t="shared" si="14"/>
         <v>239</v>
       </c>
+      <c r="B240" t="s">
+        <v>26</v>
+      </c>
       <c r="C240">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4804,6 +5524,9 @@
         <f t="shared" si="14"/>
         <v>240</v>
       </c>
+      <c r="B241" t="s">
+        <v>26</v>
+      </c>
       <c r="C241">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4822,6 +5545,9 @@
         <f t="shared" si="14"/>
         <v>241</v>
       </c>
+      <c r="B242" t="s">
+        <v>26</v>
+      </c>
       <c r="C242">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4840,6 +5566,9 @@
         <f t="shared" si="14"/>
         <v>242</v>
       </c>
+      <c r="B243" t="s">
+        <v>26</v>
+      </c>
       <c r="C243">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4858,6 +5587,9 @@
         <f t="shared" si="14"/>
         <v>243</v>
       </c>
+      <c r="B244" t="s">
+        <v>26</v>
+      </c>
       <c r="C244">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4876,6 +5608,9 @@
         <f t="shared" si="14"/>
         <v>244</v>
       </c>
+      <c r="B245" t="s">
+        <v>26</v>
+      </c>
       <c r="C245">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4894,6 +5629,9 @@
         <f t="shared" si="14"/>
         <v>245</v>
       </c>
+      <c r="B246" t="s">
+        <v>26</v>
+      </c>
       <c r="C246">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4912,6 +5650,9 @@
         <f t="shared" si="14"/>
         <v>246</v>
       </c>
+      <c r="B247" t="s">
+        <v>26</v>
+      </c>
       <c r="C247">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4930,6 +5671,9 @@
         <f t="shared" si="14"/>
         <v>247</v>
       </c>
+      <c r="B248" t="s">
+        <v>26</v>
+      </c>
       <c r="C248">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4948,6 +5692,9 @@
         <f t="shared" si="14"/>
         <v>248</v>
       </c>
+      <c r="B249" t="s">
+        <v>26</v>
+      </c>
       <c r="C249">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4966,6 +5713,9 @@
         <f t="shared" si="14"/>
         <v>249</v>
       </c>
+      <c r="B250" t="s">
+        <v>26</v>
+      </c>
       <c r="C250">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -4984,6 +5734,9 @@
         <f t="shared" si="14"/>
         <v>250</v>
       </c>
+      <c r="B251" t="s">
+        <v>26</v>
+      </c>
       <c r="C251">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -5002,6 +5755,9 @@
         <f t="shared" si="14"/>
         <v>251</v>
       </c>
+      <c r="B252" t="s">
+        <v>26</v>
+      </c>
       <c r="C252">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -5020,6 +5776,9 @@
         <f t="shared" si="14"/>
         <v>252</v>
       </c>
+      <c r="B253" t="s">
+        <v>26</v>
+      </c>
       <c r="C253">
         <f t="shared" si="12"/>
         <v>109</v>
@@ -5038,6 +5797,9 @@
         <f t="shared" si="14"/>
         <v>253</v>
       </c>
+      <c r="B254" t="s">
+        <v>26</v>
+      </c>
       <c r="C254">
         <f t="shared" ref="C254:C285" si="16">C253</f>
         <v>109</v>
@@ -5082,6 +5844,9 @@
         <f t="shared" si="14"/>
         <v>254</v>
       </c>
+      <c r="B255" t="s">
+        <v>26</v>
+      </c>
       <c r="C255">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5099,6 +5864,9 @@
         <f t="shared" si="14"/>
         <v>255</v>
       </c>
+      <c r="B256" t="s">
+        <v>26</v>
+      </c>
       <c r="C256">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5117,6 +5885,9 @@
         <f t="shared" si="14"/>
         <v>256</v>
       </c>
+      <c r="B257" t="s">
+        <v>26</v>
+      </c>
       <c r="C257">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5135,6 +5906,9 @@
         <f t="shared" si="14"/>
         <v>257</v>
       </c>
+      <c r="B258" t="s">
+        <v>26</v>
+      </c>
       <c r="C258">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5153,6 +5927,9 @@
         <f t="shared" si="14"/>
         <v>258</v>
       </c>
+      <c r="B259" t="s">
+        <v>26</v>
+      </c>
       <c r="C259">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5171,6 +5948,9 @@
         <f t="shared" ref="A260:A323" si="18">A259+1</f>
         <v>259</v>
       </c>
+      <c r="B260" t="s">
+        <v>26</v>
+      </c>
       <c r="C260">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5189,6 +5969,9 @@
         <f t="shared" si="18"/>
         <v>260</v>
       </c>
+      <c r="B261" t="s">
+        <v>26</v>
+      </c>
       <c r="C261">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5207,6 +5990,9 @@
         <f t="shared" si="18"/>
         <v>261</v>
       </c>
+      <c r="B262" t="s">
+        <v>26</v>
+      </c>
       <c r="C262">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5225,6 +6011,9 @@
         <f t="shared" si="18"/>
         <v>262</v>
       </c>
+      <c r="B263" t="s">
+        <v>26</v>
+      </c>
       <c r="C263">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5243,6 +6032,9 @@
         <f t="shared" si="18"/>
         <v>263</v>
       </c>
+      <c r="B264" t="s">
+        <v>26</v>
+      </c>
       <c r="C264">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5261,6 +6053,9 @@
         <f t="shared" si="18"/>
         <v>264</v>
       </c>
+      <c r="B265" t="s">
+        <v>26</v>
+      </c>
       <c r="C265">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5279,6 +6074,9 @@
         <f t="shared" si="18"/>
         <v>265</v>
       </c>
+      <c r="B266" t="s">
+        <v>26</v>
+      </c>
       <c r="C266">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5323,6 +6121,9 @@
         <f t="shared" si="18"/>
         <v>266</v>
       </c>
+      <c r="B267" t="s">
+        <v>26</v>
+      </c>
       <c r="C267">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5367,6 +6168,9 @@
         <f t="shared" si="18"/>
         <v>267</v>
       </c>
+      <c r="B268" t="s">
+        <v>26</v>
+      </c>
       <c r="C268">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5411,6 +6215,9 @@
         <f t="shared" si="18"/>
         <v>268</v>
       </c>
+      <c r="B269" t="s">
+        <v>26</v>
+      </c>
       <c r="C269">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5455,6 +6262,9 @@
         <f t="shared" si="18"/>
         <v>269</v>
       </c>
+      <c r="B270" t="s">
+        <v>26</v>
+      </c>
       <c r="C270">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5499,6 +6309,9 @@
         <f t="shared" si="18"/>
         <v>270</v>
       </c>
+      <c r="B271" t="s">
+        <v>26</v>
+      </c>
       <c r="C271">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5516,6 +6329,9 @@
         <f t="shared" si="18"/>
         <v>271</v>
       </c>
+      <c r="B272" t="s">
+        <v>26</v>
+      </c>
       <c r="C272">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5534,6 +6350,9 @@
         <f t="shared" si="18"/>
         <v>272</v>
       </c>
+      <c r="B273" t="s">
+        <v>26</v>
+      </c>
       <c r="C273">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5552,6 +6371,9 @@
         <f t="shared" si="18"/>
         <v>273</v>
       </c>
+      <c r="B274" t="s">
+        <v>26</v>
+      </c>
       <c r="C274">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5570,6 +6392,9 @@
         <f t="shared" si="18"/>
         <v>274</v>
       </c>
+      <c r="B275" t="s">
+        <v>26</v>
+      </c>
       <c r="C275">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5588,6 +6413,9 @@
         <f t="shared" si="18"/>
         <v>275</v>
       </c>
+      <c r="B276" t="s">
+        <v>26</v>
+      </c>
       <c r="C276">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5606,6 +6434,9 @@
         <f t="shared" si="18"/>
         <v>276</v>
       </c>
+      <c r="B277" t="s">
+        <v>26</v>
+      </c>
       <c r="C277">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5624,6 +6455,9 @@
         <f t="shared" si="18"/>
         <v>277</v>
       </c>
+      <c r="B278" t="s">
+        <v>26</v>
+      </c>
       <c r="C278">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5642,6 +6476,9 @@
         <f t="shared" si="18"/>
         <v>278</v>
       </c>
+      <c r="B279" t="s">
+        <v>26</v>
+      </c>
       <c r="C279">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5660,6 +6497,9 @@
         <f t="shared" si="18"/>
         <v>279</v>
       </c>
+      <c r="B280" t="s">
+        <v>26</v>
+      </c>
       <c r="C280">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5678,6 +6518,9 @@
         <f t="shared" si="18"/>
         <v>280</v>
       </c>
+      <c r="B281" t="s">
+        <v>26</v>
+      </c>
       <c r="C281">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5696,6 +6539,9 @@
         <f t="shared" si="18"/>
         <v>281</v>
       </c>
+      <c r="B282" t="s">
+        <v>26</v>
+      </c>
       <c r="C282">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5714,6 +6560,9 @@
         <f t="shared" si="18"/>
         <v>282</v>
       </c>
+      <c r="B283" t="s">
+        <v>26</v>
+      </c>
       <c r="C283">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5732,6 +6581,9 @@
         <f t="shared" si="18"/>
         <v>283</v>
       </c>
+      <c r="B284" t="s">
+        <v>26</v>
+      </c>
       <c r="C284">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5750,6 +6602,9 @@
         <f t="shared" si="18"/>
         <v>284</v>
       </c>
+      <c r="B285" t="s">
+        <v>26</v>
+      </c>
       <c r="C285">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -5768,6 +6623,9 @@
         <f t="shared" si="18"/>
         <v>285</v>
       </c>
+      <c r="B286" t="s">
+        <v>26</v>
+      </c>
       <c r="C286">
         <v>110</v>
       </c>
@@ -5784,6 +6642,9 @@
         <f t="shared" si="18"/>
         <v>286</v>
       </c>
+      <c r="B287" t="s">
+        <v>26</v>
+      </c>
       <c r="C287">
         <f>C286</f>
         <v>110</v>
@@ -5802,6 +6663,9 @@
         <f t="shared" si="18"/>
         <v>287</v>
       </c>
+      <c r="B288" t="s">
+        <v>26</v>
+      </c>
       <c r="C288">
         <f t="shared" ref="C288:C351" si="20">C287</f>
         <v>110</v>
@@ -5820,6 +6684,9 @@
         <f t="shared" si="18"/>
         <v>288</v>
       </c>
+      <c r="B289" t="s">
+        <v>26</v>
+      </c>
       <c r="C289">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -5838,6 +6705,9 @@
         <f t="shared" si="18"/>
         <v>289</v>
       </c>
+      <c r="B290" t="s">
+        <v>26</v>
+      </c>
       <c r="C290">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -5856,6 +6726,9 @@
         <f t="shared" si="18"/>
         <v>290</v>
       </c>
+      <c r="B291" t="s">
+        <v>26</v>
+      </c>
       <c r="C291">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -5874,6 +6747,9 @@
         <f t="shared" si="18"/>
         <v>291</v>
       </c>
+      <c r="B292" t="s">
+        <v>26</v>
+      </c>
       <c r="C292">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -5892,6 +6768,9 @@
         <f t="shared" si="18"/>
         <v>292</v>
       </c>
+      <c r="B293" t="s">
+        <v>26</v>
+      </c>
       <c r="C293">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -5910,6 +6789,9 @@
         <f t="shared" si="18"/>
         <v>293</v>
       </c>
+      <c r="B294" t="s">
+        <v>26</v>
+      </c>
       <c r="C294">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -5928,6 +6810,9 @@
         <f t="shared" si="18"/>
         <v>294</v>
       </c>
+      <c r="B295" t="s">
+        <v>26</v>
+      </c>
       <c r="C295">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -5972,6 +6857,9 @@
         <f t="shared" si="18"/>
         <v>295</v>
       </c>
+      <c r="B296" t="s">
+        <v>26</v>
+      </c>
       <c r="C296">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6016,6 +6904,9 @@
         <f t="shared" si="18"/>
         <v>296</v>
       </c>
+      <c r="B297" t="s">
+        <v>26</v>
+      </c>
       <c r="C297">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6033,6 +6924,9 @@
         <f t="shared" si="18"/>
         <v>297</v>
       </c>
+      <c r="B298" t="s">
+        <v>26</v>
+      </c>
       <c r="C298">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6051,6 +6945,9 @@
         <f t="shared" si="18"/>
         <v>298</v>
       </c>
+      <c r="B299" t="s">
+        <v>26</v>
+      </c>
       <c r="C299">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6069,6 +6966,9 @@
         <f t="shared" si="18"/>
         <v>299</v>
       </c>
+      <c r="B300" t="s">
+        <v>26</v>
+      </c>
       <c r="C300">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6087,6 +6987,9 @@
         <f t="shared" si="18"/>
         <v>300</v>
       </c>
+      <c r="B301" t="s">
+        <v>26</v>
+      </c>
       <c r="C301">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6105,6 +7008,9 @@
         <f t="shared" si="18"/>
         <v>301</v>
       </c>
+      <c r="B302" t="s">
+        <v>26</v>
+      </c>
       <c r="C302">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6123,6 +7029,9 @@
         <f t="shared" si="18"/>
         <v>302</v>
       </c>
+      <c r="B303" t="s">
+        <v>26</v>
+      </c>
       <c r="C303">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6141,6 +7050,9 @@
         <f t="shared" si="18"/>
         <v>303</v>
       </c>
+      <c r="B304" t="s">
+        <v>26</v>
+      </c>
       <c r="C304">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6159,6 +7071,9 @@
         <f t="shared" si="18"/>
         <v>304</v>
       </c>
+      <c r="B305" t="s">
+        <v>26</v>
+      </c>
       <c r="C305">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6177,6 +7092,9 @@
         <f t="shared" si="18"/>
         <v>305</v>
       </c>
+      <c r="B306" t="s">
+        <v>26</v>
+      </c>
       <c r="C306">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6195,6 +7113,9 @@
         <f t="shared" si="18"/>
         <v>306</v>
       </c>
+      <c r="B307" t="s">
+        <v>26</v>
+      </c>
       <c r="C307">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6213,6 +7134,9 @@
         <f t="shared" si="18"/>
         <v>307</v>
       </c>
+      <c r="B308" t="s">
+        <v>26</v>
+      </c>
       <c r="C308">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6231,6 +7155,9 @@
         <f t="shared" si="18"/>
         <v>308</v>
       </c>
+      <c r="B309" t="s">
+        <v>26</v>
+      </c>
       <c r="C309">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6249,6 +7176,9 @@
         <f t="shared" si="18"/>
         <v>309</v>
       </c>
+      <c r="B310" t="s">
+        <v>26</v>
+      </c>
       <c r="C310">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6267,6 +7197,9 @@
         <f t="shared" si="18"/>
         <v>310</v>
       </c>
+      <c r="B311" t="s">
+        <v>26</v>
+      </c>
       <c r="C311">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6285,6 +7218,9 @@
         <f t="shared" si="18"/>
         <v>311</v>
       </c>
+      <c r="B312" t="s">
+        <v>26</v>
+      </c>
       <c r="C312">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6303,6 +7239,9 @@
         <f t="shared" si="18"/>
         <v>312</v>
       </c>
+      <c r="B313" t="s">
+        <v>26</v>
+      </c>
       <c r="C313">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6321,6 +7260,9 @@
         <f t="shared" si="18"/>
         <v>313</v>
       </c>
+      <c r="B314" t="s">
+        <v>26</v>
+      </c>
       <c r="C314">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6339,6 +7281,9 @@
         <f t="shared" si="18"/>
         <v>314</v>
       </c>
+      <c r="B315" t="s">
+        <v>26</v>
+      </c>
       <c r="C315">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6357,6 +7302,9 @@
         <f t="shared" si="18"/>
         <v>315</v>
       </c>
+      <c r="B316" t="s">
+        <v>26</v>
+      </c>
       <c r="C316">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6375,6 +7323,9 @@
         <f t="shared" si="18"/>
         <v>316</v>
       </c>
+      <c r="B317" t="s">
+        <v>26</v>
+      </c>
       <c r="C317">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6393,6 +7344,9 @@
         <f t="shared" si="18"/>
         <v>317</v>
       </c>
+      <c r="B318" t="s">
+        <v>26</v>
+      </c>
       <c r="C318">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6411,6 +7365,9 @@
         <f t="shared" si="18"/>
         <v>318</v>
       </c>
+      <c r="B319" t="s">
+        <v>26</v>
+      </c>
       <c r="C319">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6429,6 +7386,9 @@
         <f t="shared" si="18"/>
         <v>319</v>
       </c>
+      <c r="B320" t="s">
+        <v>26</v>
+      </c>
       <c r="C320">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6447,6 +7407,9 @@
         <f t="shared" si="18"/>
         <v>320</v>
       </c>
+      <c r="B321" t="s">
+        <v>26</v>
+      </c>
       <c r="C321">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6465,6 +7428,9 @@
         <f t="shared" si="18"/>
         <v>321</v>
       </c>
+      <c r="B322" t="s">
+        <v>26</v>
+      </c>
       <c r="C322">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6483,6 +7449,9 @@
         <f t="shared" si="18"/>
         <v>322</v>
       </c>
+      <c r="B323" t="s">
+        <v>26</v>
+      </c>
       <c r="C323">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6501,6 +7470,9 @@
         <f t="shared" ref="A324:A387" si="22">A323+1</f>
         <v>323</v>
       </c>
+      <c r="B324" t="s">
+        <v>26</v>
+      </c>
       <c r="C324">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6519,6 +7491,9 @@
         <f t="shared" si="22"/>
         <v>324</v>
       </c>
+      <c r="B325" t="s">
+        <v>26</v>
+      </c>
       <c r="C325">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6537,6 +7512,9 @@
         <f t="shared" si="22"/>
         <v>325</v>
       </c>
+      <c r="B326" t="s">
+        <v>26</v>
+      </c>
       <c r="C326">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6555,6 +7533,9 @@
         <f t="shared" si="22"/>
         <v>326</v>
       </c>
+      <c r="B327" t="s">
+        <v>26</v>
+      </c>
       <c r="C327">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6573,6 +7554,9 @@
         <f t="shared" si="22"/>
         <v>327</v>
       </c>
+      <c r="B328" t="s">
+        <v>26</v>
+      </c>
       <c r="C328">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6591,6 +7575,9 @@
         <f t="shared" si="22"/>
         <v>328</v>
       </c>
+      <c r="B329" t="s">
+        <v>26</v>
+      </c>
       <c r="C329">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6609,6 +7596,9 @@
         <f t="shared" si="22"/>
         <v>329</v>
       </c>
+      <c r="B330" t="s">
+        <v>26</v>
+      </c>
       <c r="C330">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6627,6 +7617,9 @@
         <f t="shared" si="22"/>
         <v>330</v>
       </c>
+      <c r="B331" t="s">
+        <v>26</v>
+      </c>
       <c r="C331">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6645,6 +7638,9 @@
         <f t="shared" si="22"/>
         <v>331</v>
       </c>
+      <c r="B332" t="s">
+        <v>26</v>
+      </c>
       <c r="C332">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6663,6 +7659,9 @@
         <f t="shared" si="22"/>
         <v>332</v>
       </c>
+      <c r="B333" t="s">
+        <v>26</v>
+      </c>
       <c r="C333">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6681,6 +7680,9 @@
         <f t="shared" si="22"/>
         <v>333</v>
       </c>
+      <c r="B334" t="s">
+        <v>26</v>
+      </c>
       <c r="C334">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6699,6 +7701,9 @@
         <f t="shared" si="22"/>
         <v>334</v>
       </c>
+      <c r="B335" t="s">
+        <v>26</v>
+      </c>
       <c r="C335">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6717,6 +7722,9 @@
         <f t="shared" si="22"/>
         <v>335</v>
       </c>
+      <c r="B336" t="s">
+        <v>26</v>
+      </c>
       <c r="C336">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6735,6 +7743,9 @@
         <f t="shared" si="22"/>
         <v>336</v>
       </c>
+      <c r="B337" t="s">
+        <v>26</v>
+      </c>
       <c r="C337">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6753,6 +7764,9 @@
         <f t="shared" si="22"/>
         <v>337</v>
       </c>
+      <c r="B338" t="s">
+        <v>26</v>
+      </c>
       <c r="C338">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6771,6 +7785,9 @@
         <f t="shared" si="22"/>
         <v>338</v>
       </c>
+      <c r="B339" t="s">
+        <v>26</v>
+      </c>
       <c r="C339">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6789,6 +7806,9 @@
         <f t="shared" si="22"/>
         <v>339</v>
       </c>
+      <c r="B340" t="s">
+        <v>26</v>
+      </c>
       <c r="C340">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6807,6 +7827,9 @@
         <f t="shared" si="22"/>
         <v>340</v>
       </c>
+      <c r="B341" t="s">
+        <v>26</v>
+      </c>
       <c r="C341">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6825,6 +7848,9 @@
         <f t="shared" si="22"/>
         <v>341</v>
       </c>
+      <c r="B342" t="s">
+        <v>26</v>
+      </c>
       <c r="C342">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6843,6 +7869,9 @@
         <f t="shared" si="22"/>
         <v>342</v>
       </c>
+      <c r="B343" t="s">
+        <v>26</v>
+      </c>
       <c r="C343">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6861,6 +7890,9 @@
         <f t="shared" si="22"/>
         <v>343</v>
       </c>
+      <c r="B344" t="s">
+        <v>26</v>
+      </c>
       <c r="C344">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6879,6 +7911,9 @@
         <f t="shared" si="22"/>
         <v>344</v>
       </c>
+      <c r="B345" t="s">
+        <v>26</v>
+      </c>
       <c r="C345">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6897,6 +7932,9 @@
         <f t="shared" si="22"/>
         <v>345</v>
       </c>
+      <c r="B346" t="s">
+        <v>26</v>
+      </c>
       <c r="C346">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6915,6 +7953,9 @@
         <f t="shared" si="22"/>
         <v>346</v>
       </c>
+      <c r="B347" t="s">
+        <v>26</v>
+      </c>
       <c r="C347">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6933,6 +7974,9 @@
         <f t="shared" si="22"/>
         <v>347</v>
       </c>
+      <c r="B348" t="s">
+        <v>26</v>
+      </c>
       <c r="C348">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6951,6 +7995,9 @@
         <f t="shared" si="22"/>
         <v>348</v>
       </c>
+      <c r="B349" t="s">
+        <v>26</v>
+      </c>
       <c r="C349">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6969,6 +8016,9 @@
         <f t="shared" si="22"/>
         <v>349</v>
       </c>
+      <c r="B350" t="s">
+        <v>26</v>
+      </c>
       <c r="C350">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -6987,6 +8037,9 @@
         <f t="shared" si="22"/>
         <v>350</v>
       </c>
+      <c r="B351" t="s">
+        <v>26</v>
+      </c>
       <c r="C351">
         <f t="shared" si="20"/>
         <v>110</v>
@@ -7005,6 +8058,9 @@
         <f t="shared" si="22"/>
         <v>351</v>
       </c>
+      <c r="B352" t="s">
+        <v>26</v>
+      </c>
       <c r="C352">
         <f t="shared" ref="C352:C415" si="24">C351</f>
         <v>110</v>
@@ -7023,6 +8079,9 @@
         <f t="shared" si="22"/>
         <v>352</v>
       </c>
+      <c r="B353" t="s">
+        <v>26</v>
+      </c>
       <c r="C353">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7041,6 +8100,9 @@
         <f t="shared" si="22"/>
         <v>353</v>
       </c>
+      <c r="B354" t="s">
+        <v>26</v>
+      </c>
       <c r="C354">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7059,6 +8121,9 @@
         <f t="shared" si="22"/>
         <v>354</v>
       </c>
+      <c r="B355" t="s">
+        <v>26</v>
+      </c>
       <c r="C355">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7077,6 +8142,9 @@
         <f t="shared" si="22"/>
         <v>355</v>
       </c>
+      <c r="B356" t="s">
+        <v>26</v>
+      </c>
       <c r="C356">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7095,6 +8163,9 @@
         <f t="shared" si="22"/>
         <v>356</v>
       </c>
+      <c r="B357" t="s">
+        <v>26</v>
+      </c>
       <c r="C357">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7113,6 +8184,9 @@
         <f t="shared" si="22"/>
         <v>357</v>
       </c>
+      <c r="B358" t="s">
+        <v>26</v>
+      </c>
       <c r="C358">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7131,6 +8205,9 @@
         <f t="shared" si="22"/>
         <v>358</v>
       </c>
+      <c r="B359" t="s">
+        <v>26</v>
+      </c>
       <c r="C359">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7149,6 +8226,9 @@
         <f t="shared" si="22"/>
         <v>359</v>
       </c>
+      <c r="B360" t="s">
+        <v>26</v>
+      </c>
       <c r="C360">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7167,6 +8247,9 @@
         <f t="shared" si="22"/>
         <v>360</v>
       </c>
+      <c r="B361" t="s">
+        <v>26</v>
+      </c>
       <c r="C361">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7185,6 +8268,9 @@
         <f t="shared" si="22"/>
         <v>361</v>
       </c>
+      <c r="B362" t="s">
+        <v>26</v>
+      </c>
       <c r="C362">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7203,6 +8289,9 @@
         <f t="shared" si="22"/>
         <v>362</v>
       </c>
+      <c r="B363" t="s">
+        <v>26</v>
+      </c>
       <c r="C363">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7221,6 +8310,9 @@
         <f t="shared" si="22"/>
         <v>363</v>
       </c>
+      <c r="B364" t="s">
+        <v>26</v>
+      </c>
       <c r="C364">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7239,6 +8331,9 @@
         <f t="shared" si="22"/>
         <v>364</v>
       </c>
+      <c r="B365" t="s">
+        <v>26</v>
+      </c>
       <c r="C365">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7257,6 +8352,9 @@
         <f t="shared" si="22"/>
         <v>365</v>
       </c>
+      <c r="B366" t="s">
+        <v>26</v>
+      </c>
       <c r="C366">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7275,6 +8373,9 @@
         <f t="shared" si="22"/>
         <v>366</v>
       </c>
+      <c r="B367" t="s">
+        <v>26</v>
+      </c>
       <c r="C367">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7293,6 +8394,9 @@
         <f t="shared" si="22"/>
         <v>367</v>
       </c>
+      <c r="B368" t="s">
+        <v>26</v>
+      </c>
       <c r="C368">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7337,6 +8441,9 @@
         <f t="shared" si="22"/>
         <v>368</v>
       </c>
+      <c r="B369" t="s">
+        <v>26</v>
+      </c>
       <c r="C369">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7354,6 +8461,9 @@
         <f t="shared" si="22"/>
         <v>369</v>
       </c>
+      <c r="B370" t="s">
+        <v>26</v>
+      </c>
       <c r="C370">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7372,6 +8482,9 @@
         <f t="shared" si="22"/>
         <v>370</v>
       </c>
+      <c r="B371" t="s">
+        <v>26</v>
+      </c>
       <c r="C371">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7390,6 +8503,9 @@
         <f t="shared" si="22"/>
         <v>371</v>
       </c>
+      <c r="B372" t="s">
+        <v>26</v>
+      </c>
       <c r="C372">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7408,6 +8524,9 @@
         <f t="shared" si="22"/>
         <v>372</v>
       </c>
+      <c r="B373" t="s">
+        <v>26</v>
+      </c>
       <c r="C373">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7426,6 +8545,9 @@
         <f t="shared" si="22"/>
         <v>373</v>
       </c>
+      <c r="B374" t="s">
+        <v>26</v>
+      </c>
       <c r="C374">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7444,6 +8566,9 @@
         <f t="shared" si="22"/>
         <v>374</v>
       </c>
+      <c r="B375" t="s">
+        <v>26</v>
+      </c>
       <c r="C375">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7462,6 +8587,9 @@
         <f t="shared" si="22"/>
         <v>375</v>
       </c>
+      <c r="B376" t="s">
+        <v>26</v>
+      </c>
       <c r="C376">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7480,6 +8608,9 @@
         <f t="shared" si="22"/>
         <v>376</v>
       </c>
+      <c r="B377" t="s">
+        <v>26</v>
+      </c>
       <c r="C377">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7498,6 +8629,9 @@
         <f t="shared" si="22"/>
         <v>377</v>
       </c>
+      <c r="B378" t="s">
+        <v>26</v>
+      </c>
       <c r="C378">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7516,6 +8650,9 @@
         <f t="shared" si="22"/>
         <v>378</v>
       </c>
+      <c r="B379" t="s">
+        <v>26</v>
+      </c>
       <c r="C379">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7534,6 +8671,9 @@
         <f t="shared" si="22"/>
         <v>379</v>
       </c>
+      <c r="B380" t="s">
+        <v>26</v>
+      </c>
       <c r="C380">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7552,6 +8692,9 @@
         <f t="shared" si="22"/>
         <v>380</v>
       </c>
+      <c r="B381" t="s">
+        <v>26</v>
+      </c>
       <c r="C381">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7570,6 +8713,9 @@
         <f t="shared" si="22"/>
         <v>381</v>
       </c>
+      <c r="B382" t="s">
+        <v>26</v>
+      </c>
       <c r="C382">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7588,6 +8734,9 @@
         <f t="shared" si="22"/>
         <v>382</v>
       </c>
+      <c r="B383" t="s">
+        <v>26</v>
+      </c>
       <c r="C383">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7606,6 +8755,9 @@
         <f t="shared" si="22"/>
         <v>383</v>
       </c>
+      <c r="B384" t="s">
+        <v>26</v>
+      </c>
       <c r="C384">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7624,6 +8776,9 @@
         <f t="shared" si="22"/>
         <v>384</v>
       </c>
+      <c r="B385" t="s">
+        <v>26</v>
+      </c>
       <c r="C385">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7642,6 +8797,9 @@
         <f t="shared" si="22"/>
         <v>385</v>
       </c>
+      <c r="B386" t="s">
+        <v>26</v>
+      </c>
       <c r="C386">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7660,6 +8818,9 @@
         <f t="shared" si="22"/>
         <v>386</v>
       </c>
+      <c r="B387" t="s">
+        <v>26</v>
+      </c>
       <c r="C387">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7678,6 +8839,9 @@
         <f t="shared" ref="A388:A451" si="26">A387+1</f>
         <v>387</v>
       </c>
+      <c r="B388" t="s">
+        <v>26</v>
+      </c>
       <c r="C388">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7696,6 +8860,9 @@
         <f t="shared" si="26"/>
         <v>388</v>
       </c>
+      <c r="B389" t="s">
+        <v>26</v>
+      </c>
       <c r="C389">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7714,6 +8881,9 @@
         <f t="shared" si="26"/>
         <v>389</v>
       </c>
+      <c r="B390" t="s">
+        <v>26</v>
+      </c>
       <c r="C390">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7732,6 +8902,9 @@
         <f t="shared" si="26"/>
         <v>390</v>
       </c>
+      <c r="B391" t="s">
+        <v>26</v>
+      </c>
       <c r="C391">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7750,6 +8923,9 @@
         <f t="shared" si="26"/>
         <v>391</v>
       </c>
+      <c r="B392" t="s">
+        <v>26</v>
+      </c>
       <c r="C392">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7768,6 +8944,9 @@
         <f t="shared" si="26"/>
         <v>392</v>
       </c>
+      <c r="B393" t="s">
+        <v>26</v>
+      </c>
       <c r="C393">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7786,6 +8965,9 @@
         <f t="shared" si="26"/>
         <v>393</v>
       </c>
+      <c r="B394" t="s">
+        <v>26</v>
+      </c>
       <c r="C394">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7804,6 +8986,9 @@
         <f t="shared" si="26"/>
         <v>394</v>
       </c>
+      <c r="B395" t="s">
+        <v>26</v>
+      </c>
       <c r="C395">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7822,6 +9007,9 @@
         <f t="shared" si="26"/>
         <v>395</v>
       </c>
+      <c r="B396" t="s">
+        <v>26</v>
+      </c>
       <c r="C396">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7840,6 +9028,9 @@
         <f t="shared" si="26"/>
         <v>396</v>
       </c>
+      <c r="B397" t="s">
+        <v>26</v>
+      </c>
       <c r="C397">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7858,6 +9049,9 @@
         <f t="shared" si="26"/>
         <v>397</v>
       </c>
+      <c r="B398" t="s">
+        <v>26</v>
+      </c>
       <c r="C398">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7876,6 +9070,9 @@
         <f t="shared" si="26"/>
         <v>398</v>
       </c>
+      <c r="B399" t="s">
+        <v>26</v>
+      </c>
       <c r="C399">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7894,6 +9091,9 @@
         <f t="shared" si="26"/>
         <v>399</v>
       </c>
+      <c r="B400" t="s">
+        <v>26</v>
+      </c>
       <c r="C400">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7912,6 +9112,9 @@
         <f t="shared" si="26"/>
         <v>400</v>
       </c>
+      <c r="B401" t="s">
+        <v>26</v>
+      </c>
       <c r="C401">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7930,6 +9133,9 @@
         <f t="shared" si="26"/>
         <v>401</v>
       </c>
+      <c r="B402" t="s">
+        <v>26</v>
+      </c>
       <c r="C402">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7948,6 +9154,9 @@
         <f t="shared" si="26"/>
         <v>402</v>
       </c>
+      <c r="B403" t="s">
+        <v>26</v>
+      </c>
       <c r="C403">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7966,6 +9175,9 @@
         <f t="shared" si="26"/>
         <v>403</v>
       </c>
+      <c r="B404" t="s">
+        <v>26</v>
+      </c>
       <c r="C404">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -7984,6 +9196,9 @@
         <f t="shared" si="26"/>
         <v>404</v>
       </c>
+      <c r="B405" t="s">
+        <v>26</v>
+      </c>
       <c r="C405">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8002,6 +9217,9 @@
         <f t="shared" si="26"/>
         <v>405</v>
       </c>
+      <c r="B406" t="s">
+        <v>26</v>
+      </c>
       <c r="C406">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8020,6 +9238,9 @@
         <f t="shared" si="26"/>
         <v>406</v>
       </c>
+      <c r="B407" t="s">
+        <v>26</v>
+      </c>
       <c r="C407">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8038,6 +9259,9 @@
         <f t="shared" si="26"/>
         <v>407</v>
       </c>
+      <c r="B408" t="s">
+        <v>26</v>
+      </c>
       <c r="C408">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8056,6 +9280,9 @@
         <f t="shared" si="26"/>
         <v>408</v>
       </c>
+      <c r="B409" t="s">
+        <v>26</v>
+      </c>
       <c r="C409">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8074,6 +9301,9 @@
         <f t="shared" si="26"/>
         <v>409</v>
       </c>
+      <c r="B410" t="s">
+        <v>26</v>
+      </c>
       <c r="C410">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8092,6 +9322,9 @@
         <f t="shared" si="26"/>
         <v>410</v>
       </c>
+      <c r="B411" t="s">
+        <v>26</v>
+      </c>
       <c r="C411">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8110,6 +9343,9 @@
         <f t="shared" si="26"/>
         <v>411</v>
       </c>
+      <c r="B412" t="s">
+        <v>26</v>
+      </c>
       <c r="C412">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8128,6 +9364,9 @@
         <f t="shared" si="26"/>
         <v>412</v>
       </c>
+      <c r="B413" t="s">
+        <v>26</v>
+      </c>
       <c r="C413">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8146,6 +9385,9 @@
         <f t="shared" si="26"/>
         <v>413</v>
       </c>
+      <c r="B414" t="s">
+        <v>26</v>
+      </c>
       <c r="C414">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8164,6 +9406,9 @@
         <f t="shared" si="26"/>
         <v>414</v>
       </c>
+      <c r="B415" t="s">
+        <v>26</v>
+      </c>
       <c r="C415">
         <f t="shared" si="24"/>
         <v>110</v>
@@ -8182,6 +9427,9 @@
         <f t="shared" si="26"/>
         <v>415</v>
       </c>
+      <c r="B416" t="s">
+        <v>26</v>
+      </c>
       <c r="C416">
         <f t="shared" ref="C416:C442" si="28">C415</f>
         <v>110</v>
@@ -8200,6 +9448,9 @@
         <f t="shared" si="26"/>
         <v>416</v>
       </c>
+      <c r="B417" t="s">
+        <v>26</v>
+      </c>
       <c r="C417">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8218,6 +9469,9 @@
         <f t="shared" si="26"/>
         <v>417</v>
       </c>
+      <c r="B418" t="s">
+        <v>26</v>
+      </c>
       <c r="C418">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8236,6 +9490,9 @@
         <f t="shared" si="26"/>
         <v>418</v>
       </c>
+      <c r="B419" t="s">
+        <v>26</v>
+      </c>
       <c r="C419">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8254,6 +9511,9 @@
         <f t="shared" si="26"/>
         <v>419</v>
       </c>
+      <c r="B420" t="s">
+        <v>26</v>
+      </c>
       <c r="C420">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8272,6 +9532,9 @@
         <f t="shared" si="26"/>
         <v>420</v>
       </c>
+      <c r="B421" t="s">
+        <v>26</v>
+      </c>
       <c r="C421">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8290,6 +9553,9 @@
         <f t="shared" si="26"/>
         <v>421</v>
       </c>
+      <c r="B422" t="s">
+        <v>26</v>
+      </c>
       <c r="C422">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8308,6 +9574,9 @@
         <f t="shared" si="26"/>
         <v>422</v>
       </c>
+      <c r="B423" t="s">
+        <v>26</v>
+      </c>
       <c r="C423">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8326,6 +9595,9 @@
         <f t="shared" si="26"/>
         <v>423</v>
       </c>
+      <c r="B424" t="s">
+        <v>26</v>
+      </c>
       <c r="C424">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8344,6 +9616,9 @@
         <f t="shared" si="26"/>
         <v>424</v>
       </c>
+      <c r="B425" t="s">
+        <v>26</v>
+      </c>
       <c r="C425">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8362,6 +9637,9 @@
         <f t="shared" si="26"/>
         <v>425</v>
       </c>
+      <c r="B426" t="s">
+        <v>26</v>
+      </c>
       <c r="C426">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8380,6 +9658,9 @@
         <f t="shared" si="26"/>
         <v>426</v>
       </c>
+      <c r="B427" t="s">
+        <v>26</v>
+      </c>
       <c r="C427">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8398,6 +9679,9 @@
         <f t="shared" si="26"/>
         <v>427</v>
       </c>
+      <c r="B428" t="s">
+        <v>26</v>
+      </c>
       <c r="C428">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8416,6 +9700,9 @@
         <f t="shared" si="26"/>
         <v>428</v>
       </c>
+      <c r="B429" t="s">
+        <v>26</v>
+      </c>
       <c r="C429">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8434,6 +9721,9 @@
         <f t="shared" si="26"/>
         <v>429</v>
       </c>
+      <c r="B430" t="s">
+        <v>26</v>
+      </c>
       <c r="C430">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8452,6 +9742,9 @@
         <f t="shared" si="26"/>
         <v>430</v>
       </c>
+      <c r="B431" t="s">
+        <v>26</v>
+      </c>
       <c r="C431">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8470,6 +9763,9 @@
         <f t="shared" si="26"/>
         <v>431</v>
       </c>
+      <c r="B432" t="s">
+        <v>26</v>
+      </c>
       <c r="C432">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8488,6 +9784,9 @@
         <f t="shared" si="26"/>
         <v>432</v>
       </c>
+      <c r="B433" t="s">
+        <v>26</v>
+      </c>
       <c r="C433">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8506,6 +9805,9 @@
         <f t="shared" si="26"/>
         <v>433</v>
       </c>
+      <c r="B434" t="s">
+        <v>26</v>
+      </c>
       <c r="C434">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8524,6 +9826,9 @@
         <f t="shared" si="26"/>
         <v>434</v>
       </c>
+      <c r="B435" t="s">
+        <v>26</v>
+      </c>
       <c r="C435">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8542,6 +9847,9 @@
         <f t="shared" si="26"/>
         <v>435</v>
       </c>
+      <c r="B436" t="s">
+        <v>26</v>
+      </c>
       <c r="C436">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8560,6 +9868,9 @@
         <f t="shared" si="26"/>
         <v>436</v>
       </c>
+      <c r="B437" t="s">
+        <v>26</v>
+      </c>
       <c r="C437">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8578,6 +9889,9 @@
         <f t="shared" si="26"/>
         <v>437</v>
       </c>
+      <c r="B438" t="s">
+        <v>26</v>
+      </c>
       <c r="C438">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8596,6 +9910,9 @@
         <f t="shared" si="26"/>
         <v>438</v>
       </c>
+      <c r="B439" t="s">
+        <v>26</v>
+      </c>
       <c r="C439">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8614,6 +9931,9 @@
         <f t="shared" si="26"/>
         <v>439</v>
       </c>
+      <c r="B440" t="s">
+        <v>26</v>
+      </c>
       <c r="C440">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8632,6 +9952,9 @@
         <f t="shared" si="26"/>
         <v>440</v>
       </c>
+      <c r="B441" t="s">
+        <v>26</v>
+      </c>
       <c r="C441">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8650,6 +9973,9 @@
         <f t="shared" si="26"/>
         <v>441</v>
       </c>
+      <c r="B442" t="s">
+        <v>26</v>
+      </c>
       <c r="C442">
         <f t="shared" si="28"/>
         <v>110</v>
@@ -8668,6 +9994,9 @@
         <f t="shared" si="26"/>
         <v>442</v>
       </c>
+      <c r="B443" t="s">
+        <v>26</v>
+      </c>
       <c r="C443">
         <v>111</v>
       </c>
@@ -8684,6 +10013,9 @@
         <f t="shared" si="26"/>
         <v>443</v>
       </c>
+      <c r="B444" t="s">
+        <v>26</v>
+      </c>
       <c r="C444">
         <f>C443</f>
         <v>111</v>
@@ -8702,6 +10034,9 @@
         <f t="shared" si="26"/>
         <v>444</v>
       </c>
+      <c r="B445" t="s">
+        <v>26</v>
+      </c>
       <c r="C445">
         <f t="shared" ref="C445:C508" si="30">C444</f>
         <v>111</v>
@@ -8720,6 +10055,9 @@
         <f t="shared" si="26"/>
         <v>445</v>
       </c>
+      <c r="B446" t="s">
+        <v>26</v>
+      </c>
       <c r="C446">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8738,6 +10076,9 @@
         <f t="shared" si="26"/>
         <v>446</v>
       </c>
+      <c r="B447" t="s">
+        <v>26</v>
+      </c>
       <c r="C447">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8756,6 +10097,9 @@
         <f t="shared" si="26"/>
         <v>447</v>
       </c>
+      <c r="B448" t="s">
+        <v>26</v>
+      </c>
       <c r="C448">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8774,6 +10118,9 @@
         <f t="shared" si="26"/>
         <v>448</v>
       </c>
+      <c r="B449" t="s">
+        <v>26</v>
+      </c>
       <c r="C449">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8792,6 +10139,9 @@
         <f t="shared" si="26"/>
         <v>449</v>
       </c>
+      <c r="B450" t="s">
+        <v>26</v>
+      </c>
       <c r="C450">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8810,6 +10160,9 @@
         <f t="shared" si="26"/>
         <v>450</v>
       </c>
+      <c r="B451" t="s">
+        <v>26</v>
+      </c>
       <c r="C451">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8828,6 +10181,9 @@
         <f t="shared" ref="A452:A515" si="32">A451+1</f>
         <v>451</v>
       </c>
+      <c r="B452" t="s">
+        <v>26</v>
+      </c>
       <c r="C452">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8846,6 +10202,9 @@
         <f t="shared" si="32"/>
         <v>452</v>
       </c>
+      <c r="B453" t="s">
+        <v>26</v>
+      </c>
       <c r="C453">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8864,6 +10223,9 @@
         <f t="shared" si="32"/>
         <v>453</v>
       </c>
+      <c r="B454" t="s">
+        <v>26</v>
+      </c>
       <c r="C454">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8882,6 +10244,9 @@
         <f t="shared" si="32"/>
         <v>454</v>
       </c>
+      <c r="B455" t="s">
+        <v>26</v>
+      </c>
       <c r="C455">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8900,6 +10265,9 @@
         <f t="shared" si="32"/>
         <v>455</v>
       </c>
+      <c r="B456" t="s">
+        <v>26</v>
+      </c>
       <c r="C456">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8944,6 +10312,9 @@
         <f t="shared" si="32"/>
         <v>456</v>
       </c>
+      <c r="B457" t="s">
+        <v>26</v>
+      </c>
       <c r="C457">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -8988,6 +10359,9 @@
         <f t="shared" si="32"/>
         <v>457</v>
       </c>
+      <c r="B458" t="s">
+        <v>26</v>
+      </c>
       <c r="C458">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9032,6 +10406,9 @@
         <f t="shared" si="32"/>
         <v>458</v>
       </c>
+      <c r="B459" t="s">
+        <v>26</v>
+      </c>
       <c r="C459">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9076,6 +10453,9 @@
         <f t="shared" si="32"/>
         <v>459</v>
       </c>
+      <c r="B460" t="s">
+        <v>26</v>
+      </c>
       <c r="C460">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9120,6 +10500,9 @@
         <f t="shared" si="32"/>
         <v>460</v>
       </c>
+      <c r="B461" t="s">
+        <v>26</v>
+      </c>
       <c r="C461">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9164,6 +10547,9 @@
         <f t="shared" si="32"/>
         <v>461</v>
       </c>
+      <c r="B462" t="s">
+        <v>26</v>
+      </c>
       <c r="C462">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9208,6 +10594,9 @@
         <f t="shared" si="32"/>
         <v>462</v>
       </c>
+      <c r="B463" t="s">
+        <v>26</v>
+      </c>
       <c r="C463">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9225,6 +10614,9 @@
         <f t="shared" si="32"/>
         <v>463</v>
       </c>
+      <c r="B464" t="s">
+        <v>26</v>
+      </c>
       <c r="C464">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9243,6 +10635,9 @@
         <f t="shared" si="32"/>
         <v>464</v>
       </c>
+      <c r="B465" t="s">
+        <v>26</v>
+      </c>
       <c r="C465">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9261,6 +10656,9 @@
         <f t="shared" si="32"/>
         <v>465</v>
       </c>
+      <c r="B466" t="s">
+        <v>26</v>
+      </c>
       <c r="C466">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9279,6 +10677,9 @@
         <f t="shared" si="32"/>
         <v>466</v>
       </c>
+      <c r="B467" t="s">
+        <v>26</v>
+      </c>
       <c r="C467">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9297,6 +10698,9 @@
         <f t="shared" si="32"/>
         <v>467</v>
       </c>
+      <c r="B468" t="s">
+        <v>26</v>
+      </c>
       <c r="C468">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9315,6 +10719,9 @@
         <f t="shared" si="32"/>
         <v>468</v>
       </c>
+      <c r="B469" t="s">
+        <v>26</v>
+      </c>
       <c r="C469">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9333,6 +10740,9 @@
         <f t="shared" si="32"/>
         <v>469</v>
       </c>
+      <c r="B470" t="s">
+        <v>26</v>
+      </c>
       <c r="C470">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9351,6 +10761,9 @@
         <f t="shared" si="32"/>
         <v>470</v>
       </c>
+      <c r="B471" t="s">
+        <v>26</v>
+      </c>
       <c r="C471">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9369,6 +10782,9 @@
         <f t="shared" si="32"/>
         <v>471</v>
       </c>
+      <c r="B472" t="s">
+        <v>26</v>
+      </c>
       <c r="C472">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9387,6 +10803,9 @@
         <f t="shared" si="32"/>
         <v>472</v>
       </c>
+      <c r="B473" t="s">
+        <v>26</v>
+      </c>
       <c r="C473">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9405,6 +10824,9 @@
         <f t="shared" si="32"/>
         <v>473</v>
       </c>
+      <c r="B474" t="s">
+        <v>26</v>
+      </c>
       <c r="C474">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9423,6 +10845,9 @@
         <f t="shared" si="32"/>
         <v>474</v>
       </c>
+      <c r="B475" t="s">
+        <v>26</v>
+      </c>
       <c r="C475">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9441,6 +10866,9 @@
         <f t="shared" si="32"/>
         <v>475</v>
       </c>
+      <c r="B476" t="s">
+        <v>26</v>
+      </c>
       <c r="C476">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9459,6 +10887,9 @@
         <f t="shared" si="32"/>
         <v>476</v>
       </c>
+      <c r="B477" t="s">
+        <v>26</v>
+      </c>
       <c r="C477">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9477,6 +10908,9 @@
         <f t="shared" si="32"/>
         <v>477</v>
       </c>
+      <c r="B478" t="s">
+        <v>26</v>
+      </c>
       <c r="C478">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9495,6 +10929,9 @@
         <f t="shared" si="32"/>
         <v>478</v>
       </c>
+      <c r="B479" t="s">
+        <v>26</v>
+      </c>
       <c r="C479">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9513,6 +10950,9 @@
         <f t="shared" si="32"/>
         <v>479</v>
       </c>
+      <c r="B480" t="s">
+        <v>26</v>
+      </c>
       <c r="C480">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9531,6 +10971,9 @@
         <f t="shared" si="32"/>
         <v>480</v>
       </c>
+      <c r="B481" t="s">
+        <v>26</v>
+      </c>
       <c r="C481">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9549,6 +10992,9 @@
         <f t="shared" si="32"/>
         <v>481</v>
       </c>
+      <c r="B482" t="s">
+        <v>26</v>
+      </c>
       <c r="C482">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9567,6 +11013,9 @@
         <f t="shared" si="32"/>
         <v>482</v>
       </c>
+      <c r="B483" t="s">
+        <v>26</v>
+      </c>
       <c r="C483">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9585,6 +11034,9 @@
         <f t="shared" si="32"/>
         <v>483</v>
       </c>
+      <c r="B484" t="s">
+        <v>26</v>
+      </c>
       <c r="C484">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9603,6 +11055,9 @@
         <f t="shared" si="32"/>
         <v>484</v>
       </c>
+      <c r="B485" t="s">
+        <v>26</v>
+      </c>
       <c r="C485">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9621,6 +11076,9 @@
         <f t="shared" si="32"/>
         <v>485</v>
       </c>
+      <c r="B486" t="s">
+        <v>26</v>
+      </c>
       <c r="C486">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9639,6 +11097,9 @@
         <f t="shared" si="32"/>
         <v>486</v>
       </c>
+      <c r="B487" t="s">
+        <v>26</v>
+      </c>
       <c r="C487">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9657,6 +11118,9 @@
         <f t="shared" si="32"/>
         <v>487</v>
       </c>
+      <c r="B488" t="s">
+        <v>26</v>
+      </c>
       <c r="C488">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9675,6 +11139,9 @@
         <f t="shared" si="32"/>
         <v>488</v>
       </c>
+      <c r="B489" t="s">
+        <v>26</v>
+      </c>
       <c r="C489">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9693,6 +11160,9 @@
         <f t="shared" si="32"/>
         <v>489</v>
       </c>
+      <c r="B490" t="s">
+        <v>26</v>
+      </c>
       <c r="C490">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9711,6 +11181,9 @@
         <f t="shared" si="32"/>
         <v>490</v>
       </c>
+      <c r="B491" t="s">
+        <v>26</v>
+      </c>
       <c r="C491">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9729,6 +11202,9 @@
         <f t="shared" si="32"/>
         <v>491</v>
       </c>
+      <c r="B492" t="s">
+        <v>26</v>
+      </c>
       <c r="C492">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9747,6 +11223,9 @@
         <f t="shared" si="32"/>
         <v>492</v>
       </c>
+      <c r="B493" t="s">
+        <v>26</v>
+      </c>
       <c r="C493">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9765,6 +11244,9 @@
         <f t="shared" si="32"/>
         <v>493</v>
       </c>
+      <c r="B494" t="s">
+        <v>26</v>
+      </c>
       <c r="C494">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9783,6 +11265,9 @@
         <f t="shared" si="32"/>
         <v>494</v>
       </c>
+      <c r="B495" t="s">
+        <v>26</v>
+      </c>
       <c r="C495">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9801,6 +11286,9 @@
         <f t="shared" si="32"/>
         <v>495</v>
       </c>
+      <c r="B496" t="s">
+        <v>26</v>
+      </c>
       <c r="C496">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9819,6 +11307,9 @@
         <f t="shared" si="32"/>
         <v>496</v>
       </c>
+      <c r="B497" t="s">
+        <v>26</v>
+      </c>
       <c r="C497">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9837,6 +11328,9 @@
         <f t="shared" si="32"/>
         <v>497</v>
       </c>
+      <c r="B498" t="s">
+        <v>26</v>
+      </c>
       <c r="C498">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9855,6 +11349,9 @@
         <f t="shared" si="32"/>
         <v>498</v>
       </c>
+      <c r="B499" t="s">
+        <v>26</v>
+      </c>
       <c r="C499">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9873,6 +11370,9 @@
         <f t="shared" si="32"/>
         <v>499</v>
       </c>
+      <c r="B500" t="s">
+        <v>26</v>
+      </c>
       <c r="C500">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9891,6 +11391,9 @@
         <f t="shared" si="32"/>
         <v>500</v>
       </c>
+      <c r="B501" t="s">
+        <v>26</v>
+      </c>
       <c r="C501">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9909,6 +11412,9 @@
         <f t="shared" si="32"/>
         <v>501</v>
       </c>
+      <c r="B502" t="s">
+        <v>26</v>
+      </c>
       <c r="C502">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9927,6 +11433,9 @@
         <f t="shared" si="32"/>
         <v>502</v>
       </c>
+      <c r="B503" t="s">
+        <v>26</v>
+      </c>
       <c r="C503">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9945,6 +11454,9 @@
         <f t="shared" si="32"/>
         <v>503</v>
       </c>
+      <c r="B504" t="s">
+        <v>26</v>
+      </c>
       <c r="C504">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9963,6 +11475,9 @@
         <f t="shared" si="32"/>
         <v>504</v>
       </c>
+      <c r="B505" t="s">
+        <v>26</v>
+      </c>
       <c r="C505">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9981,6 +11496,9 @@
         <f t="shared" si="32"/>
         <v>505</v>
       </c>
+      <c r="B506" t="s">
+        <v>26</v>
+      </c>
       <c r="C506">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -9999,6 +11517,9 @@
         <f t="shared" si="32"/>
         <v>506</v>
       </c>
+      <c r="B507" t="s">
+        <v>26</v>
+      </c>
       <c r="C507">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -10017,6 +11538,9 @@
         <f t="shared" si="32"/>
         <v>507</v>
       </c>
+      <c r="B508" t="s">
+        <v>26</v>
+      </c>
       <c r="C508">
         <f t="shared" si="30"/>
         <v>111</v>
@@ -10035,6 +11559,9 @@
         <f t="shared" si="32"/>
         <v>508</v>
       </c>
+      <c r="B509" t="s">
+        <v>26</v>
+      </c>
       <c r="C509">
         <f t="shared" ref="C509:C572" si="34">C508</f>
         <v>111</v>
@@ -10053,6 +11580,9 @@
         <f t="shared" si="32"/>
         <v>509</v>
       </c>
+      <c r="B510" t="s">
+        <v>26</v>
+      </c>
       <c r="C510">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10071,6 +11601,9 @@
         <f t="shared" si="32"/>
         <v>510</v>
       </c>
+      <c r="B511" t="s">
+        <v>26</v>
+      </c>
       <c r="C511">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10089,6 +11622,9 @@
         <f t="shared" si="32"/>
         <v>511</v>
       </c>
+      <c r="B512" t="s">
+        <v>26</v>
+      </c>
       <c r="C512">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10107,6 +11643,9 @@
         <f t="shared" si="32"/>
         <v>512</v>
       </c>
+      <c r="B513" t="s">
+        <v>26</v>
+      </c>
       <c r="C513">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10125,6 +11664,9 @@
         <f t="shared" si="32"/>
         <v>513</v>
       </c>
+      <c r="B514" t="s">
+        <v>26</v>
+      </c>
       <c r="C514">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10143,6 +11685,9 @@
         <f t="shared" si="32"/>
         <v>514</v>
       </c>
+      <c r="B515" t="s">
+        <v>26</v>
+      </c>
       <c r="C515">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10161,6 +11706,9 @@
         <f t="shared" ref="A516:A579" si="36">A515+1</f>
         <v>515</v>
       </c>
+      <c r="B516" t="s">
+        <v>26</v>
+      </c>
       <c r="C516">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10179,6 +11727,9 @@
         <f t="shared" si="36"/>
         <v>516</v>
       </c>
+      <c r="B517" t="s">
+        <v>26</v>
+      </c>
       <c r="C517">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10197,6 +11748,9 @@
         <f t="shared" si="36"/>
         <v>517</v>
       </c>
+      <c r="B518" t="s">
+        <v>26</v>
+      </c>
       <c r="C518">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10215,6 +11769,9 @@
         <f t="shared" si="36"/>
         <v>518</v>
       </c>
+      <c r="B519" t="s">
+        <v>26</v>
+      </c>
       <c r="C519">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10233,6 +11790,9 @@
         <f t="shared" si="36"/>
         <v>519</v>
       </c>
+      <c r="B520" t="s">
+        <v>26</v>
+      </c>
       <c r="C520">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10251,6 +11811,9 @@
         <f t="shared" si="36"/>
         <v>520</v>
       </c>
+      <c r="B521" t="s">
+        <v>26</v>
+      </c>
       <c r="C521">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10269,6 +11832,9 @@
         <f t="shared" si="36"/>
         <v>521</v>
       </c>
+      <c r="B522" t="s">
+        <v>26</v>
+      </c>
       <c r="C522">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10287,6 +11853,9 @@
         <f t="shared" si="36"/>
         <v>522</v>
       </c>
+      <c r="B523" t="s">
+        <v>26</v>
+      </c>
       <c r="C523">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10305,6 +11874,9 @@
         <f t="shared" si="36"/>
         <v>523</v>
       </c>
+      <c r="B524" t="s">
+        <v>26</v>
+      </c>
       <c r="C524">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10323,6 +11895,9 @@
         <f t="shared" si="36"/>
         <v>524</v>
       </c>
+      <c r="B525" t="s">
+        <v>26</v>
+      </c>
       <c r="C525">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10341,6 +11916,9 @@
         <f t="shared" si="36"/>
         <v>525</v>
       </c>
+      <c r="B526" t="s">
+        <v>26</v>
+      </c>
       <c r="C526">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10359,6 +11937,9 @@
         <f t="shared" si="36"/>
         <v>526</v>
       </c>
+      <c r="B527" t="s">
+        <v>26</v>
+      </c>
       <c r="C527">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10377,6 +11958,9 @@
         <f t="shared" si="36"/>
         <v>527</v>
       </c>
+      <c r="B528" t="s">
+        <v>26</v>
+      </c>
       <c r="C528">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10395,6 +11979,9 @@
         <f t="shared" si="36"/>
         <v>528</v>
       </c>
+      <c r="B529" t="s">
+        <v>26</v>
+      </c>
       <c r="C529">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10413,6 +12000,9 @@
         <f t="shared" si="36"/>
         <v>529</v>
       </c>
+      <c r="B530" t="s">
+        <v>26</v>
+      </c>
       <c r="C530">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10431,6 +12021,9 @@
         <f t="shared" si="36"/>
         <v>530</v>
       </c>
+      <c r="B531" t="s">
+        <v>26</v>
+      </c>
       <c r="C531">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10449,6 +12042,9 @@
         <f t="shared" si="36"/>
         <v>531</v>
       </c>
+      <c r="B532" t="s">
+        <v>26</v>
+      </c>
       <c r="C532">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10467,6 +12063,9 @@
         <f t="shared" si="36"/>
         <v>532</v>
       </c>
+      <c r="B533" t="s">
+        <v>26</v>
+      </c>
       <c r="C533">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10485,6 +12084,9 @@
         <f t="shared" si="36"/>
         <v>533</v>
       </c>
+      <c r="B534" t="s">
+        <v>26</v>
+      </c>
       <c r="C534">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10503,6 +12105,9 @@
         <f t="shared" si="36"/>
         <v>534</v>
       </c>
+      <c r="B535" t="s">
+        <v>26</v>
+      </c>
       <c r="C535">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10521,6 +12126,9 @@
         <f t="shared" si="36"/>
         <v>535</v>
       </c>
+      <c r="B536" t="s">
+        <v>26</v>
+      </c>
       <c r="C536">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10539,6 +12147,9 @@
         <f t="shared" si="36"/>
         <v>536</v>
       </c>
+      <c r="B537" t="s">
+        <v>26</v>
+      </c>
       <c r="C537">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10557,6 +12168,9 @@
         <f t="shared" si="36"/>
         <v>537</v>
       </c>
+      <c r="B538" t="s">
+        <v>26</v>
+      </c>
       <c r="C538">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10575,6 +12189,9 @@
         <f t="shared" si="36"/>
         <v>538</v>
       </c>
+      <c r="B539" t="s">
+        <v>26</v>
+      </c>
       <c r="C539">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10593,6 +12210,9 @@
         <f t="shared" si="36"/>
         <v>539</v>
       </c>
+      <c r="B540" t="s">
+        <v>26</v>
+      </c>
       <c r="C540">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10611,6 +12231,9 @@
         <f t="shared" si="36"/>
         <v>540</v>
       </c>
+      <c r="B541" t="s">
+        <v>26</v>
+      </c>
       <c r="C541">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10629,6 +12252,9 @@
         <f t="shared" si="36"/>
         <v>541</v>
       </c>
+      <c r="B542" t="s">
+        <v>26</v>
+      </c>
       <c r="C542">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10647,6 +12273,9 @@
         <f t="shared" si="36"/>
         <v>542</v>
       </c>
+      <c r="B543" t="s">
+        <v>26</v>
+      </c>
       <c r="C543">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10665,6 +12294,9 @@
         <f t="shared" si="36"/>
         <v>543</v>
       </c>
+      <c r="B544" t="s">
+        <v>26</v>
+      </c>
       <c r="C544">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10683,6 +12315,9 @@
         <f t="shared" si="36"/>
         <v>544</v>
       </c>
+      <c r="B545" t="s">
+        <v>26</v>
+      </c>
       <c r="C545">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10701,6 +12336,9 @@
         <f t="shared" si="36"/>
         <v>545</v>
       </c>
+      <c r="B546" t="s">
+        <v>26</v>
+      </c>
       <c r="C546">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10719,6 +12357,9 @@
         <f t="shared" si="36"/>
         <v>546</v>
       </c>
+      <c r="B547" t="s">
+        <v>26</v>
+      </c>
       <c r="C547">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10737,6 +12378,9 @@
         <f t="shared" si="36"/>
         <v>547</v>
       </c>
+      <c r="B548" t="s">
+        <v>26</v>
+      </c>
       <c r="C548">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10755,6 +12399,9 @@
         <f t="shared" si="36"/>
         <v>548</v>
       </c>
+      <c r="B549" t="s">
+        <v>26</v>
+      </c>
       <c r="C549">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10773,6 +12420,9 @@
         <f t="shared" si="36"/>
         <v>549</v>
       </c>
+      <c r="B550" t="s">
+        <v>26</v>
+      </c>
       <c r="C550">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10791,6 +12441,9 @@
         <f t="shared" si="36"/>
         <v>550</v>
       </c>
+      <c r="B551" t="s">
+        <v>26</v>
+      </c>
       <c r="C551">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10809,6 +12462,9 @@
         <f t="shared" si="36"/>
         <v>551</v>
       </c>
+      <c r="B552" t="s">
+        <v>26</v>
+      </c>
       <c r="C552">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10827,6 +12483,9 @@
         <f t="shared" si="36"/>
         <v>552</v>
       </c>
+      <c r="B553" t="s">
+        <v>26</v>
+      </c>
       <c r="C553">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10845,6 +12504,9 @@
         <f t="shared" si="36"/>
         <v>553</v>
       </c>
+      <c r="B554" t="s">
+        <v>26</v>
+      </c>
       <c r="C554">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10863,6 +12525,9 @@
         <f t="shared" si="36"/>
         <v>554</v>
       </c>
+      <c r="B555" t="s">
+        <v>26</v>
+      </c>
       <c r="C555">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10881,6 +12546,9 @@
         <f t="shared" si="36"/>
         <v>555</v>
       </c>
+      <c r="B556" t="s">
+        <v>26</v>
+      </c>
       <c r="C556">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10899,6 +12567,9 @@
         <f t="shared" si="36"/>
         <v>556</v>
       </c>
+      <c r="B557" t="s">
+        <v>26</v>
+      </c>
       <c r="C557">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10917,6 +12588,9 @@
         <f t="shared" si="36"/>
         <v>557</v>
       </c>
+      <c r="B558" t="s">
+        <v>26</v>
+      </c>
       <c r="C558">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10935,6 +12609,9 @@
         <f t="shared" si="36"/>
         <v>558</v>
       </c>
+      <c r="B559" t="s">
+        <v>26</v>
+      </c>
       <c r="C559">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10953,6 +12630,9 @@
         <f t="shared" si="36"/>
         <v>559</v>
       </c>
+      <c r="B560" t="s">
+        <v>26</v>
+      </c>
       <c r="C560">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10971,6 +12651,9 @@
         <f t="shared" si="36"/>
         <v>560</v>
       </c>
+      <c r="B561" t="s">
+        <v>26</v>
+      </c>
       <c r="C561">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -10989,6 +12672,9 @@
         <f t="shared" si="36"/>
         <v>561</v>
       </c>
+      <c r="B562" t="s">
+        <v>26</v>
+      </c>
       <c r="C562">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11007,6 +12693,9 @@
         <f t="shared" si="36"/>
         <v>562</v>
       </c>
+      <c r="B563" t="s">
+        <v>26</v>
+      </c>
       <c r="C563">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11025,6 +12714,9 @@
         <f t="shared" si="36"/>
         <v>563</v>
       </c>
+      <c r="B564" t="s">
+        <v>26</v>
+      </c>
       <c r="C564">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11043,6 +12735,9 @@
         <f t="shared" si="36"/>
         <v>564</v>
       </c>
+      <c r="B565" t="s">
+        <v>26</v>
+      </c>
       <c r="C565">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11061,6 +12756,9 @@
         <f t="shared" si="36"/>
         <v>565</v>
       </c>
+      <c r="B566" t="s">
+        <v>26</v>
+      </c>
       <c r="C566">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11079,6 +12777,9 @@
         <f t="shared" si="36"/>
         <v>566</v>
       </c>
+      <c r="B567" t="s">
+        <v>26</v>
+      </c>
       <c r="C567">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11097,6 +12798,9 @@
         <f t="shared" si="36"/>
         <v>567</v>
       </c>
+      <c r="B568" t="s">
+        <v>26</v>
+      </c>
       <c r="C568">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11115,6 +12819,9 @@
         <f t="shared" si="36"/>
         <v>568</v>
       </c>
+      <c r="B569" t="s">
+        <v>26</v>
+      </c>
       <c r="C569">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11133,6 +12840,9 @@
         <f t="shared" si="36"/>
         <v>569</v>
       </c>
+      <c r="B570" t="s">
+        <v>26</v>
+      </c>
       <c r="C570">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11151,6 +12861,9 @@
         <f t="shared" si="36"/>
         <v>570</v>
       </c>
+      <c r="B571" t="s">
+        <v>26</v>
+      </c>
       <c r="C571">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11169,6 +12882,9 @@
         <f t="shared" si="36"/>
         <v>571</v>
       </c>
+      <c r="B572" t="s">
+        <v>26</v>
+      </c>
       <c r="C572">
         <f t="shared" si="34"/>
         <v>111</v>
@@ -11187,6 +12903,9 @@
         <f t="shared" si="36"/>
         <v>572</v>
       </c>
+      <c r="B573" t="s">
+        <v>26</v>
+      </c>
       <c r="C573">
         <f t="shared" ref="C573:C606" si="38">C572</f>
         <v>111</v>
@@ -11205,6 +12924,9 @@
         <f t="shared" si="36"/>
         <v>573</v>
       </c>
+      <c r="B574" t="s">
+        <v>26</v>
+      </c>
       <c r="C574">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11223,6 +12945,9 @@
         <f t="shared" si="36"/>
         <v>574</v>
       </c>
+      <c r="B575" t="s">
+        <v>26</v>
+      </c>
       <c r="C575">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11241,6 +12966,9 @@
         <f t="shared" si="36"/>
         <v>575</v>
       </c>
+      <c r="B576" t="s">
+        <v>26</v>
+      </c>
       <c r="C576">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11259,6 +12987,9 @@
         <f t="shared" si="36"/>
         <v>576</v>
       </c>
+      <c r="B577" t="s">
+        <v>26</v>
+      </c>
       <c r="C577">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11277,6 +13008,9 @@
         <f t="shared" si="36"/>
         <v>577</v>
       </c>
+      <c r="B578" t="s">
+        <v>26</v>
+      </c>
       <c r="C578">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11295,6 +13029,9 @@
         <f t="shared" si="36"/>
         <v>578</v>
       </c>
+      <c r="B579" t="s">
+        <v>26</v>
+      </c>
       <c r="C579">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11313,6 +13050,9 @@
         <f t="shared" ref="A580:A643" si="40">A579+1</f>
         <v>579</v>
       </c>
+      <c r="B580" t="s">
+        <v>26</v>
+      </c>
       <c r="C580">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11331,6 +13071,9 @@
         <f t="shared" si="40"/>
         <v>580</v>
       </c>
+      <c r="B581" t="s">
+        <v>26</v>
+      </c>
       <c r="C581">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11349,6 +13092,9 @@
         <f t="shared" si="40"/>
         <v>581</v>
       </c>
+      <c r="B582" t="s">
+        <v>26</v>
+      </c>
       <c r="C582">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11367,6 +13113,9 @@
         <f t="shared" si="40"/>
         <v>582</v>
       </c>
+      <c r="B583" t="s">
+        <v>26</v>
+      </c>
       <c r="C583">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11385,6 +13134,9 @@
         <f t="shared" si="40"/>
         <v>583</v>
       </c>
+      <c r="B584" t="s">
+        <v>26</v>
+      </c>
       <c r="C584">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11403,6 +13155,9 @@
         <f t="shared" si="40"/>
         <v>584</v>
       </c>
+      <c r="B585" t="s">
+        <v>26</v>
+      </c>
       <c r="C585">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11421,6 +13176,9 @@
         <f t="shared" si="40"/>
         <v>585</v>
       </c>
+      <c r="B586" t="s">
+        <v>26</v>
+      </c>
       <c r="C586">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11439,6 +13197,9 @@
         <f t="shared" si="40"/>
         <v>586</v>
       </c>
+      <c r="B587" t="s">
+        <v>26</v>
+      </c>
       <c r="C587">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11457,6 +13218,9 @@
         <f t="shared" si="40"/>
         <v>587</v>
       </c>
+      <c r="B588" t="s">
+        <v>26</v>
+      </c>
       <c r="C588">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11475,6 +13239,9 @@
         <f t="shared" si="40"/>
         <v>588</v>
       </c>
+      <c r="B589" t="s">
+        <v>26</v>
+      </c>
       <c r="C589">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11493,6 +13260,9 @@
         <f t="shared" si="40"/>
         <v>589</v>
       </c>
+      <c r="B590" t="s">
+        <v>26</v>
+      </c>
       <c r="C590">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11511,6 +13281,9 @@
         <f t="shared" si="40"/>
         <v>590</v>
       </c>
+      <c r="B591" t="s">
+        <v>26</v>
+      </c>
       <c r="C591">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11529,6 +13302,9 @@
         <f t="shared" si="40"/>
         <v>591</v>
       </c>
+      <c r="B592" t="s">
+        <v>26</v>
+      </c>
       <c r="C592">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11547,6 +13323,9 @@
         <f t="shared" si="40"/>
         <v>592</v>
       </c>
+      <c r="B593" t="s">
+        <v>26</v>
+      </c>
       <c r="C593">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11565,6 +13344,9 @@
         <f t="shared" si="40"/>
         <v>593</v>
       </c>
+      <c r="B594" t="s">
+        <v>26</v>
+      </c>
       <c r="C594">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11583,6 +13365,9 @@
         <f t="shared" si="40"/>
         <v>594</v>
       </c>
+      <c r="B595" t="s">
+        <v>26</v>
+      </c>
       <c r="C595">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11601,6 +13386,9 @@
         <f t="shared" si="40"/>
         <v>595</v>
       </c>
+      <c r="B596" t="s">
+        <v>26</v>
+      </c>
       <c r="C596">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11619,6 +13407,9 @@
         <f t="shared" si="40"/>
         <v>596</v>
       </c>
+      <c r="B597" t="s">
+        <v>26</v>
+      </c>
       <c r="C597">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11637,6 +13428,9 @@
         <f t="shared" si="40"/>
         <v>597</v>
       </c>
+      <c r="B598" t="s">
+        <v>26</v>
+      </c>
       <c r="C598">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11655,6 +13449,9 @@
         <f t="shared" si="40"/>
         <v>598</v>
       </c>
+      <c r="B599" t="s">
+        <v>26</v>
+      </c>
       <c r="C599">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11673,6 +13470,9 @@
         <f t="shared" si="40"/>
         <v>599</v>
       </c>
+      <c r="B600" t="s">
+        <v>26</v>
+      </c>
       <c r="C600">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11691,6 +13491,9 @@
         <f t="shared" si="40"/>
         <v>600</v>
       </c>
+      <c r="B601" t="s">
+        <v>26</v>
+      </c>
       <c r="C601">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11709,6 +13512,9 @@
         <f t="shared" si="40"/>
         <v>601</v>
       </c>
+      <c r="B602" t="s">
+        <v>26</v>
+      </c>
       <c r="C602">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11727,6 +13533,9 @@
         <f t="shared" si="40"/>
         <v>602</v>
       </c>
+      <c r="B603" t="s">
+        <v>26</v>
+      </c>
       <c r="C603">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11745,6 +13554,9 @@
         <f t="shared" si="40"/>
         <v>603</v>
       </c>
+      <c r="B604" t="s">
+        <v>26</v>
+      </c>
       <c r="C604">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11763,6 +13575,9 @@
         <f t="shared" si="40"/>
         <v>604</v>
       </c>
+      <c r="B605" t="s">
+        <v>26</v>
+      </c>
       <c r="C605">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11781,6 +13596,9 @@
         <f t="shared" si="40"/>
         <v>605</v>
       </c>
+      <c r="B606" t="s">
+        <v>26</v>
+      </c>
       <c r="C606">
         <f t="shared" si="38"/>
         <v>111</v>
@@ -11799,6 +13617,9 @@
         <f t="shared" si="40"/>
         <v>606</v>
       </c>
+      <c r="B607" t="s">
+        <v>26</v>
+      </c>
       <c r="C607">
         <v>112</v>
       </c>
@@ -11815,6 +13636,9 @@
         <f t="shared" si="40"/>
         <v>607</v>
       </c>
+      <c r="B608" t="s">
+        <v>26</v>
+      </c>
       <c r="C608">
         <f>C607</f>
         <v>112</v>
@@ -11833,6 +13657,9 @@
         <f t="shared" si="40"/>
         <v>608</v>
       </c>
+      <c r="B609" t="s">
+        <v>26</v>
+      </c>
       <c r="C609">
         <f t="shared" ref="C609:C672" si="42">C608</f>
         <v>112</v>
@@ -11851,6 +13678,9 @@
         <f t="shared" si="40"/>
         <v>609</v>
       </c>
+      <c r="B610" t="s">
+        <v>26</v>
+      </c>
       <c r="C610">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -11869,6 +13699,9 @@
         <f t="shared" si="40"/>
         <v>610</v>
       </c>
+      <c r="B611" t="s">
+        <v>26</v>
+      </c>
       <c r="C611">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -11887,6 +13720,9 @@
         <f t="shared" si="40"/>
         <v>611</v>
       </c>
+      <c r="B612" t="s">
+        <v>26</v>
+      </c>
       <c r="C612">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -11905,6 +13741,9 @@
         <f t="shared" si="40"/>
         <v>612</v>
       </c>
+      <c r="B613" t="s">
+        <v>26</v>
+      </c>
       <c r="C613">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -11923,6 +13762,9 @@
         <f t="shared" si="40"/>
         <v>613</v>
       </c>
+      <c r="B614" t="s">
+        <v>26</v>
+      </c>
       <c r="C614">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -11941,6 +13783,9 @@
         <f t="shared" si="40"/>
         <v>614</v>
       </c>
+      <c r="B615" t="s">
+        <v>26</v>
+      </c>
       <c r="C615">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -11959,6 +13804,9 @@
         <f t="shared" si="40"/>
         <v>615</v>
       </c>
+      <c r="B616" t="s">
+        <v>26</v>
+      </c>
       <c r="C616">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -11977,6 +13825,9 @@
         <f t="shared" si="40"/>
         <v>616</v>
       </c>
+      <c r="B617" t="s">
+        <v>26</v>
+      </c>
       <c r="C617">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -11995,6 +13846,9 @@
         <f t="shared" si="40"/>
         <v>617</v>
       </c>
+      <c r="B618" t="s">
+        <v>26</v>
+      </c>
       <c r="C618">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12013,6 +13867,9 @@
         <f t="shared" si="40"/>
         <v>618</v>
       </c>
+      <c r="B619" t="s">
+        <v>26</v>
+      </c>
       <c r="C619">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12031,6 +13888,9 @@
         <f t="shared" si="40"/>
         <v>619</v>
       </c>
+      <c r="B620" t="s">
+        <v>26</v>
+      </c>
       <c r="C620">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12049,6 +13909,9 @@
         <f t="shared" si="40"/>
         <v>620</v>
       </c>
+      <c r="B621" t="s">
+        <v>26</v>
+      </c>
       <c r="C621">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12067,6 +13930,9 @@
         <f t="shared" si="40"/>
         <v>621</v>
       </c>
+      <c r="B622" t="s">
+        <v>26</v>
+      </c>
       <c r="C622">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12085,6 +13951,9 @@
         <f t="shared" si="40"/>
         <v>622</v>
       </c>
+      <c r="B623" t="s">
+        <v>26</v>
+      </c>
       <c r="C623">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12103,6 +13972,9 @@
         <f t="shared" si="40"/>
         <v>623</v>
       </c>
+      <c r="B624" t="s">
+        <v>26</v>
+      </c>
       <c r="C624">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12121,6 +13993,9 @@
         <f t="shared" si="40"/>
         <v>624</v>
       </c>
+      <c r="B625" t="s">
+        <v>26</v>
+      </c>
       <c r="C625">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12139,6 +14014,9 @@
         <f t="shared" si="40"/>
         <v>625</v>
       </c>
+      <c r="B626" t="s">
+        <v>26</v>
+      </c>
       <c r="C626">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12157,6 +14035,9 @@
         <f t="shared" si="40"/>
         <v>626</v>
       </c>
+      <c r="B627" t="s">
+        <v>26</v>
+      </c>
       <c r="C627">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12175,6 +14056,9 @@
         <f t="shared" si="40"/>
         <v>627</v>
       </c>
+      <c r="B628" t="s">
+        <v>26</v>
+      </c>
       <c r="C628">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12193,6 +14077,9 @@
         <f t="shared" si="40"/>
         <v>628</v>
       </c>
+      <c r="B629" t="s">
+        <v>26</v>
+      </c>
       <c r="C629">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12211,6 +14098,9 @@
         <f t="shared" si="40"/>
         <v>629</v>
       </c>
+      <c r="B630" t="s">
+        <v>26</v>
+      </c>
       <c r="C630">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12229,6 +14119,9 @@
         <f t="shared" si="40"/>
         <v>630</v>
       </c>
+      <c r="B631" t="s">
+        <v>26</v>
+      </c>
       <c r="C631">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12247,6 +14140,9 @@
         <f t="shared" si="40"/>
         <v>631</v>
       </c>
+      <c r="B632" t="s">
+        <v>26</v>
+      </c>
       <c r="C632">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12265,6 +14161,9 @@
         <f t="shared" si="40"/>
         <v>632</v>
       </c>
+      <c r="B633" t="s">
+        <v>26</v>
+      </c>
       <c r="C633">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12283,6 +14182,9 @@
         <f t="shared" si="40"/>
         <v>633</v>
       </c>
+      <c r="B634" t="s">
+        <v>26</v>
+      </c>
       <c r="C634">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12301,6 +14203,9 @@
         <f t="shared" si="40"/>
         <v>634</v>
       </c>
+      <c r="B635" t="s">
+        <v>26</v>
+      </c>
       <c r="C635">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12319,6 +14224,9 @@
         <f t="shared" si="40"/>
         <v>635</v>
       </c>
+      <c r="B636" t="s">
+        <v>26</v>
+      </c>
       <c r="C636">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12337,6 +14245,9 @@
         <f t="shared" si="40"/>
         <v>636</v>
       </c>
+      <c r="B637" t="s">
+        <v>26</v>
+      </c>
       <c r="C637">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12355,6 +14266,9 @@
         <f t="shared" si="40"/>
         <v>637</v>
       </c>
+      <c r="B638" t="s">
+        <v>26</v>
+      </c>
       <c r="C638">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12373,6 +14287,9 @@
         <f t="shared" si="40"/>
         <v>638</v>
       </c>
+      <c r="B639" t="s">
+        <v>26</v>
+      </c>
       <c r="C639">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12391,6 +14308,9 @@
         <f t="shared" si="40"/>
         <v>639</v>
       </c>
+      <c r="B640" t="s">
+        <v>26</v>
+      </c>
       <c r="C640">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12409,6 +14329,9 @@
         <f t="shared" si="40"/>
         <v>640</v>
       </c>
+      <c r="B641" t="s">
+        <v>26</v>
+      </c>
       <c r="C641">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12427,6 +14350,9 @@
         <f t="shared" si="40"/>
         <v>641</v>
       </c>
+      <c r="B642" t="s">
+        <v>26</v>
+      </c>
       <c r="C642">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12445,6 +14371,9 @@
         <f t="shared" si="40"/>
         <v>642</v>
       </c>
+      <c r="B643" t="s">
+        <v>26</v>
+      </c>
       <c r="C643">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12463,12 +14392,15 @@
         <f t="shared" ref="A644:A707" si="44">A643+1</f>
         <v>643</v>
       </c>
+      <c r="B644" t="s">
+        <v>26</v>
+      </c>
       <c r="C644">
         <f t="shared" si="42"/>
         <v>112</v>
       </c>
       <c r="L644" t="str">
-        <f t="shared" ref="L644:L707" si="45">L643</f>
+        <f t="shared" ref="L644:L706" si="45">L643</f>
         <v>Blood (Minor)</v>
       </c>
       <c r="N644" t="str">
@@ -12481,6 +14413,9 @@
         <f t="shared" si="44"/>
         <v>644</v>
       </c>
+      <c r="B645" t="s">
+        <v>26</v>
+      </c>
       <c r="C645">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12499,6 +14434,9 @@
         <f t="shared" si="44"/>
         <v>645</v>
       </c>
+      <c r="B646" t="s">
+        <v>26</v>
+      </c>
       <c r="C646">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12517,6 +14455,9 @@
         <f t="shared" si="44"/>
         <v>646</v>
       </c>
+      <c r="B647" t="s">
+        <v>26</v>
+      </c>
       <c r="C647">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12535,6 +14476,9 @@
         <f t="shared" si="44"/>
         <v>647</v>
       </c>
+      <c r="B648" t="s">
+        <v>26</v>
+      </c>
       <c r="C648">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12553,6 +14497,9 @@
         <f t="shared" si="44"/>
         <v>648</v>
       </c>
+      <c r="B649" t="s">
+        <v>26</v>
+      </c>
       <c r="C649">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12571,6 +14518,9 @@
         <f t="shared" si="44"/>
         <v>649</v>
       </c>
+      <c r="B650" t="s">
+        <v>26</v>
+      </c>
       <c r="C650">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12589,6 +14539,9 @@
         <f t="shared" si="44"/>
         <v>650</v>
       </c>
+      <c r="B651" t="s">
+        <v>26</v>
+      </c>
       <c r="C651">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12607,6 +14560,9 @@
         <f t="shared" si="44"/>
         <v>651</v>
       </c>
+      <c r="B652" t="s">
+        <v>26</v>
+      </c>
       <c r="C652">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12625,6 +14581,9 @@
         <f t="shared" si="44"/>
         <v>652</v>
       </c>
+      <c r="B653" t="s">
+        <v>26</v>
+      </c>
       <c r="C653">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12643,6 +14602,9 @@
         <f t="shared" si="44"/>
         <v>653</v>
       </c>
+      <c r="B654" t="s">
+        <v>26</v>
+      </c>
       <c r="C654">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12661,6 +14623,9 @@
         <f t="shared" si="44"/>
         <v>654</v>
       </c>
+      <c r="B655" t="s">
+        <v>26</v>
+      </c>
       <c r="C655">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12679,6 +14644,9 @@
         <f t="shared" si="44"/>
         <v>655</v>
       </c>
+      <c r="B656" t="s">
+        <v>26</v>
+      </c>
       <c r="C656">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12697,6 +14665,9 @@
         <f t="shared" si="44"/>
         <v>656</v>
       </c>
+      <c r="B657" t="s">
+        <v>26</v>
+      </c>
       <c r="C657">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12715,6 +14686,9 @@
         <f t="shared" si="44"/>
         <v>657</v>
       </c>
+      <c r="B658" t="s">
+        <v>26</v>
+      </c>
       <c r="C658">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12733,6 +14707,9 @@
         <f t="shared" si="44"/>
         <v>658</v>
       </c>
+      <c r="B659" t="s">
+        <v>26</v>
+      </c>
       <c r="C659">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12751,6 +14728,9 @@
         <f t="shared" si="44"/>
         <v>659</v>
       </c>
+      <c r="B660" t="s">
+        <v>26</v>
+      </c>
       <c r="C660">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12769,6 +14749,9 @@
         <f t="shared" si="44"/>
         <v>660</v>
       </c>
+      <c r="B661" t="s">
+        <v>26</v>
+      </c>
       <c r="C661">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12787,6 +14770,9 @@
         <f t="shared" si="44"/>
         <v>661</v>
       </c>
+      <c r="B662" t="s">
+        <v>26</v>
+      </c>
       <c r="C662">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12805,6 +14791,9 @@
         <f t="shared" si="44"/>
         <v>662</v>
       </c>
+      <c r="B663" t="s">
+        <v>26</v>
+      </c>
       <c r="C663">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12823,6 +14812,9 @@
         <f t="shared" si="44"/>
         <v>663</v>
       </c>
+      <c r="B664" t="s">
+        <v>26</v>
+      </c>
       <c r="C664">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12841,6 +14833,9 @@
         <f t="shared" si="44"/>
         <v>664</v>
       </c>
+      <c r="B665" t="s">
+        <v>26</v>
+      </c>
       <c r="C665">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12859,6 +14854,9 @@
         <f t="shared" si="44"/>
         <v>665</v>
       </c>
+      <c r="B666" t="s">
+        <v>26</v>
+      </c>
       <c r="C666">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12877,6 +14875,9 @@
         <f t="shared" si="44"/>
         <v>666</v>
       </c>
+      <c r="B667" t="s">
+        <v>26</v>
+      </c>
       <c r="C667">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12895,6 +14896,9 @@
         <f t="shared" si="44"/>
         <v>667</v>
       </c>
+      <c r="B668" t="s">
+        <v>26</v>
+      </c>
       <c r="C668">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12913,6 +14917,9 @@
         <f t="shared" si="44"/>
         <v>668</v>
       </c>
+      <c r="B669" t="s">
+        <v>26</v>
+      </c>
       <c r="C669">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12931,6 +14938,9 @@
         <f t="shared" si="44"/>
         <v>669</v>
       </c>
+      <c r="B670" t="s">
+        <v>26</v>
+      </c>
       <c r="C670">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12975,6 +14985,9 @@
         <f t="shared" si="44"/>
         <v>670</v>
       </c>
+      <c r="B671" t="s">
+        <v>26</v>
+      </c>
       <c r="C671">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -12992,6 +15005,9 @@
         <f t="shared" si="44"/>
         <v>671</v>
       </c>
+      <c r="B672" t="s">
+        <v>26</v>
+      </c>
       <c r="C672">
         <f t="shared" si="42"/>
         <v>112</v>
@@ -13010,6 +15026,9 @@
         <f t="shared" si="44"/>
         <v>672</v>
       </c>
+      <c r="B673" t="s">
+        <v>26</v>
+      </c>
       <c r="C673">
         <f t="shared" ref="C673:C736" si="46">C672</f>
         <v>112</v>
@@ -13028,6 +15047,9 @@
         <f t="shared" si="44"/>
         <v>673</v>
       </c>
+      <c r="B674" t="s">
+        <v>26</v>
+      </c>
       <c r="C674">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13046,6 +15068,9 @@
         <f t="shared" si="44"/>
         <v>674</v>
       </c>
+      <c r="B675" t="s">
+        <v>26</v>
+      </c>
       <c r="C675">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13090,6 +15115,9 @@
         <f t="shared" si="44"/>
         <v>675</v>
       </c>
+      <c r="B676" t="s">
+        <v>26</v>
+      </c>
       <c r="C676">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13107,6 +15135,9 @@
         <f t="shared" si="44"/>
         <v>676</v>
       </c>
+      <c r="B677" t="s">
+        <v>26</v>
+      </c>
       <c r="C677">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13125,6 +15156,9 @@
         <f t="shared" si="44"/>
         <v>677</v>
       </c>
+      <c r="B678" t="s">
+        <v>26</v>
+      </c>
       <c r="C678">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13143,6 +15177,9 @@
         <f t="shared" si="44"/>
         <v>678</v>
       </c>
+      <c r="B679" t="s">
+        <v>26</v>
+      </c>
       <c r="C679">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13161,6 +15198,9 @@
         <f t="shared" si="44"/>
         <v>679</v>
       </c>
+      <c r="B680" t="s">
+        <v>26</v>
+      </c>
       <c r="C680">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13179,6 +15219,9 @@
         <f t="shared" si="44"/>
         <v>680</v>
       </c>
+      <c r="B681" t="s">
+        <v>26</v>
+      </c>
       <c r="C681">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13197,6 +15240,9 @@
         <f t="shared" si="44"/>
         <v>681</v>
       </c>
+      <c r="B682" t="s">
+        <v>26</v>
+      </c>
       <c r="C682">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13215,6 +15261,9 @@
         <f t="shared" si="44"/>
         <v>682</v>
       </c>
+      <c r="B683" t="s">
+        <v>26</v>
+      </c>
       <c r="C683">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13233,6 +15282,9 @@
         <f t="shared" si="44"/>
         <v>683</v>
       </c>
+      <c r="B684" t="s">
+        <v>26</v>
+      </c>
       <c r="C684">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13251,6 +15303,9 @@
         <f t="shared" si="44"/>
         <v>684</v>
       </c>
+      <c r="B685" t="s">
+        <v>26</v>
+      </c>
       <c r="C685">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13269,6 +15324,9 @@
         <f t="shared" si="44"/>
         <v>685</v>
       </c>
+      <c r="B686" t="s">
+        <v>26</v>
+      </c>
       <c r="C686">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13313,6 +15371,9 @@
         <f t="shared" si="44"/>
         <v>686</v>
       </c>
+      <c r="B687" t="s">
+        <v>26</v>
+      </c>
       <c r="C687">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13330,6 +15391,9 @@
         <f t="shared" si="44"/>
         <v>687</v>
       </c>
+      <c r="B688" t="s">
+        <v>26</v>
+      </c>
       <c r="C688">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13348,6 +15412,9 @@
         <f t="shared" si="44"/>
         <v>688</v>
       </c>
+      <c r="B689" t="s">
+        <v>26</v>
+      </c>
       <c r="C689">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13366,6 +15433,9 @@
         <f t="shared" si="44"/>
         <v>689</v>
       </c>
+      <c r="B690" t="s">
+        <v>26</v>
+      </c>
       <c r="C690">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13384,6 +15454,9 @@
         <f t="shared" si="44"/>
         <v>690</v>
       </c>
+      <c r="B691" t="s">
+        <v>26</v>
+      </c>
       <c r="C691">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13402,6 +15475,9 @@
         <f t="shared" si="44"/>
         <v>691</v>
       </c>
+      <c r="B692" t="s">
+        <v>26</v>
+      </c>
       <c r="C692">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13420,6 +15496,9 @@
         <f t="shared" si="44"/>
         <v>692</v>
       </c>
+      <c r="B693" t="s">
+        <v>26</v>
+      </c>
       <c r="C693">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13438,6 +15517,9 @@
         <f t="shared" si="44"/>
         <v>693</v>
       </c>
+      <c r="B694" t="s">
+        <v>26</v>
+      </c>
       <c r="C694">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13456,6 +15538,9 @@
         <f t="shared" si="44"/>
         <v>694</v>
       </c>
+      <c r="B695" t="s">
+        <v>26</v>
+      </c>
       <c r="C695">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13474,6 +15559,9 @@
         <f t="shared" si="44"/>
         <v>695</v>
       </c>
+      <c r="B696" t="s">
+        <v>26</v>
+      </c>
       <c r="C696">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13492,6 +15580,9 @@
         <f t="shared" si="44"/>
         <v>696</v>
       </c>
+      <c r="B697" t="s">
+        <v>26</v>
+      </c>
       <c r="C697">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13510,6 +15601,9 @@
         <f t="shared" si="44"/>
         <v>697</v>
       </c>
+      <c r="B698" t="s">
+        <v>26</v>
+      </c>
       <c r="C698">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13528,6 +15622,9 @@
         <f t="shared" si="44"/>
         <v>698</v>
       </c>
+      <c r="B699" t="s">
+        <v>26</v>
+      </c>
       <c r="C699">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13546,6 +15643,9 @@
         <f t="shared" si="44"/>
         <v>699</v>
       </c>
+      <c r="B700" t="s">
+        <v>26</v>
+      </c>
       <c r="C700">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13564,6 +15664,9 @@
         <f t="shared" si="44"/>
         <v>700</v>
       </c>
+      <c r="B701" t="s">
+        <v>26</v>
+      </c>
       <c r="C701">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13582,6 +15685,9 @@
         <f t="shared" si="44"/>
         <v>701</v>
       </c>
+      <c r="B702" t="s">
+        <v>26</v>
+      </c>
       <c r="C702">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13600,6 +15706,9 @@
         <f t="shared" si="44"/>
         <v>702</v>
       </c>
+      <c r="B703" t="s">
+        <v>26</v>
+      </c>
       <c r="C703">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13618,6 +15727,9 @@
         <f t="shared" si="44"/>
         <v>703</v>
       </c>
+      <c r="B704" t="s">
+        <v>26</v>
+      </c>
       <c r="C704">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13636,6 +15748,9 @@
         <f t="shared" si="44"/>
         <v>704</v>
       </c>
+      <c r="B705" t="s">
+        <v>26</v>
+      </c>
       <c r="C705">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13654,6 +15769,9 @@
         <f t="shared" si="44"/>
         <v>705</v>
       </c>
+      <c r="B706" t="s">
+        <v>26</v>
+      </c>
       <c r="C706">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13672,6 +15790,9 @@
         <f t="shared" si="44"/>
         <v>706</v>
       </c>
+      <c r="B707" t="s">
+        <v>26</v>
+      </c>
       <c r="C707">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13716,6 +15837,9 @@
         <f t="shared" ref="A708:A771" si="48">A707+1</f>
         <v>707</v>
       </c>
+      <c r="B708" t="s">
+        <v>26</v>
+      </c>
       <c r="C708">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13760,6 +15884,9 @@
         <f t="shared" si="48"/>
         <v>708</v>
       </c>
+      <c r="B709" t="s">
+        <v>26</v>
+      </c>
       <c r="C709">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13777,12 +15904,15 @@
         <f t="shared" si="48"/>
         <v>709</v>
       </c>
+      <c r="B710" t="s">
+        <v>26</v>
+      </c>
       <c r="C710">
         <f t="shared" si="46"/>
         <v>112</v>
       </c>
       <c r="L710" t="str">
-        <f t="shared" ref="L708:L771" si="49">L709</f>
+        <f t="shared" ref="L710:L771" si="49">L709</f>
         <v>Blood (Minor)</v>
       </c>
       <c r="N710" t="str">
@@ -13795,6 +15925,9 @@
         <f t="shared" si="48"/>
         <v>710</v>
       </c>
+      <c r="B711" t="s">
+        <v>26</v>
+      </c>
       <c r="C711">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13813,6 +15946,9 @@
         <f t="shared" si="48"/>
         <v>711</v>
       </c>
+      <c r="B712" t="s">
+        <v>26</v>
+      </c>
       <c r="C712">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13831,6 +15967,9 @@
         <f t="shared" si="48"/>
         <v>712</v>
       </c>
+      <c r="B713" t="s">
+        <v>26</v>
+      </c>
       <c r="C713">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13849,6 +15988,9 @@
         <f t="shared" si="48"/>
         <v>713</v>
       </c>
+      <c r="B714" t="s">
+        <v>26</v>
+      </c>
       <c r="C714">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13867,6 +16009,9 @@
         <f t="shared" si="48"/>
         <v>714</v>
       </c>
+      <c r="B715" t="s">
+        <v>26</v>
+      </c>
       <c r="C715">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13885,6 +16030,9 @@
         <f t="shared" si="48"/>
         <v>715</v>
       </c>
+      <c r="B716" t="s">
+        <v>26</v>
+      </c>
       <c r="C716">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13903,6 +16051,9 @@
         <f t="shared" si="48"/>
         <v>716</v>
       </c>
+      <c r="B717" t="s">
+        <v>26</v>
+      </c>
       <c r="C717">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13921,6 +16072,9 @@
         <f t="shared" si="48"/>
         <v>717</v>
       </c>
+      <c r="B718" t="s">
+        <v>26</v>
+      </c>
       <c r="C718">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13939,6 +16093,9 @@
         <f t="shared" si="48"/>
         <v>718</v>
       </c>
+      <c r="B719" t="s">
+        <v>26</v>
+      </c>
       <c r="C719">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13957,6 +16114,9 @@
         <f t="shared" si="48"/>
         <v>719</v>
       </c>
+      <c r="B720" t="s">
+        <v>26</v>
+      </c>
       <c r="C720">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13975,6 +16135,9 @@
         <f t="shared" si="48"/>
         <v>720</v>
       </c>
+      <c r="B721" t="s">
+        <v>26</v>
+      </c>
       <c r="C721">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -13993,6 +16156,9 @@
         <f t="shared" si="48"/>
         <v>721</v>
       </c>
+      <c r="B722" t="s">
+        <v>26</v>
+      </c>
       <c r="C722">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14011,6 +16177,9 @@
         <f t="shared" si="48"/>
         <v>722</v>
       </c>
+      <c r="B723" t="s">
+        <v>26</v>
+      </c>
       <c r="C723">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14055,6 +16224,9 @@
         <f t="shared" si="48"/>
         <v>723</v>
       </c>
+      <c r="B724" t="s">
+        <v>26</v>
+      </c>
       <c r="C724">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14072,6 +16244,9 @@
         <f t="shared" si="48"/>
         <v>724</v>
       </c>
+      <c r="B725" t="s">
+        <v>26</v>
+      </c>
       <c r="C725">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14090,6 +16265,9 @@
         <f t="shared" si="48"/>
         <v>725</v>
       </c>
+      <c r="B726" t="s">
+        <v>26</v>
+      </c>
       <c r="C726">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14108,6 +16286,9 @@
         <f t="shared" si="48"/>
         <v>726</v>
       </c>
+      <c r="B727" t="s">
+        <v>26</v>
+      </c>
       <c r="C727">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14126,6 +16307,9 @@
         <f t="shared" si="48"/>
         <v>727</v>
       </c>
+      <c r="B728" t="s">
+        <v>26</v>
+      </c>
       <c r="C728">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14144,6 +16328,9 @@
         <f t="shared" si="48"/>
         <v>728</v>
       </c>
+      <c r="B729" t="s">
+        <v>26</v>
+      </c>
       <c r="C729">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14162,6 +16349,9 @@
         <f t="shared" si="48"/>
         <v>729</v>
       </c>
+      <c r="B730" t="s">
+        <v>26</v>
+      </c>
       <c r="C730">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14180,6 +16370,9 @@
         <f t="shared" si="48"/>
         <v>730</v>
       </c>
+      <c r="B731" t="s">
+        <v>26</v>
+      </c>
       <c r="C731">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14198,6 +16391,9 @@
         <f t="shared" si="48"/>
         <v>731</v>
       </c>
+      <c r="B732" t="s">
+        <v>26</v>
+      </c>
       <c r="C732">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14216,6 +16412,9 @@
         <f t="shared" si="48"/>
         <v>732</v>
       </c>
+      <c r="B733" t="s">
+        <v>26</v>
+      </c>
       <c r="C733">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14234,6 +16433,9 @@
         <f t="shared" si="48"/>
         <v>733</v>
       </c>
+      <c r="B734" t="s">
+        <v>26</v>
+      </c>
       <c r="C734">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14252,6 +16454,9 @@
         <f t="shared" si="48"/>
         <v>734</v>
       </c>
+      <c r="B735" t="s">
+        <v>26</v>
+      </c>
       <c r="C735">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14270,6 +16475,9 @@
         <f t="shared" si="48"/>
         <v>735</v>
       </c>
+      <c r="B736" t="s">
+        <v>26</v>
+      </c>
       <c r="C736">
         <f t="shared" si="46"/>
         <v>112</v>
@@ -14288,6 +16496,9 @@
         <f t="shared" si="48"/>
         <v>736</v>
       </c>
+      <c r="B737" t="s">
+        <v>26</v>
+      </c>
       <c r="C737">
         <f t="shared" ref="C737:C769" si="50">C736</f>
         <v>112</v>
@@ -14306,6 +16517,9 @@
         <f t="shared" si="48"/>
         <v>737</v>
       </c>
+      <c r="B738" t="s">
+        <v>26</v>
+      </c>
       <c r="C738">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14324,6 +16538,9 @@
         <f t="shared" si="48"/>
         <v>738</v>
       </c>
+      <c r="B739" t="s">
+        <v>26</v>
+      </c>
       <c r="C739">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14342,6 +16559,9 @@
         <f t="shared" si="48"/>
         <v>739</v>
       </c>
+      <c r="B740" t="s">
+        <v>26</v>
+      </c>
       <c r="C740">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14360,6 +16580,9 @@
         <f t="shared" si="48"/>
         <v>740</v>
       </c>
+      <c r="B741" t="s">
+        <v>26</v>
+      </c>
       <c r="C741">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14378,6 +16601,9 @@
         <f t="shared" si="48"/>
         <v>741</v>
       </c>
+      <c r="B742" t="s">
+        <v>26</v>
+      </c>
       <c r="C742">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14396,6 +16622,9 @@
         <f t="shared" si="48"/>
         <v>742</v>
       </c>
+      <c r="B743" t="s">
+        <v>26</v>
+      </c>
       <c r="C743">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14414,6 +16643,9 @@
         <f t="shared" si="48"/>
         <v>743</v>
       </c>
+      <c r="B744" t="s">
+        <v>26</v>
+      </c>
       <c r="C744">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14432,6 +16664,9 @@
         <f t="shared" si="48"/>
         <v>744</v>
       </c>
+      <c r="B745" t="s">
+        <v>26</v>
+      </c>
       <c r="C745">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14450,6 +16685,9 @@
         <f t="shared" si="48"/>
         <v>745</v>
       </c>
+      <c r="B746" t="s">
+        <v>26</v>
+      </c>
       <c r="C746">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14468,6 +16706,9 @@
         <f t="shared" si="48"/>
         <v>746</v>
       </c>
+      <c r="B747" t="s">
+        <v>26</v>
+      </c>
       <c r="C747">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14486,6 +16727,9 @@
         <f t="shared" si="48"/>
         <v>747</v>
       </c>
+      <c r="B748" t="s">
+        <v>26</v>
+      </c>
       <c r="C748">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14504,6 +16748,9 @@
         <f t="shared" si="48"/>
         <v>748</v>
       </c>
+      <c r="B749" t="s">
+        <v>26</v>
+      </c>
       <c r="C749">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14522,6 +16769,9 @@
         <f t="shared" si="48"/>
         <v>749</v>
       </c>
+      <c r="B750" t="s">
+        <v>26</v>
+      </c>
       <c r="C750">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14540,6 +16790,9 @@
         <f t="shared" si="48"/>
         <v>750</v>
       </c>
+      <c r="B751" t="s">
+        <v>26</v>
+      </c>
       <c r="C751">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14558,6 +16811,9 @@
         <f t="shared" si="48"/>
         <v>751</v>
       </c>
+      <c r="B752" t="s">
+        <v>26</v>
+      </c>
       <c r="C752">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14576,6 +16832,9 @@
         <f t="shared" si="48"/>
         <v>752</v>
       </c>
+      <c r="B753" t="s">
+        <v>26</v>
+      </c>
       <c r="C753">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14594,6 +16853,9 @@
         <f t="shared" si="48"/>
         <v>753</v>
       </c>
+      <c r="B754" t="s">
+        <v>26</v>
+      </c>
       <c r="C754">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14612,6 +16874,9 @@
         <f t="shared" si="48"/>
         <v>754</v>
       </c>
+      <c r="B755" t="s">
+        <v>26</v>
+      </c>
       <c r="C755">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14630,6 +16895,9 @@
         <f t="shared" si="48"/>
         <v>755</v>
       </c>
+      <c r="B756" t="s">
+        <v>26</v>
+      </c>
       <c r="C756">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14648,6 +16916,9 @@
         <f t="shared" si="48"/>
         <v>756</v>
       </c>
+      <c r="B757" t="s">
+        <v>26</v>
+      </c>
       <c r="C757">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14666,6 +16937,9 @@
         <f t="shared" si="48"/>
         <v>757</v>
       </c>
+      <c r="B758" t="s">
+        <v>26</v>
+      </c>
       <c r="C758">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14684,6 +16958,9 @@
         <f t="shared" si="48"/>
         <v>758</v>
       </c>
+      <c r="B759" t="s">
+        <v>26</v>
+      </c>
       <c r="C759">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14702,6 +16979,9 @@
         <f t="shared" si="48"/>
         <v>759</v>
       </c>
+      <c r="B760" t="s">
+        <v>26</v>
+      </c>
       <c r="C760">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14720,6 +17000,9 @@
         <f t="shared" si="48"/>
         <v>760</v>
       </c>
+      <c r="B761" t="s">
+        <v>26</v>
+      </c>
       <c r="C761">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14738,6 +17021,9 @@
         <f t="shared" si="48"/>
         <v>761</v>
       </c>
+      <c r="B762" t="s">
+        <v>26</v>
+      </c>
       <c r="C762">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14756,6 +17042,9 @@
         <f t="shared" si="48"/>
         <v>762</v>
       </c>
+      <c r="B763" t="s">
+        <v>26</v>
+      </c>
       <c r="C763">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14774,6 +17063,9 @@
         <f t="shared" si="48"/>
         <v>763</v>
       </c>
+      <c r="B764" t="s">
+        <v>26</v>
+      </c>
       <c r="C764">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14792,6 +17084,9 @@
         <f t="shared" si="48"/>
         <v>764</v>
       </c>
+      <c r="B765" t="s">
+        <v>26</v>
+      </c>
       <c r="C765">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14810,6 +17105,9 @@
         <f t="shared" si="48"/>
         <v>765</v>
       </c>
+      <c r="B766" t="s">
+        <v>26</v>
+      </c>
       <c r="C766">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14828,6 +17126,9 @@
         <f t="shared" si="48"/>
         <v>766</v>
       </c>
+      <c r="B767" t="s">
+        <v>26</v>
+      </c>
       <c r="C767">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14846,6 +17147,9 @@
         <f t="shared" si="48"/>
         <v>767</v>
       </c>
+      <c r="B768" t="s">
+        <v>26</v>
+      </c>
       <c r="C768">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14864,6 +17168,9 @@
         <f t="shared" si="48"/>
         <v>768</v>
       </c>
+      <c r="B769" t="s">
+        <v>26</v>
+      </c>
       <c r="C769">
         <f t="shared" si="50"/>
         <v>112</v>
@@ -14882,6 +17189,9 @@
         <f t="shared" si="48"/>
         <v>769</v>
       </c>
+      <c r="B770" t="s">
+        <v>26</v>
+      </c>
       <c r="C770">
         <v>113</v>
       </c>
@@ -14898,6 +17208,9 @@
         <f t="shared" si="48"/>
         <v>770</v>
       </c>
+      <c r="B771" t="s">
+        <v>26</v>
+      </c>
       <c r="C771">
         <f>C770</f>
         <v>113</v>
@@ -14916,6 +17229,9 @@
         <f t="shared" ref="A772:A835" si="52">A771+1</f>
         <v>771</v>
       </c>
+      <c r="B772" t="s">
+        <v>26</v>
+      </c>
       <c r="C772">
         <f t="shared" ref="C772:C835" si="53">C771</f>
         <v>113</v>
@@ -14934,6 +17250,9 @@
         <f t="shared" si="52"/>
         <v>772</v>
       </c>
+      <c r="B773" t="s">
+        <v>26</v>
+      </c>
       <c r="C773">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -14952,6 +17271,9 @@
         <f t="shared" si="52"/>
         <v>773</v>
       </c>
+      <c r="B774" t="s">
+        <v>26</v>
+      </c>
       <c r="C774">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -14970,6 +17292,9 @@
         <f t="shared" si="52"/>
         <v>774</v>
       </c>
+      <c r="B775" t="s">
+        <v>26</v>
+      </c>
       <c r="C775">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -14988,6 +17313,9 @@
         <f t="shared" si="52"/>
         <v>775</v>
       </c>
+      <c r="B776" t="s">
+        <v>26</v>
+      </c>
       <c r="C776">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15006,6 +17334,9 @@
         <f t="shared" si="52"/>
         <v>776</v>
       </c>
+      <c r="B777" t="s">
+        <v>26</v>
+      </c>
       <c r="C777">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15024,6 +17355,9 @@
         <f t="shared" si="52"/>
         <v>777</v>
       </c>
+      <c r="B778" t="s">
+        <v>26</v>
+      </c>
       <c r="C778">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15042,6 +17376,9 @@
         <f t="shared" si="52"/>
         <v>778</v>
       </c>
+      <c r="B779" t="s">
+        <v>26</v>
+      </c>
       <c r="C779">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15060,6 +17397,9 @@
         <f t="shared" si="52"/>
         <v>779</v>
       </c>
+      <c r="B780" t="s">
+        <v>26</v>
+      </c>
       <c r="C780">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15078,6 +17418,9 @@
         <f t="shared" si="52"/>
         <v>780</v>
       </c>
+      <c r="B781" t="s">
+        <v>26</v>
+      </c>
       <c r="C781">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15096,6 +17439,9 @@
         <f t="shared" si="52"/>
         <v>781</v>
       </c>
+      <c r="B782" t="s">
+        <v>26</v>
+      </c>
       <c r="C782">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15114,6 +17460,9 @@
         <f t="shared" si="52"/>
         <v>782</v>
       </c>
+      <c r="B783" t="s">
+        <v>26</v>
+      </c>
       <c r="C783">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15132,6 +17481,9 @@
         <f t="shared" si="52"/>
         <v>783</v>
       </c>
+      <c r="B784" t="s">
+        <v>26</v>
+      </c>
       <c r="C784">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15150,6 +17502,9 @@
         <f t="shared" si="52"/>
         <v>784</v>
       </c>
+      <c r="B785" t="s">
+        <v>26</v>
+      </c>
       <c r="C785">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15168,6 +17523,9 @@
         <f t="shared" si="52"/>
         <v>785</v>
       </c>
+      <c r="B786" t="s">
+        <v>26</v>
+      </c>
       <c r="C786">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15186,6 +17544,9 @@
         <f t="shared" si="52"/>
         <v>786</v>
       </c>
+      <c r="B787" t="s">
+        <v>26</v>
+      </c>
       <c r="C787">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15204,6 +17565,9 @@
         <f t="shared" si="52"/>
         <v>787</v>
       </c>
+      <c r="B788" t="s">
+        <v>26</v>
+      </c>
       <c r="C788">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15222,6 +17586,9 @@
         <f t="shared" si="52"/>
         <v>788</v>
       </c>
+      <c r="B789" t="s">
+        <v>26</v>
+      </c>
       <c r="C789">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15240,6 +17607,9 @@
         <f t="shared" si="52"/>
         <v>789</v>
       </c>
+      <c r="B790" t="s">
+        <v>26</v>
+      </c>
       <c r="C790">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15258,6 +17628,9 @@
         <f t="shared" si="52"/>
         <v>790</v>
       </c>
+      <c r="B791" t="s">
+        <v>26</v>
+      </c>
       <c r="C791">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15302,6 +17675,9 @@
         <f t="shared" si="52"/>
         <v>791</v>
       </c>
+      <c r="B792" t="s">
+        <v>26</v>
+      </c>
       <c r="C792">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15346,6 +17722,9 @@
         <f t="shared" si="52"/>
         <v>792</v>
       </c>
+      <c r="B793" t="s">
+        <v>26</v>
+      </c>
       <c r="C793">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15363,6 +17742,9 @@
         <f t="shared" si="52"/>
         <v>793</v>
       </c>
+      <c r="B794" t="s">
+        <v>26</v>
+      </c>
       <c r="C794">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15381,6 +17763,9 @@
         <f t="shared" si="52"/>
         <v>794</v>
       </c>
+      <c r="B795" t="s">
+        <v>26</v>
+      </c>
       <c r="C795">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15399,6 +17784,9 @@
         <f t="shared" si="52"/>
         <v>795</v>
       </c>
+      <c r="B796" t="s">
+        <v>26</v>
+      </c>
       <c r="C796">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15417,6 +17805,9 @@
         <f t="shared" si="52"/>
         <v>796</v>
       </c>
+      <c r="B797" t="s">
+        <v>26</v>
+      </c>
       <c r="C797">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15435,6 +17826,9 @@
         <f t="shared" si="52"/>
         <v>797</v>
       </c>
+      <c r="B798" t="s">
+        <v>26</v>
+      </c>
       <c r="C798">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15453,6 +17847,9 @@
         <f t="shared" si="52"/>
         <v>798</v>
       </c>
+      <c r="B799" t="s">
+        <v>26</v>
+      </c>
       <c r="C799">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15471,6 +17868,9 @@
         <f t="shared" si="52"/>
         <v>799</v>
       </c>
+      <c r="B800" t="s">
+        <v>26</v>
+      </c>
       <c r="C800">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15489,6 +17889,9 @@
         <f t="shared" si="52"/>
         <v>800</v>
       </c>
+      <c r="B801" t="s">
+        <v>26</v>
+      </c>
       <c r="C801">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15507,6 +17910,9 @@
         <f t="shared" si="52"/>
         <v>801</v>
       </c>
+      <c r="B802" t="s">
+        <v>26</v>
+      </c>
       <c r="C802">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15525,6 +17931,9 @@
         <f t="shared" si="52"/>
         <v>802</v>
       </c>
+      <c r="B803" t="s">
+        <v>26</v>
+      </c>
       <c r="C803">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15543,6 +17952,9 @@
         <f t="shared" si="52"/>
         <v>803</v>
       </c>
+      <c r="B804" t="s">
+        <v>26</v>
+      </c>
       <c r="C804">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15561,6 +17973,9 @@
         <f t="shared" si="52"/>
         <v>804</v>
       </c>
+      <c r="B805" t="s">
+        <v>26</v>
+      </c>
       <c r="C805">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15579,6 +17994,9 @@
         <f t="shared" si="52"/>
         <v>805</v>
       </c>
+      <c r="B806" t="s">
+        <v>26</v>
+      </c>
       <c r="C806">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15597,6 +18015,9 @@
         <f t="shared" si="52"/>
         <v>806</v>
       </c>
+      <c r="B807" t="s">
+        <v>26</v>
+      </c>
       <c r="C807">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15615,6 +18036,9 @@
         <f t="shared" si="52"/>
         <v>807</v>
       </c>
+      <c r="B808" t="s">
+        <v>26</v>
+      </c>
       <c r="C808">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15633,6 +18057,9 @@
         <f t="shared" si="52"/>
         <v>808</v>
       </c>
+      <c r="B809" t="s">
+        <v>26</v>
+      </c>
       <c r="C809">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15651,6 +18078,9 @@
         <f t="shared" si="52"/>
         <v>809</v>
       </c>
+      <c r="B810" t="s">
+        <v>26</v>
+      </c>
       <c r="C810">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15669,6 +18099,9 @@
         <f t="shared" si="52"/>
         <v>810</v>
       </c>
+      <c r="B811" t="s">
+        <v>26</v>
+      </c>
       <c r="C811">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15687,6 +18120,9 @@
         <f t="shared" si="52"/>
         <v>811</v>
       </c>
+      <c r="B812" t="s">
+        <v>26</v>
+      </c>
       <c r="C812">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15705,6 +18141,9 @@
         <f t="shared" si="52"/>
         <v>812</v>
       </c>
+      <c r="B813" t="s">
+        <v>26</v>
+      </c>
       <c r="C813">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15723,6 +18162,9 @@
         <f t="shared" si="52"/>
         <v>813</v>
       </c>
+      <c r="B814" t="s">
+        <v>26</v>
+      </c>
       <c r="C814">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15741,6 +18183,9 @@
         <f t="shared" si="52"/>
         <v>814</v>
       </c>
+      <c r="B815" t="s">
+        <v>26</v>
+      </c>
       <c r="C815">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15759,6 +18204,9 @@
         <f t="shared" si="52"/>
         <v>815</v>
       </c>
+      <c r="B816" t="s">
+        <v>26</v>
+      </c>
       <c r="C816">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15777,6 +18225,9 @@
         <f t="shared" si="52"/>
         <v>816</v>
       </c>
+      <c r="B817" t="s">
+        <v>26</v>
+      </c>
       <c r="C817">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15795,6 +18246,9 @@
         <f t="shared" si="52"/>
         <v>817</v>
       </c>
+      <c r="B818" t="s">
+        <v>26</v>
+      </c>
       <c r="C818">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15813,6 +18267,9 @@
         <f t="shared" si="52"/>
         <v>818</v>
       </c>
+      <c r="B819" t="s">
+        <v>26</v>
+      </c>
       <c r="C819">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15831,6 +18288,9 @@
         <f t="shared" si="52"/>
         <v>819</v>
       </c>
+      <c r="B820" t="s">
+        <v>26</v>
+      </c>
       <c r="C820">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15849,6 +18309,9 @@
         <f t="shared" si="52"/>
         <v>820</v>
       </c>
+      <c r="B821" t="s">
+        <v>26</v>
+      </c>
       <c r="C821">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15867,6 +18330,9 @@
         <f t="shared" si="52"/>
         <v>821</v>
       </c>
+      <c r="B822" t="s">
+        <v>26</v>
+      </c>
       <c r="C822">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15885,6 +18351,9 @@
         <f t="shared" si="52"/>
         <v>822</v>
       </c>
+      <c r="B823" t="s">
+        <v>26</v>
+      </c>
       <c r="C823">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15903,6 +18372,9 @@
         <f t="shared" si="52"/>
         <v>823</v>
       </c>
+      <c r="B824" t="s">
+        <v>26</v>
+      </c>
       <c r="C824">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15921,6 +18393,9 @@
         <f t="shared" si="52"/>
         <v>824</v>
       </c>
+      <c r="B825" t="s">
+        <v>26</v>
+      </c>
       <c r="C825">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15939,6 +18414,9 @@
         <f t="shared" si="52"/>
         <v>825</v>
       </c>
+      <c r="B826" t="s">
+        <v>26</v>
+      </c>
       <c r="C826">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15957,6 +18435,9 @@
         <f t="shared" si="52"/>
         <v>826</v>
       </c>
+      <c r="B827" t="s">
+        <v>26</v>
+      </c>
       <c r="C827">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15975,6 +18456,9 @@
         <f t="shared" si="52"/>
         <v>827</v>
       </c>
+      <c r="B828" t="s">
+        <v>26</v>
+      </c>
       <c r="C828">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -15993,6 +18477,9 @@
         <f t="shared" si="52"/>
         <v>828</v>
       </c>
+      <c r="B829" t="s">
+        <v>26</v>
+      </c>
       <c r="C829">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -16011,6 +18498,9 @@
         <f t="shared" si="52"/>
         <v>829</v>
       </c>
+      <c r="B830" t="s">
+        <v>26</v>
+      </c>
       <c r="C830">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -16029,6 +18519,9 @@
         <f t="shared" si="52"/>
         <v>830</v>
       </c>
+      <c r="B831" t="s">
+        <v>26</v>
+      </c>
       <c r="C831">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -16047,6 +18540,9 @@
         <f t="shared" si="52"/>
         <v>831</v>
       </c>
+      <c r="B832" t="s">
+        <v>26</v>
+      </c>
       <c r="C832">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -16065,6 +18561,9 @@
         <f t="shared" si="52"/>
         <v>832</v>
       </c>
+      <c r="B833" t="s">
+        <v>26</v>
+      </c>
       <c r="C833">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -16083,6 +18582,9 @@
         <f t="shared" si="52"/>
         <v>833</v>
       </c>
+      <c r="B834" t="s">
+        <v>26</v>
+      </c>
       <c r="C834">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -16101,6 +18603,9 @@
         <f t="shared" si="52"/>
         <v>834</v>
       </c>
+      <c r="B835" t="s">
+        <v>26</v>
+      </c>
       <c r="C835">
         <f t="shared" si="53"/>
         <v>113</v>
@@ -16119,6 +18624,9 @@
         <f t="shared" ref="A836:A899" si="56">A835+1</f>
         <v>835</v>
       </c>
+      <c r="B836" t="s">
+        <v>26</v>
+      </c>
       <c r="C836">
         <f t="shared" ref="C836:C899" si="57">C835</f>
         <v>113</v>
@@ -16137,6 +18645,9 @@
         <f t="shared" si="56"/>
         <v>836</v>
       </c>
+      <c r="B837" t="s">
+        <v>26</v>
+      </c>
       <c r="C837">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16155,6 +18666,9 @@
         <f t="shared" si="56"/>
         <v>837</v>
       </c>
+      <c r="B838" t="s">
+        <v>26</v>
+      </c>
       <c r="C838">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16173,6 +18687,9 @@
         <f t="shared" si="56"/>
         <v>838</v>
       </c>
+      <c r="B839" t="s">
+        <v>26</v>
+      </c>
       <c r="C839">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16191,6 +18708,9 @@
         <f t="shared" si="56"/>
         <v>839</v>
       </c>
+      <c r="B840" t="s">
+        <v>26</v>
+      </c>
       <c r="C840">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16209,6 +18729,9 @@
         <f t="shared" si="56"/>
         <v>840</v>
       </c>
+      <c r="B841" t="s">
+        <v>26</v>
+      </c>
       <c r="C841">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16227,6 +18750,9 @@
         <f t="shared" si="56"/>
         <v>841</v>
       </c>
+      <c r="B842" t="s">
+        <v>26</v>
+      </c>
       <c r="C842">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16245,6 +18771,9 @@
         <f t="shared" si="56"/>
         <v>842</v>
       </c>
+      <c r="B843" t="s">
+        <v>26</v>
+      </c>
       <c r="C843">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16263,6 +18792,9 @@
         <f t="shared" si="56"/>
         <v>843</v>
       </c>
+      <c r="B844" t="s">
+        <v>26</v>
+      </c>
       <c r="C844">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16281,6 +18813,9 @@
         <f t="shared" si="56"/>
         <v>844</v>
       </c>
+      <c r="B845" t="s">
+        <v>26</v>
+      </c>
       <c r="C845">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16325,6 +18860,9 @@
         <f t="shared" si="56"/>
         <v>845</v>
       </c>
+      <c r="B846" t="s">
+        <v>26</v>
+      </c>
       <c r="C846">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16369,6 +18907,9 @@
         <f t="shared" si="56"/>
         <v>846</v>
       </c>
+      <c r="B847" t="s">
+        <v>26</v>
+      </c>
       <c r="C847">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16413,6 +18954,9 @@
         <f t="shared" si="56"/>
         <v>847</v>
       </c>
+      <c r="B848" t="s">
+        <v>26</v>
+      </c>
       <c r="C848">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16457,6 +19001,9 @@
         <f t="shared" si="56"/>
         <v>848</v>
       </c>
+      <c r="B849" t="s">
+        <v>26</v>
+      </c>
       <c r="C849">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16501,6 +19048,9 @@
         <f t="shared" si="56"/>
         <v>849</v>
       </c>
+      <c r="B850" t="s">
+        <v>26</v>
+      </c>
       <c r="C850">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16545,6 +19095,9 @@
         <f t="shared" si="56"/>
         <v>850</v>
       </c>
+      <c r="B851" t="s">
+        <v>26</v>
+      </c>
       <c r="C851">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16589,6 +19142,9 @@
         <f t="shared" si="56"/>
         <v>851</v>
       </c>
+      <c r="B852" t="s">
+        <v>26</v>
+      </c>
       <c r="C852">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16633,6 +19189,9 @@
         <f t="shared" si="56"/>
         <v>852</v>
       </c>
+      <c r="B853" t="s">
+        <v>26</v>
+      </c>
       <c r="C853">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16677,6 +19236,9 @@
         <f t="shared" si="56"/>
         <v>853</v>
       </c>
+      <c r="B854" t="s">
+        <v>26</v>
+      </c>
       <c r="C854">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16721,6 +19283,9 @@
         <f t="shared" si="56"/>
         <v>854</v>
       </c>
+      <c r="B855" t="s">
+        <v>26</v>
+      </c>
       <c r="C855">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16765,6 +19330,9 @@
         <f t="shared" si="56"/>
         <v>855</v>
       </c>
+      <c r="B856" t="s">
+        <v>26</v>
+      </c>
       <c r="C856">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16809,6 +19377,9 @@
         <f t="shared" si="56"/>
         <v>856</v>
       </c>
+      <c r="B857" t="s">
+        <v>26</v>
+      </c>
       <c r="C857">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16853,6 +19424,9 @@
         <f t="shared" si="56"/>
         <v>857</v>
       </c>
+      <c r="B858" t="s">
+        <v>26</v>
+      </c>
       <c r="C858">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16897,6 +19471,9 @@
         <f t="shared" si="56"/>
         <v>858</v>
       </c>
+      <c r="B859" t="s">
+        <v>26</v>
+      </c>
       <c r="C859">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16941,6 +19518,9 @@
         <f t="shared" si="56"/>
         <v>859</v>
       </c>
+      <c r="B860" t="s">
+        <v>26</v>
+      </c>
       <c r="C860">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -16985,6 +19565,9 @@
         <f t="shared" si="56"/>
         <v>860</v>
       </c>
+      <c r="B861" t="s">
+        <v>26</v>
+      </c>
       <c r="C861">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17029,6 +19612,9 @@
         <f t="shared" si="56"/>
         <v>861</v>
       </c>
+      <c r="B862" t="s">
+        <v>26</v>
+      </c>
       <c r="C862">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17073,6 +19659,9 @@
         <f t="shared" si="56"/>
         <v>862</v>
       </c>
+      <c r="B863" t="s">
+        <v>26</v>
+      </c>
       <c r="C863">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17117,6 +19706,9 @@
         <f t="shared" si="56"/>
         <v>863</v>
       </c>
+      <c r="B864" t="s">
+        <v>26</v>
+      </c>
       <c r="C864">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17161,6 +19753,9 @@
         <f t="shared" si="56"/>
         <v>864</v>
       </c>
+      <c r="B865" t="s">
+        <v>26</v>
+      </c>
       <c r="C865">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17205,6 +19800,9 @@
         <f t="shared" si="56"/>
         <v>865</v>
       </c>
+      <c r="B866" t="s">
+        <v>26</v>
+      </c>
       <c r="C866">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17249,6 +19847,9 @@
         <f t="shared" si="56"/>
         <v>866</v>
       </c>
+      <c r="B867" t="s">
+        <v>26</v>
+      </c>
       <c r="C867">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17293,6 +19894,9 @@
         <f t="shared" si="56"/>
         <v>867</v>
       </c>
+      <c r="B868" t="s">
+        <v>26</v>
+      </c>
       <c r="C868">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17337,6 +19941,9 @@
         <f t="shared" si="56"/>
         <v>868</v>
       </c>
+      <c r="B869" t="s">
+        <v>26</v>
+      </c>
       <c r="C869">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17381,6 +19988,9 @@
         <f t="shared" si="56"/>
         <v>869</v>
       </c>
+      <c r="B870" t="s">
+        <v>26</v>
+      </c>
       <c r="C870">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17425,6 +20035,9 @@
         <f t="shared" si="56"/>
         <v>870</v>
       </c>
+      <c r="B871" t="s">
+        <v>26</v>
+      </c>
       <c r="C871">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17469,6 +20082,9 @@
         <f t="shared" si="56"/>
         <v>871</v>
       </c>
+      <c r="B872" t="s">
+        <v>26</v>
+      </c>
       <c r="C872">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17513,6 +20129,9 @@
         <f t="shared" si="56"/>
         <v>872</v>
       </c>
+      <c r="B873" t="s">
+        <v>26</v>
+      </c>
       <c r="C873">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17557,6 +20176,9 @@
         <f t="shared" si="56"/>
         <v>873</v>
       </c>
+      <c r="B874" t="s">
+        <v>26</v>
+      </c>
       <c r="C874">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17574,6 +20196,9 @@
         <f t="shared" si="56"/>
         <v>874</v>
       </c>
+      <c r="B875" t="s">
+        <v>26</v>
+      </c>
       <c r="C875">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17592,6 +20217,9 @@
         <f t="shared" si="56"/>
         <v>875</v>
       </c>
+      <c r="B876" t="s">
+        <v>26</v>
+      </c>
       <c r="C876">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17610,6 +20238,9 @@
         <f t="shared" si="56"/>
         <v>876</v>
       </c>
+      <c r="B877" t="s">
+        <v>26</v>
+      </c>
       <c r="C877">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17628,6 +20259,9 @@
         <f t="shared" si="56"/>
         <v>877</v>
       </c>
+      <c r="B878" t="s">
+        <v>26</v>
+      </c>
       <c r="C878">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17646,6 +20280,9 @@
         <f t="shared" si="56"/>
         <v>878</v>
       </c>
+      <c r="B879" t="s">
+        <v>26</v>
+      </c>
       <c r="C879">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17664,6 +20301,9 @@
         <f t="shared" si="56"/>
         <v>879</v>
       </c>
+      <c r="B880" t="s">
+        <v>26</v>
+      </c>
       <c r="C880">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17682,6 +20322,9 @@
         <f t="shared" si="56"/>
         <v>880</v>
       </c>
+      <c r="B881" t="s">
+        <v>26</v>
+      </c>
       <c r="C881">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17700,6 +20343,9 @@
         <f t="shared" si="56"/>
         <v>881</v>
       </c>
+      <c r="B882" t="s">
+        <v>26</v>
+      </c>
       <c r="C882">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17718,6 +20364,9 @@
         <f t="shared" si="56"/>
         <v>882</v>
       </c>
+      <c r="B883" t="s">
+        <v>26</v>
+      </c>
       <c r="C883">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17736,6 +20385,9 @@
         <f t="shared" si="56"/>
         <v>883</v>
       </c>
+      <c r="B884" t="s">
+        <v>26</v>
+      </c>
       <c r="C884">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17754,6 +20406,9 @@
         <f t="shared" si="56"/>
         <v>884</v>
       </c>
+      <c r="B885" t="s">
+        <v>26</v>
+      </c>
       <c r="C885">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17772,6 +20427,9 @@
         <f t="shared" si="56"/>
         <v>885</v>
       </c>
+      <c r="B886" t="s">
+        <v>26</v>
+      </c>
       <c r="C886">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17790,6 +20448,9 @@
         <f t="shared" si="56"/>
         <v>886</v>
       </c>
+      <c r="B887" t="s">
+        <v>26</v>
+      </c>
       <c r="C887">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17808,6 +20469,9 @@
         <f t="shared" si="56"/>
         <v>887</v>
       </c>
+      <c r="B888" t="s">
+        <v>26</v>
+      </c>
       <c r="C888">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17826,6 +20490,9 @@
         <f t="shared" si="56"/>
         <v>888</v>
       </c>
+      <c r="B889" t="s">
+        <v>26</v>
+      </c>
       <c r="C889">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17844,6 +20511,9 @@
         <f t="shared" si="56"/>
         <v>889</v>
       </c>
+      <c r="B890" t="s">
+        <v>26</v>
+      </c>
       <c r="C890">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17862,6 +20532,9 @@
         <f t="shared" si="56"/>
         <v>890</v>
       </c>
+      <c r="B891" t="s">
+        <v>26</v>
+      </c>
       <c r="C891">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17880,6 +20553,9 @@
         <f t="shared" si="56"/>
         <v>891</v>
       </c>
+      <c r="B892" t="s">
+        <v>26</v>
+      </c>
       <c r="C892">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17898,6 +20574,9 @@
         <f t="shared" si="56"/>
         <v>892</v>
       </c>
+      <c r="B893" t="s">
+        <v>26</v>
+      </c>
       <c r="C893">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17916,6 +20595,9 @@
         <f t="shared" si="56"/>
         <v>893</v>
       </c>
+      <c r="B894" t="s">
+        <v>26</v>
+      </c>
       <c r="C894">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17934,6 +20616,9 @@
         <f t="shared" si="56"/>
         <v>894</v>
       </c>
+      <c r="B895" t="s">
+        <v>26</v>
+      </c>
       <c r="C895">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17952,6 +20637,9 @@
         <f t="shared" si="56"/>
         <v>895</v>
       </c>
+      <c r="B896" t="s">
+        <v>26</v>
+      </c>
       <c r="C896">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17970,6 +20658,9 @@
         <f t="shared" si="56"/>
         <v>896</v>
       </c>
+      <c r="B897" t="s">
+        <v>26</v>
+      </c>
       <c r="C897">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -17988,6 +20679,9 @@
         <f t="shared" si="56"/>
         <v>897</v>
       </c>
+      <c r="B898" t="s">
+        <v>26</v>
+      </c>
       <c r="C898">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -18006,6 +20700,9 @@
         <f t="shared" si="56"/>
         <v>898</v>
       </c>
+      <c r="B899" t="s">
+        <v>26</v>
+      </c>
       <c r="C899">
         <f t="shared" si="57"/>
         <v>113</v>
@@ -18024,6 +20721,9 @@
         <f t="shared" ref="A900:A957" si="60">A899+1</f>
         <v>899</v>
       </c>
+      <c r="B900" t="s">
+        <v>26</v>
+      </c>
       <c r="C900">
         <f t="shared" ref="C900:C936" si="61">C899</f>
         <v>113</v>
@@ -18042,6 +20742,9 @@
         <f t="shared" si="60"/>
         <v>900</v>
       </c>
+      <c r="B901" t="s">
+        <v>26</v>
+      </c>
       <c r="C901">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18060,6 +20763,9 @@
         <f t="shared" si="60"/>
         <v>901</v>
       </c>
+      <c r="B902" t="s">
+        <v>26</v>
+      </c>
       <c r="C902">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18078,6 +20784,9 @@
         <f t="shared" si="60"/>
         <v>902</v>
       </c>
+      <c r="B903" t="s">
+        <v>26</v>
+      </c>
       <c r="C903">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18096,6 +20805,9 @@
         <f t="shared" si="60"/>
         <v>903</v>
       </c>
+      <c r="B904" t="s">
+        <v>26</v>
+      </c>
       <c r="C904">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18114,6 +20826,9 @@
         <f t="shared" si="60"/>
         <v>904</v>
       </c>
+      <c r="B905" t="s">
+        <v>26</v>
+      </c>
       <c r="C905">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18132,6 +20847,9 @@
         <f t="shared" si="60"/>
         <v>905</v>
       </c>
+      <c r="B906" t="s">
+        <v>26</v>
+      </c>
       <c r="C906">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18150,6 +20868,9 @@
         <f t="shared" si="60"/>
         <v>906</v>
       </c>
+      <c r="B907" t="s">
+        <v>26</v>
+      </c>
       <c r="C907">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18168,6 +20889,9 @@
         <f t="shared" si="60"/>
         <v>907</v>
       </c>
+      <c r="B908" t="s">
+        <v>26</v>
+      </c>
       <c r="C908">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18186,6 +20910,9 @@
         <f t="shared" si="60"/>
         <v>908</v>
       </c>
+      <c r="B909" t="s">
+        <v>26</v>
+      </c>
       <c r="C909">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18204,6 +20931,9 @@
         <f t="shared" si="60"/>
         <v>909</v>
       </c>
+      <c r="B910" t="s">
+        <v>26</v>
+      </c>
       <c r="C910">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18222,6 +20952,9 @@
         <f t="shared" si="60"/>
         <v>910</v>
       </c>
+      <c r="B911" t="s">
+        <v>26</v>
+      </c>
       <c r="C911">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18240,6 +20973,9 @@
         <f t="shared" si="60"/>
         <v>911</v>
       </c>
+      <c r="B912" t="s">
+        <v>26</v>
+      </c>
       <c r="C912">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18258,6 +20994,9 @@
         <f t="shared" si="60"/>
         <v>912</v>
       </c>
+      <c r="B913" t="s">
+        <v>26</v>
+      </c>
       <c r="C913">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18276,6 +21015,9 @@
         <f t="shared" si="60"/>
         <v>913</v>
       </c>
+      <c r="B914" t="s">
+        <v>26</v>
+      </c>
       <c r="C914">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18294,6 +21036,9 @@
         <f t="shared" si="60"/>
         <v>914</v>
       </c>
+      <c r="B915" t="s">
+        <v>26</v>
+      </c>
       <c r="C915">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18312,6 +21057,9 @@
         <f t="shared" si="60"/>
         <v>915</v>
       </c>
+      <c r="B916" t="s">
+        <v>26</v>
+      </c>
       <c r="C916">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18330,6 +21078,9 @@
         <f t="shared" si="60"/>
         <v>916</v>
       </c>
+      <c r="B917" t="s">
+        <v>26</v>
+      </c>
       <c r="C917">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18348,6 +21099,9 @@
         <f t="shared" si="60"/>
         <v>917</v>
       </c>
+      <c r="B918" t="s">
+        <v>26</v>
+      </c>
       <c r="C918">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18366,6 +21120,9 @@
         <f t="shared" si="60"/>
         <v>918</v>
       </c>
+      <c r="B919" t="s">
+        <v>26</v>
+      </c>
       <c r="C919">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18384,6 +21141,9 @@
         <f t="shared" si="60"/>
         <v>919</v>
       </c>
+      <c r="B920" t="s">
+        <v>26</v>
+      </c>
       <c r="C920">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18428,6 +21188,9 @@
         <f t="shared" si="60"/>
         <v>920</v>
       </c>
+      <c r="B921" t="s">
+        <v>26</v>
+      </c>
       <c r="C921">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18472,6 +21235,9 @@
         <f t="shared" si="60"/>
         <v>921</v>
       </c>
+      <c r="B922" t="s">
+        <v>26</v>
+      </c>
       <c r="C922">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18516,6 +21282,9 @@
         <f t="shared" si="60"/>
         <v>922</v>
       </c>
+      <c r="B923" t="s">
+        <v>26</v>
+      </c>
       <c r="C923">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18560,6 +21329,9 @@
         <f t="shared" si="60"/>
         <v>923</v>
       </c>
+      <c r="B924" t="s">
+        <v>26</v>
+      </c>
       <c r="C924">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18604,6 +21376,9 @@
         <f t="shared" si="60"/>
         <v>924</v>
       </c>
+      <c r="B925" t="s">
+        <v>26</v>
+      </c>
       <c r="C925">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18648,6 +21423,9 @@
         <f t="shared" si="60"/>
         <v>925</v>
       </c>
+      <c r="B926" t="s">
+        <v>26</v>
+      </c>
       <c r="C926">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18692,6 +21470,9 @@
         <f t="shared" si="60"/>
         <v>926</v>
       </c>
+      <c r="B927" t="s">
+        <v>26</v>
+      </c>
       <c r="C927">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18736,6 +21517,9 @@
         <f t="shared" si="60"/>
         <v>927</v>
       </c>
+      <c r="B928" t="s">
+        <v>26</v>
+      </c>
       <c r="C928">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18780,6 +21564,9 @@
         <f t="shared" si="60"/>
         <v>928</v>
       </c>
+      <c r="B929" t="s">
+        <v>26</v>
+      </c>
       <c r="C929">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18824,6 +21611,9 @@
         <f t="shared" si="60"/>
         <v>929</v>
       </c>
+      <c r="B930" t="s">
+        <v>26</v>
+      </c>
       <c r="C930">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18841,6 +21631,9 @@
         <f t="shared" si="60"/>
         <v>930</v>
       </c>
+      <c r="B931" t="s">
+        <v>26</v>
+      </c>
       <c r="C931">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18859,6 +21652,9 @@
         <f t="shared" si="60"/>
         <v>931</v>
       </c>
+      <c r="B932" t="s">
+        <v>26</v>
+      </c>
       <c r="C932">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18877,6 +21673,9 @@
         <f t="shared" si="60"/>
         <v>932</v>
       </c>
+      <c r="B933" t="s">
+        <v>26</v>
+      </c>
       <c r="C933">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18895,6 +21694,9 @@
         <f t="shared" si="60"/>
         <v>933</v>
       </c>
+      <c r="B934" t="s">
+        <v>26</v>
+      </c>
       <c r="C934">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18913,6 +21715,9 @@
         <f t="shared" si="60"/>
         <v>934</v>
       </c>
+      <c r="B935" t="s">
+        <v>26</v>
+      </c>
       <c r="C935">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18931,6 +21736,9 @@
         <f t="shared" si="60"/>
         <v>935</v>
       </c>
+      <c r="B936" t="s">
+        <v>26</v>
+      </c>
       <c r="C936">
         <f t="shared" si="61"/>
         <v>113</v>
@@ -18949,6 +21757,9 @@
         <f t="shared" si="60"/>
         <v>936</v>
       </c>
+      <c r="B937" t="s">
+        <v>26</v>
+      </c>
       <c r="C937">
         <v>114</v>
       </c>
@@ -18965,6 +21776,9 @@
         <f t="shared" si="60"/>
         <v>937</v>
       </c>
+      <c r="B938" t="s">
+        <v>26</v>
+      </c>
       <c r="C938">
         <f>C937</f>
         <v>114</v>
@@ -18983,6 +21797,9 @@
         <f t="shared" si="60"/>
         <v>938</v>
       </c>
+      <c r="B939" t="s">
+        <v>26</v>
+      </c>
       <c r="C939">
         <f t="shared" ref="C939:C957" si="64">C938</f>
         <v>114</v>
@@ -19001,6 +21818,9 @@
         <f t="shared" si="60"/>
         <v>939</v>
       </c>
+      <c r="B940" t="s">
+        <v>26</v>
+      </c>
       <c r="C940">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19019,6 +21839,9 @@
         <f t="shared" si="60"/>
         <v>940</v>
       </c>
+      <c r="B941" t="s">
+        <v>26</v>
+      </c>
       <c r="C941">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19037,6 +21860,9 @@
         <f t="shared" si="60"/>
         <v>941</v>
       </c>
+      <c r="B942" t="s">
+        <v>26</v>
+      </c>
       <c r="C942">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19055,6 +21881,9 @@
         <f t="shared" si="60"/>
         <v>942</v>
       </c>
+      <c r="B943" t="s">
+        <v>26</v>
+      </c>
       <c r="C943">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19073,6 +21902,9 @@
         <f t="shared" si="60"/>
         <v>943</v>
       </c>
+      <c r="B944" t="s">
+        <v>26</v>
+      </c>
       <c r="C944">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19091,6 +21923,9 @@
         <f t="shared" si="60"/>
         <v>944</v>
       </c>
+      <c r="B945" t="s">
+        <v>26</v>
+      </c>
       <c r="C945">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19109,6 +21944,9 @@
         <f t="shared" si="60"/>
         <v>945</v>
       </c>
+      <c r="B946" t="s">
+        <v>26</v>
+      </c>
       <c r="C946">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19127,6 +21965,9 @@
         <f t="shared" si="60"/>
         <v>946</v>
       </c>
+      <c r="B947" t="s">
+        <v>26</v>
+      </c>
       <c r="C947">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19145,6 +21986,9 @@
         <f t="shared" si="60"/>
         <v>947</v>
       </c>
+      <c r="B948" t="s">
+        <v>26</v>
+      </c>
       <c r="C948">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19163,6 +22007,9 @@
         <f t="shared" si="60"/>
         <v>948</v>
       </c>
+      <c r="B949" t="s">
+        <v>26</v>
+      </c>
       <c r="C949">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19181,6 +22028,9 @@
         <f t="shared" si="60"/>
         <v>949</v>
       </c>
+      <c r="B950" t="s">
+        <v>26</v>
+      </c>
       <c r="C950">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19199,6 +22049,9 @@
         <f t="shared" si="60"/>
         <v>950</v>
       </c>
+      <c r="B951" t="s">
+        <v>26</v>
+      </c>
       <c r="C951">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19217,6 +22070,9 @@
         <f t="shared" si="60"/>
         <v>951</v>
       </c>
+      <c r="B952" t="s">
+        <v>26</v>
+      </c>
       <c r="C952">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19261,6 +22117,9 @@
         <f t="shared" si="60"/>
         <v>952</v>
       </c>
+      <c r="B953" t="s">
+        <v>26</v>
+      </c>
       <c r="C953">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19278,6 +22137,9 @@
         <f t="shared" si="60"/>
         <v>953</v>
       </c>
+      <c r="B954" t="s">
+        <v>26</v>
+      </c>
       <c r="C954">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19296,6 +22158,9 @@
         <f t="shared" si="60"/>
         <v>954</v>
       </c>
+      <c r="B955" t="s">
+        <v>26</v>
+      </c>
       <c r="C955">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19314,6 +22179,9 @@
         <f t="shared" si="60"/>
         <v>955</v>
       </c>
+      <c r="B956" t="s">
+        <v>26</v>
+      </c>
       <c r="C956">
         <f t="shared" si="64"/>
         <v>114</v>
@@ -19332,6 +22200,9 @@
         <f t="shared" si="60"/>
         <v>956</v>
       </c>
+      <c r="B957" t="s">
+        <v>26</v>
+      </c>
       <c r="C957">
         <f t="shared" si="64"/>
         <v>114</v>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -95,6 +95,12 @@
   </si>
   <si>
     <t>Choctaw</t>
+  </si>
+  <si>
+    <t>Image Name</t>
+  </si>
+  <si>
+    <t>Image Binary</t>
   </si>
 </sst>
 </file>
@@ -426,15 +432,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O957"/>
+  <dimension ref="A1:Q957"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="36.140625" customWidth="1"/>
     <col min="12" max="12" width="16.28515625" customWidth="1"/>
     <col min="14" max="14" width="52.140625" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,8 +488,14 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -498,7 +512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -519,7 +533,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -540,7 +554,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -587,7 +601,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -607,7 +621,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -628,7 +642,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -649,7 +663,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -670,7 +684,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -691,7 +705,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -712,7 +726,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -733,7 +747,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -754,7 +768,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -775,7 +789,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -796,7 +810,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -16251,9 +16265,35 @@
         <f t="shared" si="46"/>
         <v>112</v>
       </c>
-      <c r="L725" t="str">
-        <f t="shared" si="49"/>
-        <v>Blood (Minor)</v>
+      <c r="D725" t="s">
+        <v>23</v>
+      </c>
+      <c r="E725" t="s">
+        <v>24</v>
+      </c>
+      <c r="F725" t="s">
+        <v>24</v>
+      </c>
+      <c r="G725" t="s">
+        <v>24</v>
+      </c>
+      <c r="H725">
+        <v>-1</v>
+      </c>
+      <c r="I725" t="s">
+        <v>24</v>
+      </c>
+      <c r="J725" t="s">
+        <v>24</v>
+      </c>
+      <c r="K725" t="s">
+        <v>24</v>
+      </c>
+      <c r="L725" t="s">
+        <v>24</v>
+      </c>
+      <c r="M725" t="s">
+        <v>24</v>
       </c>
       <c r="N725" t="str">
         <f t="shared" si="47"/>
@@ -16272,9 +16312,8 @@
         <f t="shared" si="46"/>
         <v>112</v>
       </c>
-      <c r="L726" t="str">
-        <f t="shared" si="49"/>
-        <v>Blood (Minor)</v>
+      <c r="L726" t="s">
+        <v>15</v>
       </c>
       <c r="N726" t="str">
         <f t="shared" si="47"/>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Minor By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -97,10 +97,13 @@
     <t>Choctaw</t>
   </si>
   <si>
-    <t>Image Name</t>
+    <t>ImageName</t>
   </si>
   <si>
-    <t>Image Binary</t>
+    <t>ImageBinary</t>
+  </si>
+  <si>
+    <t>TribeRelationship</t>
   </si>
 </sst>
 </file>
@@ -432,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q957"/>
+  <dimension ref="A1:R957"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="36.140625" customWidth="1"/>
@@ -440,9 +443,10 @@
     <col min="14" max="14" width="52.140625" customWidth="1"/>
     <col min="16" max="16" width="13.7109375" customWidth="1"/>
     <col min="17" max="17" width="16.28515625" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -494,8 +498,11 @@
       <c r="Q1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -512,7 +519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -533,7 +540,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -554,7 +561,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -601,7 +608,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -621,7 +628,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -642,7 +649,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -663,7 +670,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -684,7 +691,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -705,7 +712,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -726,7 +733,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -747,7 +754,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -768,7 +775,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -789,7 +796,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -810,7 +817,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 108</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
